--- a/api/2/clv2/xlsx/en/SectorCOFOG.xlsx
+++ b/api/2/clv2/xlsx/en/SectorCOFOG.xlsx
@@ -28,21 +28,21 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
+    <t>codeforiati:cofog-division</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-class</t>
   </si>
   <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
     <t>codeforiati:category-name</t>
   </si>
   <si>
@@ -61,21 +61,21 @@
     <t>active</t>
   </si>
   <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
     <t>110</t>
   </si>
   <si>
+    <t>09 - Education</t>
+  </si>
+  <si>
     <t>09.8.0 - Education n.e.c. (CS)</t>
   </si>
   <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
     <t>Education, Level Unspecified</t>
   </si>
   <si>
@@ -91,12 +91,12 @@
     <t>Educational buildings, equipment, materials; subsidiary services to education (boarding facilities, staff housing); language training; colloquia, seminars, lectures, etc.</t>
   </si>
   <si>
+    <t>09.6 - Subsidiary services to education</t>
+  </si>
+  <si>
     <t>09.6.0 - Subsidiary services to education (IS)</t>
   </si>
   <si>
-    <t>09.6 - Subsidiary services to education</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
@@ -115,12 +115,12 @@
     <t>Research and studies on education effectiveness, relevance and quality; systematic evaluation and monitoring.</t>
   </si>
   <si>
+    <t>09.7 - R&amp;D Education</t>
+  </si>
+  <si>
     <t>09.7.0 - R&amp;D Education (CS)</t>
   </si>
   <si>
-    <t>09.7 - R&amp;D Education</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
@@ -130,15 +130,15 @@
     <t>Formal and non-formal primary education for children; all elementary and first cycle systematic instruction; provision of learning materials.</t>
   </si>
   <si>
+    <t>09.1 - Pre‐primary and primary education</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
-    <t>09.1 - Pre‐primary and primary education</t>
-  </si>
-  <si>
     <t>Basic Education</t>
   </si>
   <si>
@@ -190,15 +190,15 @@
     <t>Provision of meals or snacks at school; other uses of food for the achievement of educational outcomes including 'take-home' food rations provided as economic incentives to families (or foster families, or other child care institutions) in return for a child's regular attendance at school; food provided to adults or youth who attend literacy or vocational training programmes; food for pre-school activities with an educational component. These activities may help reduce children's hunger during the school day if provision of food/meals contains bioavailable nutrients to address specific nutrition needs and have nutrition expected outcomes in school children, or if the rationale mainstream nutrition or expected outcome is nutrition-linked.</t>
   </si>
   <si>
+    <t>07.4 - Public health services</t>
+  </si>
+  <si>
+    <t>07 - Health</t>
+  </si>
+  <si>
     <t>07.4.0 - Public health services (IS)</t>
   </si>
   <si>
-    <t>07 - Health</t>
-  </si>
-  <si>
-    <t>07.4 - Public health services</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
@@ -208,12 +208,12 @@
     <t>Second cycle systematic instruction at junior level.</t>
   </si>
   <si>
+    <t>09.2 - Secondary education</t>
+  </si>
+  <si>
     <t>09.2.1 - Lower‐secondary education (IS)</t>
   </si>
   <si>
-    <t>09.2 - Secondary education</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
@@ -241,12 +241,12 @@
     <t>Elementary vocational training and secondary level technical education; on-the job training; apprenticeships; including informal vocational training.</t>
   </si>
   <si>
+    <t>09.5 - Education not definable by level</t>
+  </si>
+  <si>
     <t>09.5.0 - Education not definable by level (IS)</t>
   </si>
   <si>
-    <t>09.5 - Education not definable by level</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
@@ -256,15 +256,15 @@
     <t>Degree and diploma programmes at universities, colleges and polytechnics; scholarships.</t>
   </si>
   <si>
+    <t>09.4 - Tertiary education</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.4 - Tertiary education</t>
-  </si>
-  <si>
     <t>Post-Secondary Education</t>
   </si>
   <si>
@@ -277,12 +277,12 @@
     <t>Professional-level vocational training programmes and in-service training.</t>
   </si>
   <si>
+    <t>09.3 - Post‐secondary non‐tertiary education</t>
+  </si>
+  <si>
     <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.3 - Post‐secondary non‐tertiary education</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
@@ -292,6 +292,9 @@
     <t>Health sector policy, planning and programmes; aid to health ministries, public health administration; institution capacity building and advice; medical insurance programmes; including health system strengthening and health governance; unspecified health activities.</t>
   </si>
   <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
@@ -301,9 +304,6 @@
     <t>07.6.0 - Health n.e.c. (CS)</t>
   </si>
   <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
     <t>Health, General</t>
   </si>
   <si>
@@ -328,12 +328,12 @@
     <t>General medical research (excluding basic health research and research for prevention and control of NCDs (12382)).</t>
   </si>
   <si>
+    <t>07.5 - R&amp;D Health</t>
+  </si>
+  <si>
     <t>07.5.0 - R&amp;D Health (CS)</t>
   </si>
   <si>
-    <t>07.5 - R&amp;D Health</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
@@ -343,12 +343,12 @@
     <t>Laboratories, specialised clinics and hospitals (including equipment and supplies); ambulances; dental services; medical rehabilitation. Excludes noncommunicable diseases (123xx).</t>
   </si>
   <si>
+    <t>07.2 - Outpatient services</t>
+  </si>
+  <si>
     <t>07.2.1 - General medical services (IS)</t>
   </si>
   <si>
-    <t>07.2 - Outpatient services</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -382,12 +382,12 @@
     <t>District-level hospitals, clinics and dispensaries and related medical equipment; excluding specialised hospitals and clinics (12191).</t>
   </si>
   <si>
+    <t>07.3 - Hospital services</t>
+  </si>
+  <si>
     <t>07.3.1 - General hospital services (IS)</t>
   </si>
   <si>
-    <t>07.3 - Hospital services</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -580,18 +580,18 @@
     <t>Water sector policy and governance, including legislation, regulation, planning and management as well as transboundary management of water; institutional capacity development; activities supporting the Integrated Water Resource Management approach (IWRM: see box below).</t>
   </si>
   <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
+    <t>06 - Housing and community amenities</t>
+  </si>
+  <si>
     <t>06.3.0 - Water supply (CS)</t>
   </si>
   <si>
-    <t>06 - Housing and community amenities</t>
-  </si>
-  <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
     <t>Water Supply &amp; Sanitation</t>
   </si>
   <si>
@@ -604,15 +604,15 @@
     <t>Collection and usage of quantitative and qualitative data on water resources; creation and sharing of water knowledge; conservation and rehabilitation of inland surface waters (rivers, lakes etc.), ground water and coastal waters; prevention of water contamination.</t>
   </si>
   <si>
+    <t>05.6 - Environmental protection n.e.c.</t>
+  </si>
+  <si>
+    <t>05 - Environmental protection</t>
+  </si>
+  <si>
     <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>05 - Environmental protection</t>
-  </si>
-  <si>
-    <t>05.6 - Environmental protection n.e.c.</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>Large scale sewerage including trunk sewers and sewage pumping stations; domestic and industrial waste water treatment plants.</t>
   </si>
   <si>
+    <t>05.2 - Waste water management</t>
+  </si>
+  <si>
     <t>05.2.0 - Waste water management (CS)</t>
   </si>
   <si>
-    <t>05.2 - Waste water management</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -691,12 +691,12 @@
     <t>Municipal and industrial solid waste management, including hazardous and toxic waste; collection, disposal and treatment; landfill areas; composting and reuse.</t>
   </si>
   <si>
+    <t>05.1 - Waste management</t>
+  </si>
+  <si>
     <t>05.1.0 - Waste management (CS)</t>
   </si>
   <si>
-    <t>05.1 - Waste management</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
@@ -715,21 +715,21 @@
     <t>Institution-building assistance to strengthen core public sector management systems and capacities. This includes general public policy management, co-ordination, planning and reform; human resource management; organisational development; civil service reform; e-government; development planning, monitoring and evaluation; support to ministries involved in aid co-ordination; other ministries and government departments when sector cannot be specified. (Use specific sector codes for development of systems and capacities in sector ministries. For macro-economic policy use code 15142. For public procurement use code 15125.)</t>
   </si>
   <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
     <t>150</t>
   </si>
   <si>
+    <t>01 - General public services</t>
+  </si>
+  <si>
     <t>01.3.1 - General personnel services (CS)</t>
   </si>
   <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
@@ -745,12 +745,12 @@
     <t>Fiscal policy and planning; support to ministries of finance; strengthening financial and managerial accountability; public expenditure management; improving financial management systems; budget drafting; inter-governmental fiscal relations, public audit, public debt. (Use code 15114 for domestic revenue mobilisation and code 33120 for customs).</t>
   </si>
   <si>
+    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
+  </si>
+  <si>
     <t>01.1.2 - Financial and fiscal affairs (CS)</t>
   </si>
   <si>
-    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
@@ -760,12 +760,12 @@
     <t>Decentralisation processes (including political, administrative and fiscal dimensions); intergovernmental relations and federalism; strengthening departments of regional and local government, regional and local authorities and their national associations. (Use specific sector codes for decentralisation of sector management and services.)</t>
   </si>
   <si>
+    <t>01.8 - Transfers of a general character between different levels of government</t>
+  </si>
+  <si>
     <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
   </si>
   <si>
-    <t>01.8 - Transfers of a general character between different levels of government</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
@@ -775,15 +775,15 @@
     <t>Specialised organisations, institutions and frameworks for the prevention of and combat against corruption, bribery, money-laundering and other aspects of organised crime, with or without law enforcement powers, e.g. anti-corruption commissions and monitoring bodies, special investigation services, institutions and initiatives of integrity and ethics oversight, specialised NGOs, other civil society and citizens' organisations directly concerned with corruption.</t>
   </si>
   <si>
+    <t>03.6 - Public order and safety n.e.c.</t>
+  </si>
+  <si>
+    <t>03 - Public order and safety</t>
+  </si>
+  <si>
     <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
   </si>
   <si>
-    <t>03 - Public order and safety</t>
-  </si>
-  <si>
-    <t>03.6 - Public order and safety n.e.c.</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -859,12 +859,12 @@
     <t>Support to administration of developing countries' foreign aid (including triangular and south-south cooperation).</t>
   </si>
   <si>
+    <t>01.2 - Foreign economic aid</t>
+  </si>
+  <si>
     <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
   </si>
   <si>
-    <t>01.2 - Foreign economic aid</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -943,12 +943,12 @@
     <t>Judicial law and order sectors; policy development within ministries of justice or equivalents.</t>
   </si>
   <si>
+    <t>03.3 - Law courts</t>
+  </si>
+  <si>
     <t>03.3.0 - Law courts (CS)</t>
   </si>
   <si>
-    <t>03.3 - Law courts</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
@@ -958,12 +958,12 @@
     <t>Police affairs and services.</t>
   </si>
   <si>
+    <t>03.1 - Police services</t>
+  </si>
+  <si>
     <t>03.1.0 - Police services (CS)</t>
   </si>
   <si>
-    <t>03.1 - Police services</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
@@ -973,12 +973,12 @@
     <t>Fire-prevention and fire-fighting affairs and services.</t>
   </si>
   <si>
+    <t>03.2 - Fire‐protection services</t>
+  </si>
+  <si>
     <t>03.2.0 - Fire‐protection services (CS)</t>
   </si>
   <si>
-    <t>03.2 - Fire‐protection services</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -1012,12 +1012,12 @@
     <t>Prisons</t>
   </si>
   <si>
+    <t>03.4 - Prisons</t>
+  </si>
+  <si>
     <t>03.4.0 - Prisons (CS)</t>
   </si>
   <si>
-    <t>03.4 - Prisons</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
@@ -1027,15 +1027,15 @@
     <t>Support to macroeconomic stability, debt sustainability and structural reforms. Includes technical assistance for strategic formulation of policies, laws and regulation; capacity building to enhance public sector development; policy-based funding. For fiscal policy and domestic revenue mobilisation use codes 15111 and 15114.</t>
   </si>
   <si>
+    <t>04.1 - General economic, commercial and labour affairs</t>
+  </si>
+  <si>
+    <t>04 - Economic affairs</t>
+  </si>
+  <si>
     <t>04.1.1 - General economic and commercial affairs (CS)</t>
   </si>
   <si>
-    <t>04 - Economic affairs</t>
-  </si>
-  <si>
-    <t>04.1 - General economic, commercial and labour affairs</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -1072,12 +1072,12 @@
     <t>Electoral management bodies and processes, election observation, voters' education. (Use code 15230 when in the context of an international peacekeeping operation.)</t>
   </si>
   <si>
+    <t>01.6 - General public services n.e.c.</t>
+  </si>
+  <si>
     <t>01.6.0 - General public services n.e.c. (CS)</t>
   </si>
   <si>
-    <t>01.6 - General public services n.e.c.</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -1099,12 +1099,12 @@
     <t>Activities that support free and uncensored flow of information on public issues; activities that increase the editorial and technical skills and the integrity of the print and broadcast media, e.g. training of journalists. (Use codes 22010-22040 for provision of equipment and capital assistance to media.)</t>
   </si>
   <si>
+    <t>04.6 - Communication</t>
+  </si>
+  <si>
     <t>04.6.0 - Communication (CS)</t>
   </si>
   <si>
-    <t>04.6 - Communication</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -1147,15 +1147,15 @@
     <t>Support for feminist, women-led and women's rights organisations and movements, and institutions (governmental and non-govermental) at all levels to enhance their effectiveness, influence and substainability (activities and core-funding). These organisations exist to bring about transformative change for gender equality and/or the rights of women and girls in developing countries. Their activities include agenda-setting, advocacy, policy dialogue, capacity development, awareness raising and prevention, service provision, conflict-prevention and peacebuilding, research, organising, and alliance and network building</t>
   </si>
   <si>
+    <t>10.7 - Social exclusion n.e.c.</t>
+  </si>
+  <si>
+    <t>10 - Social protection</t>
+  </si>
+  <si>
     <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
   </si>
   <si>
-    <t>10 - Social protection</t>
-  </si>
-  <si>
-    <t>10.7 - Social exclusion n.e.c.</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -1192,12 +1192,12 @@
     <t>Collection, production, management and dissemination of statistics and data related to Government &amp; Civil Society. Includes macroeconomic statistics, government finance, fiscal and public sector statistics, support to development of administrative data infrastructure, civil society surveys.</t>
   </si>
   <si>
+    <t>01.5 - R&amp;D General public services</t>
+  </si>
+  <si>
     <t>01.5.0 - R&amp;D General public services (CS)</t>
   </si>
   <si>
-    <t>01.5 - R&amp;D General public services</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -1231,15 +1231,15 @@
     <t>Bilateral participation in peacekeeping operations mandated or authorised by the United Nations (UN) through Security Council resolutions, and conducted by international organisations, e.g. UN, NATO, the European Union (Security and Defence Policy security-related operations), or regional groupings of developing countries. Direct contributions to the UN Department for Peacekeeping Operations (UNDPKO) budget are excluded from bilateral ODA (they are reportable in part as multilateral ODA, see Annex 9). The activities that can be reported as bilateral ODA under this code are limited to: human rights and election monitoring; reintegration of demobilised soldiers; rehabilitation of basic national infrastructure; monitoring or retraining of civil administrators and police forces; security sector reform and other rule of law-related activities; training in customs and border control procedures; advice or training in fiscal or macroeconomic stabilisation policy; repatriation and demobilisation of armed factions, and disposal of their weapons; explosive mine removal. The enforcement aspects of international peacekeeping operations are not reportable as ODA. ODA-eligible bilateral participation in peacekeeping operations can take the form of financing or provision of equipment or military or civilian personnel (e.g. police officers). The reportable cost is calculated as the excess over what the personnel and equipment would have cost to maintain had they not been assigned to take part in a peace operation. Costs for military contingents participating in UNDPKO peacekeeping operations are not reportable as ODA. International peacekeeping operations may include humanitarian-type activities (contributions to the form of equipment or personnel), as described in codes 7xxxx. These should be included under code 15230 if they are an integrated part of the activities above, otherwise they should be reported as humanitarian aid. NB: When using this code, indicate the name of the operation in the short description of the activity reported.</t>
   </si>
   <si>
+    <t>02.3 - Foreign military aid</t>
+  </si>
+  <si>
+    <t>02 - Defence</t>
+  </si>
+  <si>
     <t>02.3.0 - Foreign military aid (CS)</t>
   </si>
   <si>
-    <t>02 - Defence</t>
-  </si>
-  <si>
-    <t>02.3 - Foreign military aid</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -1276,15 +1276,15 @@
     <t>Social protection or social security strategies, legislation and administration; institution capacity building and advice; social security and other social schemes; support programmes, cash benefits, pensions and special programmes for older persons, orphans, persons with disabilities, children, mothers with newborns, those living in poverty, without jobs and other vulnerable groups; social dimensions of structural adjustment.</t>
   </si>
   <si>
+    <t>10.9 - Social protection n.e.c.</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>10.9 - Social protection n.e.c.</t>
-  </si>
-  <si>
     <t>Other Social Infrastructure &amp; Services</t>
   </si>
   <si>
@@ -1315,12 +1315,12 @@
     <t>Social protection schemes in the form of cash or in-kind benefits, including pensions, against the risks linked to old age.</t>
   </si>
   <si>
+    <t>10.2 - Old age</t>
+  </si>
+  <si>
     <t>10.2.0 - Old age (IS)</t>
   </si>
   <si>
-    <t>10.2 - Old age</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -1348,12 +1348,12 @@
     <t>Employment policy and planning; institution capacity building and advice; employment creation and income generation programmes; including activities specifically designed for the needs of vulnerable groups.</t>
   </si>
   <si>
+    <t>10.5 - Unemployment</t>
+  </si>
+  <si>
     <t>10.5.0 - Unemployment (IS)</t>
   </si>
   <si>
-    <t>10.5 - Unemployment</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
@@ -1363,12 +1363,12 @@
     <t>Housing sector policy, planning and programmes; excluding low-cost housing and slum clearance (16040).</t>
   </si>
   <si>
+    <t>06.6 - Housing and community amenities n.e.c.</t>
+  </si>
+  <si>
     <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
   </si>
   <si>
-    <t>06.6 - Housing and community amenities n.e.c.</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
@@ -1378,12 +1378,12 @@
     <t>Including slum clearance.</t>
   </si>
   <si>
+    <t>06.1 - Housing development</t>
+  </si>
+  <si>
     <t>06.1.0 - Housing development (CS)</t>
   </si>
   <si>
-    <t>06.1 - Housing development</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
@@ -1402,15 +1402,15 @@
     <t>Including libraries and museums.</t>
   </si>
   <si>
+    <t>08.2 - Cultural services</t>
+  </si>
+  <si>
+    <t>08 - Recreation, culture and religion</t>
+  </si>
+  <si>
     <t>08.2.0 - Cultural services (IS)</t>
   </si>
   <si>
-    <t>08 - Recreation, culture and religion</t>
-  </si>
-  <si>
-    <t>08.2 - Cultural services</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -1444,12 +1444,12 @@
     <t>Recreation and sport</t>
   </si>
   <si>
+    <t>08.1 - Recreational and sporting services</t>
+  </si>
+  <si>
     <t>08.1.0 - Recreational and sporting services (IS)</t>
   </si>
   <si>
-    <t>08.1 - Recreational and sporting services</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -1528,12 +1528,12 @@
     <t>Road infrastructure, road vehicles; passenger road transport, motor passenger cars.</t>
   </si>
   <si>
+    <t>04.5 - Transport</t>
+  </si>
+  <si>
     <t>04.5.1 - Road transport (CS)</t>
   </si>
   <si>
-    <t>04.5 - Transport</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -1615,12 +1615,12 @@
     <t>Whether or not related to transportation. Whenever possible, report storage projects under the sector of the resource being stored.</t>
   </si>
   <si>
+    <t>04.7 - Other industries</t>
+  </si>
+  <si>
     <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
   </si>
   <si>
-    <t>04.7 - Other industries</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -1684,12 +1684,12 @@
     <t>Radio and TV links, equipment; newspapers; printing and publishing.</t>
   </si>
   <si>
+    <t>08.3 - Broadcasting and publishing services</t>
+  </si>
+  <si>
     <t>08.3.0 - Broadcasting and publishing services (CS)</t>
   </si>
   <si>
-    <t>08.3 - Broadcasting and publishing services</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
@@ -1708,6 +1708,9 @@
     <t>Energy sector policy, planning; aid to energy ministries and other governmental or nongovernmental institutions for activities related to the SDG7; institution capacity building and advice; tariffs, market building, unspecified energy activities; energy activities for which a more specific code cannot be assigned.</t>
   </si>
   <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
@@ -1717,9 +1720,6 @@
     <t>04.3.5 - Electricity (CS)</t>
   </si>
   <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
     <t>Energy Policy</t>
   </si>
   <si>
@@ -1741,12 +1741,12 @@
     <t>Regulation of the energy sector, including wholesale and retail electricity provision.</t>
   </si>
   <si>
+    <t>04.8 - R&amp;D Economic affairs</t>
+  </si>
+  <si>
     <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
   </si>
   <si>
-    <t>04.8 - R&amp;D Economic affairs</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -2131,6 +2131,9 @@
     <t>Agricultural sector policy, planning and programmes; aid to agricultural ministries; institution capacity building and advice; unspecified agriculture.</t>
   </si>
   <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
@@ -2140,9 +2143,6 @@
     <t>04.2.1 - Agriculture (CS)</t>
   </si>
   <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
     <t>Agriculture</t>
   </si>
   <si>
@@ -2419,6 +2419,9 @@
     <t>Industrial sector policy, planning and programmes; institution capacity building and advice; unspecified industrial activities; manufacturing of goods not specified below.</t>
   </si>
   <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
@@ -2428,9 +2431,6 @@
     <t>04.4.2 - Manufacturing (CS)</t>
   </si>
   <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
     <t>Industry</t>
   </si>
   <si>
@@ -2812,12 +2812,12 @@
     <t>Including natural reserves and actions in the surrounding areas; other measures to protect endangered or vulnerable species and their habitats (e.g. wetlands preservation).</t>
   </si>
   <si>
+    <t>05.4 - Protection of biodiversity and landscape</t>
+  </si>
+  <si>
     <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
   </si>
   <si>
-    <t>05.4 - Protection of biodiversity and landscape</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -2848,15 +2848,15 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>04.9 - Economic affairs n.e.c.</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
-    <t>04.9 - Economic affairs n.e.c.</t>
-  </si>
-  <si>
     <t>Other Multisector</t>
   </si>
   <si>
@@ -2878,12 +2878,12 @@
     <t>Urban development and planning; urban management, land information systems.</t>
   </si>
   <si>
+    <t>06.2 - Community development</t>
+  </si>
+  <si>
     <t>06.2.0 - Community development (CS)</t>
   </si>
   <si>
-    <t>06.2 - Community development</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -2935,12 +2935,12 @@
     <t>Disaster risk reduction activities if not sector specific. Comprises risk assessments, structural prevention measures (e.g. flood prevention infrastructure), preparedness measures (e.g. early warning systems) normative prevention measures (e.g. building codes, land-use planning), and risk transfer systems (e.g. insurance schemes, risk funds). Also includes building local and national capacities and supporting the establishment of efficient and sustainable national structures able to promote disaster risk reduction.</t>
   </si>
   <si>
+    <t>02.2 - Civil defence</t>
+  </si>
+  <si>
     <t>02.2.0 - Civil defence (CS)</t>
   </si>
   <si>
-    <t>02.2 - Civil defence</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
@@ -2959,12 +2959,12 @@
     <t>Short or longer term household food security programmes and activities that improve the access of households to nutritionally adequate diets (excluding any cash transfers within broader social welfare programmes that do not have a specific food security, food acquisition or nutrition focus which should be reported under code 16010).</t>
   </si>
   <si>
+    <t>10.4 - Family and children</t>
+  </si>
+  <si>
     <t>10.4.0 - Family and children (IS)</t>
   </si>
   <si>
-    <t>10.4 - Family and children</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -2992,12 +2992,12 @@
     <t>When sector cannot be identified.</t>
   </si>
   <si>
+    <t>01.4 - Basic research</t>
+  </si>
+  <si>
     <t>01.4.0 - Basic research (CS)</t>
   </si>
   <si>
-    <t>01.4 - Basic research</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -3061,13 +3061,13 @@
     <t>Actions falling outside the code headings below.</t>
   </si>
   <si>
+    <t>01.7 - Public debt transactions</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
     <t>01.7.0 - Public debt transactions (CS)</t>
-  </si>
-  <si>
-    <t>01.7 - Public debt transactions</t>
   </si>
   <si>
     <t>Action Relating to Debt</t>
@@ -3741,13 +3741,13 @@
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
         <v>18</v>
@@ -3811,13 +3811,13 @@
         <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
         <v>18</v>
@@ -3849,10 +3849,10 @@
         <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
         <v>18</v>
@@ -3881,10 +3881,10 @@
         <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G7" t="s">
         <v>17</v>
@@ -3919,10 +3919,10 @@
         <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H8" t="s">
         <v>18</v>
@@ -3954,10 +3954,10 @@
         <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H9" t="s">
         <v>18</v>
@@ -3989,16 +3989,16 @@
         <v>38</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s">
         <v>18</v>
       </c>
       <c r="I10" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="J10" t="s">
         <v>41</v>
@@ -4021,13 +4021,13 @@
         <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G11" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="H11" t="s">
         <v>59</v>
@@ -4056,13 +4056,13 @@
         <v>14</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="H12" t="s">
         <v>18</v>
@@ -4091,19 +4091,19 @@
         <v>14</v>
       </c>
       <c r="E13" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" t="s">
         <v>69</v>
       </c>
-      <c r="F13" t="s">
-        <v>16</v>
-      </c>
       <c r="G13" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="H13" t="s">
         <v>18</v>
       </c>
       <c r="I13" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J13" t="s">
         <v>71</v>
@@ -4126,13 +4126,13 @@
         <v>14</v>
       </c>
       <c r="E14" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" t="s">
         <v>69</v>
       </c>
-      <c r="F14" t="s">
-        <v>16</v>
-      </c>
       <c r="G14" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="H14" t="s">
         <v>18</v>
@@ -4164,10 +4164,10 @@
         <v>80</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="G15" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="H15" t="s">
         <v>18</v>
@@ -4196,13 +4196,13 @@
         <v>14</v>
       </c>
       <c r="E16" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F16" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="G16" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="H16" t="s">
         <v>18</v>
@@ -4301,13 +4301,13 @@
         <v>14</v>
       </c>
       <c r="E19" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="F19" t="s">
         <v>93</v>
       </c>
       <c r="G19" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="H19" t="s">
         <v>59</v>
@@ -4336,13 +4336,13 @@
         <v>14</v>
       </c>
       <c r="E20" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="F20" t="s">
         <v>93</v>
       </c>
       <c r="G20" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="H20" t="s">
         <v>59</v>
@@ -4406,13 +4406,13 @@
         <v>14</v>
       </c>
       <c r="E22" t="s">
+        <v>58</v>
+      </c>
+      <c r="F22" t="s">
         <v>117</v>
       </c>
-      <c r="F22" t="s">
-        <v>93</v>
-      </c>
       <c r="G22" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="H22" t="s">
         <v>59</v>
@@ -4441,13 +4441,13 @@
         <v>14</v>
       </c>
       <c r="E23" t="s">
+        <v>122</v>
+      </c>
+      <c r="F23" t="s">
         <v>117</v>
       </c>
-      <c r="F23" t="s">
-        <v>93</v>
-      </c>
       <c r="G23" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="H23" t="s">
         <v>59</v>
@@ -4476,13 +4476,13 @@
         <v>14</v>
       </c>
       <c r="E24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F24" t="s">
         <v>117</v>
       </c>
-      <c r="F24" t="s">
-        <v>93</v>
-      </c>
       <c r="G24" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="H24" t="s">
         <v>59</v>
@@ -4511,13 +4511,13 @@
         <v>14</v>
       </c>
       <c r="E25" t="s">
+        <v>58</v>
+      </c>
+      <c r="F25" t="s">
         <v>117</v>
       </c>
-      <c r="F25" t="s">
-        <v>93</v>
-      </c>
       <c r="G25" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s">
         <v>59</v>
@@ -4546,13 +4546,13 @@
         <v>14</v>
       </c>
       <c r="E26" t="s">
+        <v>58</v>
+      </c>
+      <c r="F26" t="s">
         <v>117</v>
       </c>
-      <c r="F26" t="s">
-        <v>93</v>
-      </c>
       <c r="G26" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="H26" t="s">
         <v>59</v>
@@ -4581,13 +4581,13 @@
         <v>14</v>
       </c>
       <c r="E27" t="s">
+        <v>58</v>
+      </c>
+      <c r="F27" t="s">
         <v>117</v>
       </c>
-      <c r="F27" t="s">
-        <v>93</v>
-      </c>
       <c r="G27" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="H27" t="s">
         <v>59</v>
@@ -4616,13 +4616,13 @@
         <v>14</v>
       </c>
       <c r="E28" t="s">
+        <v>58</v>
+      </c>
+      <c r="F28" t="s">
         <v>117</v>
       </c>
-      <c r="F28" t="s">
-        <v>93</v>
-      </c>
       <c r="G28" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="H28" t="s">
         <v>59</v>
@@ -4651,13 +4651,13 @@
         <v>14</v>
       </c>
       <c r="E29" t="s">
+        <v>58</v>
+      </c>
+      <c r="F29" t="s">
         <v>117</v>
       </c>
-      <c r="F29" t="s">
-        <v>93</v>
-      </c>
       <c r="G29" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="H29" t="s">
         <v>59</v>
@@ -4686,10 +4686,10 @@
         <v>14</v>
       </c>
       <c r="E30" t="s">
+        <v>92</v>
+      </c>
+      <c r="F30" t="s">
         <v>117</v>
-      </c>
-      <c r="F30" t="s">
-        <v>93</v>
       </c>
       <c r="G30" t="s">
         <v>94</v>
@@ -4721,13 +4721,13 @@
         <v>14</v>
       </c>
       <c r="E31" t="s">
+        <v>58</v>
+      </c>
+      <c r="F31" t="s">
         <v>148</v>
       </c>
-      <c r="F31" t="s">
-        <v>93</v>
-      </c>
       <c r="G31" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="H31" t="s">
         <v>59</v>
@@ -4756,13 +4756,13 @@
         <v>14</v>
       </c>
       <c r="E32" t="s">
+        <v>58</v>
+      </c>
+      <c r="F32" t="s">
         <v>148</v>
       </c>
-      <c r="F32" t="s">
-        <v>93</v>
-      </c>
       <c r="G32" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s">
         <v>59</v>
@@ -4791,13 +4791,13 @@
         <v>14</v>
       </c>
       <c r="E33" t="s">
+        <v>58</v>
+      </c>
+      <c r="F33" t="s">
         <v>148</v>
       </c>
-      <c r="F33" t="s">
-        <v>93</v>
-      </c>
       <c r="G33" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="H33" t="s">
         <v>59</v>
@@ -4826,13 +4826,13 @@
         <v>14</v>
       </c>
       <c r="E34" t="s">
+        <v>58</v>
+      </c>
+      <c r="F34" t="s">
         <v>148</v>
       </c>
-      <c r="F34" t="s">
-        <v>93</v>
-      </c>
       <c r="G34" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="H34" t="s">
         <v>59</v>
@@ -4861,13 +4861,13 @@
         <v>14</v>
       </c>
       <c r="E35" t="s">
+        <v>58</v>
+      </c>
+      <c r="F35" t="s">
         <v>148</v>
       </c>
-      <c r="F35" t="s">
-        <v>93</v>
-      </c>
       <c r="G35" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="H35" t="s">
         <v>59</v>
@@ -4896,13 +4896,13 @@
         <v>14</v>
       </c>
       <c r="E36" t="s">
+        <v>104</v>
+      </c>
+      <c r="F36" t="s">
         <v>148</v>
       </c>
-      <c r="F36" t="s">
-        <v>93</v>
-      </c>
       <c r="G36" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s">
         <v>59</v>
@@ -4930,11 +4930,11 @@
       <c r="D37" t="s">
         <v>14</v>
       </c>
-      <c r="F37" t="s">
+      <c r="E37" t="s">
+        <v>58</v>
+      </c>
+      <c r="G37" t="s">
         <v>168</v>
-      </c>
-      <c r="G37" t="s">
-        <v>58</v>
       </c>
       <c r="H37" t="s">
         <v>59</v>
@@ -4959,11 +4959,11 @@
       <c r="D38" t="s">
         <v>14</v>
       </c>
-      <c r="F38" t="s">
+      <c r="E38" t="s">
+        <v>58</v>
+      </c>
+      <c r="G38" t="s">
         <v>168</v>
-      </c>
-      <c r="G38" t="s">
-        <v>58</v>
       </c>
       <c r="H38" t="s">
         <v>59</v>
@@ -4988,11 +4988,11 @@
       <c r="D39" t="s">
         <v>14</v>
       </c>
-      <c r="F39" t="s">
+      <c r="E39" t="s">
+        <v>58</v>
+      </c>
+      <c r="G39" t="s">
         <v>168</v>
-      </c>
-      <c r="G39" t="s">
-        <v>58</v>
       </c>
       <c r="H39" t="s">
         <v>59</v>
@@ -5017,11 +5017,11 @@
       <c r="D40" t="s">
         <v>14</v>
       </c>
-      <c r="F40" t="s">
+      <c r="E40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G40" t="s">
         <v>168</v>
-      </c>
-      <c r="G40" t="s">
-        <v>58</v>
       </c>
       <c r="H40" t="s">
         <v>59</v>
@@ -5046,11 +5046,11 @@
       <c r="D41" t="s">
         <v>14</v>
       </c>
-      <c r="F41" t="s">
+      <c r="E41" t="s">
+        <v>92</v>
+      </c>
+      <c r="G41" t="s">
         <v>168</v>
-      </c>
-      <c r="G41" t="s">
-        <v>94</v>
       </c>
       <c r="H41" t="s">
         <v>59</v>
@@ -5075,11 +5075,11 @@
       <c r="D42" t="s">
         <v>14</v>
       </c>
-      <c r="F42" t="s">
+      <c r="E42" t="s">
+        <v>104</v>
+      </c>
+      <c r="G42" t="s">
         <v>168</v>
-      </c>
-      <c r="G42" t="s">
-        <v>104</v>
       </c>
       <c r="H42" t="s">
         <v>59</v>
@@ -5104,7 +5104,7 @@
       <c r="D43" t="s">
         <v>14</v>
       </c>
-      <c r="F43" t="s">
+      <c r="E43" t="s">
         <v>188</v>
       </c>
       <c r="G43" t="s">
@@ -5133,11 +5133,11 @@
       <c r="D44" t="s">
         <v>14</v>
       </c>
-      <c r="F44" t="s">
-        <v>188</v>
+      <c r="E44" t="s">
+        <v>196</v>
       </c>
       <c r="G44" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="H44" t="s">
         <v>197</v>
@@ -5162,7 +5162,7 @@
       <c r="D45" t="s">
         <v>14</v>
       </c>
-      <c r="F45" t="s">
+      <c r="E45" t="s">
         <v>188</v>
       </c>
       <c r="G45" t="s">
@@ -5191,7 +5191,7 @@
       <c r="D46" t="s">
         <v>14</v>
       </c>
-      <c r="F46" t="s">
+      <c r="E46" t="s">
         <v>188</v>
       </c>
       <c r="G46" t="s">
@@ -5220,11 +5220,11 @@
       <c r="D47" t="s">
         <v>14</v>
       </c>
-      <c r="F47" t="s">
-        <v>188</v>
+      <c r="E47" t="s">
+        <v>208</v>
       </c>
       <c r="G47" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="H47" t="s">
         <v>197</v>
@@ -5249,7 +5249,7 @@
       <c r="D48" t="s">
         <v>14</v>
       </c>
-      <c r="F48" t="s">
+      <c r="E48" t="s">
         <v>188</v>
       </c>
       <c r="G48" t="s">
@@ -5278,7 +5278,7 @@
       <c r="D49" t="s">
         <v>14</v>
       </c>
-      <c r="F49" t="s">
+      <c r="E49" t="s">
         <v>188</v>
       </c>
       <c r="G49" t="s">
@@ -5307,11 +5307,11 @@
       <c r="D50" t="s">
         <v>14</v>
       </c>
-      <c r="F50" t="s">
-        <v>188</v>
+      <c r="E50" t="s">
+        <v>208</v>
       </c>
       <c r="G50" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="H50" t="s">
         <v>197</v>
@@ -5336,7 +5336,7 @@
       <c r="D51" t="s">
         <v>14</v>
       </c>
-      <c r="F51" t="s">
+      <c r="E51" t="s">
         <v>188</v>
       </c>
       <c r="G51" t="s">
@@ -5365,11 +5365,11 @@
       <c r="D52" t="s">
         <v>14</v>
       </c>
-      <c r="F52" t="s">
-        <v>188</v>
+      <c r="E52" t="s">
+        <v>225</v>
       </c>
       <c r="G52" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="H52" t="s">
         <v>197</v>
@@ -5394,11 +5394,11 @@
       <c r="D53" t="s">
         <v>14</v>
       </c>
-      <c r="F53" t="s">
-        <v>188</v>
+      <c r="E53" t="s">
+        <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>17</v>
+        <v>189</v>
       </c>
       <c r="H53" t="s">
         <v>18</v>
@@ -5459,13 +5459,13 @@
         <v>14</v>
       </c>
       <c r="E55" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F55" t="s">
         <v>234</v>
       </c>
       <c r="G55" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="H55" t="s">
         <v>236</v>
@@ -5494,13 +5494,13 @@
         <v>14</v>
       </c>
       <c r="E56" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="F56" t="s">
         <v>234</v>
       </c>
       <c r="G56" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="H56" t="s">
         <v>236</v>
@@ -5529,13 +5529,13 @@
         <v>14</v>
       </c>
       <c r="E57" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="F57" t="s">
         <v>234</v>
       </c>
       <c r="G57" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="H57" t="s">
         <v>254</v>
@@ -5564,13 +5564,13 @@
         <v>14</v>
       </c>
       <c r="E58" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F58" t="s">
         <v>234</v>
       </c>
       <c r="G58" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="H58" t="s">
         <v>236</v>
@@ -5599,13 +5599,13 @@
         <v>14</v>
       </c>
       <c r="E59" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F59" t="s">
         <v>234</v>
       </c>
       <c r="G59" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="H59" t="s">
         <v>236</v>
@@ -5634,13 +5634,13 @@
         <v>14</v>
       </c>
       <c r="E60" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F60" t="s">
         <v>234</v>
       </c>
       <c r="G60" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="H60" t="s">
         <v>236</v>
@@ -5669,13 +5669,13 @@
         <v>14</v>
       </c>
       <c r="E61" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F61" t="s">
         <v>234</v>
       </c>
       <c r="G61" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="H61" t="s">
         <v>236</v>
@@ -5704,13 +5704,13 @@
         <v>14</v>
       </c>
       <c r="E62" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F62" t="s">
         <v>234</v>
       </c>
       <c r="G62" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="H62" t="s">
         <v>236</v>
@@ -5739,19 +5739,19 @@
         <v>14</v>
       </c>
       <c r="E63" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F63" t="s">
         <v>234</v>
       </c>
       <c r="G63" t="s">
-        <v>274</v>
+        <v>235</v>
       </c>
       <c r="H63" t="s">
         <v>236</v>
       </c>
       <c r="I63" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="J63" t="s">
         <v>238</v>
@@ -5774,19 +5774,19 @@
         <v>14</v>
       </c>
       <c r="E64" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F64" t="s">
         <v>234</v>
       </c>
       <c r="G64" t="s">
-        <v>274</v>
+        <v>235</v>
       </c>
       <c r="H64" t="s">
         <v>236</v>
       </c>
       <c r="I64" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="J64" t="s">
         <v>238</v>
@@ -5809,13 +5809,13 @@
         <v>14</v>
       </c>
       <c r="E65" t="s">
-        <v>233</v>
+        <v>281</v>
       </c>
       <c r="F65" t="s">
         <v>234</v>
       </c>
       <c r="G65" t="s">
-        <v>281</v>
+        <v>235</v>
       </c>
       <c r="H65" t="s">
         <v>236</v>
@@ -5879,13 +5879,13 @@
         <v>14</v>
       </c>
       <c r="E67" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F67" t="s">
         <v>234</v>
       </c>
       <c r="G67" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="H67" t="s">
         <v>236</v>
@@ -5920,13 +5920,13 @@
         <v>234</v>
       </c>
       <c r="G68" t="s">
-        <v>292</v>
+        <v>235</v>
       </c>
       <c r="H68" t="s">
         <v>236</v>
       </c>
       <c r="I68" t="s">
-        <v>237</v>
+        <v>292</v>
       </c>
       <c r="J68" t="s">
         <v>238</v>
@@ -5955,13 +5955,13 @@
         <v>234</v>
       </c>
       <c r="G69" t="s">
-        <v>296</v>
+        <v>235</v>
       </c>
       <c r="H69" t="s">
         <v>236</v>
       </c>
       <c r="I69" t="s">
-        <v>237</v>
+        <v>296</v>
       </c>
       <c r="J69" t="s">
         <v>238</v>
@@ -5984,13 +5984,13 @@
         <v>14</v>
       </c>
       <c r="E70" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="F70" t="s">
         <v>234</v>
       </c>
       <c r="G70" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="H70" t="s">
         <v>236</v>
@@ -6019,13 +6019,13 @@
         <v>14</v>
       </c>
       <c r="E71" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="F71" t="s">
         <v>234</v>
       </c>
       <c r="G71" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="H71" t="s">
         <v>236</v>
@@ -6089,13 +6089,13 @@
         <v>14</v>
       </c>
       <c r="E73" t="s">
-        <v>233</v>
+        <v>309</v>
       </c>
       <c r="F73" t="s">
         <v>234</v>
       </c>
       <c r="G73" t="s">
-        <v>309</v>
+        <v>235</v>
       </c>
       <c r="H73" t="s">
         <v>254</v>
@@ -6124,13 +6124,13 @@
         <v>14</v>
       </c>
       <c r="E74" t="s">
-        <v>233</v>
+        <v>314</v>
       </c>
       <c r="F74" t="s">
         <v>234</v>
       </c>
       <c r="G74" t="s">
-        <v>314</v>
+        <v>235</v>
       </c>
       <c r="H74" t="s">
         <v>254</v>
@@ -6159,13 +6159,13 @@
         <v>14</v>
       </c>
       <c r="E75" t="s">
-        <v>233</v>
+        <v>319</v>
       </c>
       <c r="F75" t="s">
         <v>234</v>
       </c>
       <c r="G75" t="s">
-        <v>319</v>
+        <v>235</v>
       </c>
       <c r="H75" t="s">
         <v>254</v>
@@ -6194,13 +6194,13 @@
         <v>14</v>
       </c>
       <c r="E76" t="s">
-        <v>233</v>
+        <v>309</v>
       </c>
       <c r="F76" t="s">
         <v>234</v>
       </c>
       <c r="G76" t="s">
-        <v>309</v>
+        <v>235</v>
       </c>
       <c r="H76" t="s">
         <v>254</v>
@@ -6229,13 +6229,13 @@
         <v>14</v>
       </c>
       <c r="E77" t="s">
-        <v>233</v>
+        <v>309</v>
       </c>
       <c r="F77" t="s">
         <v>234</v>
       </c>
       <c r="G77" t="s">
-        <v>309</v>
+        <v>235</v>
       </c>
       <c r="H77" t="s">
         <v>254</v>
@@ -6264,13 +6264,13 @@
         <v>14</v>
       </c>
       <c r="E78" t="s">
-        <v>233</v>
+        <v>314</v>
       </c>
       <c r="F78" t="s">
         <v>234</v>
       </c>
       <c r="G78" t="s">
-        <v>314</v>
+        <v>235</v>
       </c>
       <c r="H78" t="s">
         <v>254</v>
@@ -6296,13 +6296,13 @@
         <v>14</v>
       </c>
       <c r="E79" t="s">
-        <v>233</v>
+        <v>332</v>
       </c>
       <c r="F79" t="s">
         <v>234</v>
       </c>
       <c r="G79" t="s">
-        <v>332</v>
+        <v>235</v>
       </c>
       <c r="H79" t="s">
         <v>254</v>
@@ -6331,13 +6331,13 @@
         <v>14</v>
       </c>
       <c r="E80" t="s">
-        <v>233</v>
+        <v>337</v>
       </c>
       <c r="F80" t="s">
         <v>234</v>
       </c>
       <c r="G80" t="s">
-        <v>337</v>
+        <v>235</v>
       </c>
       <c r="H80" t="s">
         <v>338</v>
@@ -6366,13 +6366,13 @@
         <v>14</v>
       </c>
       <c r="E81" t="s">
-        <v>233</v>
+        <v>337</v>
       </c>
       <c r="F81" t="s">
         <v>234</v>
       </c>
       <c r="G81" t="s">
-        <v>337</v>
+        <v>235</v>
       </c>
       <c r="H81" t="s">
         <v>338</v>
@@ -6401,13 +6401,13 @@
         <v>14</v>
       </c>
       <c r="E82" t="s">
-        <v>233</v>
+        <v>337</v>
       </c>
       <c r="F82" t="s">
         <v>234</v>
       </c>
       <c r="G82" t="s">
-        <v>337</v>
+        <v>235</v>
       </c>
       <c r="H82" t="s">
         <v>338</v>
@@ -6442,13 +6442,13 @@
         <v>234</v>
       </c>
       <c r="G83" t="s">
-        <v>296</v>
+        <v>235</v>
       </c>
       <c r="H83" t="s">
         <v>236</v>
       </c>
       <c r="I83" t="s">
-        <v>237</v>
+        <v>296</v>
       </c>
       <c r="J83" t="s">
         <v>238</v>
@@ -6471,13 +6471,13 @@
         <v>14</v>
       </c>
       <c r="E84" t="s">
-        <v>233</v>
+        <v>352</v>
       </c>
       <c r="F84" t="s">
         <v>234</v>
       </c>
       <c r="G84" t="s">
-        <v>352</v>
+        <v>235</v>
       </c>
       <c r="H84" t="s">
         <v>236</v>
@@ -6506,19 +6506,19 @@
         <v>14</v>
       </c>
       <c r="E85" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F85" t="s">
         <v>234</v>
       </c>
       <c r="G85" t="s">
-        <v>357</v>
+        <v>235</v>
       </c>
       <c r="H85" t="s">
         <v>236</v>
       </c>
       <c r="I85" t="s">
-        <v>244</v>
+        <v>357</v>
       </c>
       <c r="J85" t="s">
         <v>238</v>
@@ -6541,13 +6541,13 @@
         <v>14</v>
       </c>
       <c r="E86" t="s">
-        <v>233</v>
+        <v>361</v>
       </c>
       <c r="F86" t="s">
         <v>234</v>
       </c>
       <c r="G86" t="s">
-        <v>361</v>
+        <v>235</v>
       </c>
       <c r="H86" t="s">
         <v>338</v>
@@ -6576,19 +6576,19 @@
         <v>14</v>
       </c>
       <c r="E87" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F87" t="s">
         <v>234</v>
       </c>
       <c r="G87" t="s">
-        <v>357</v>
+        <v>235</v>
       </c>
       <c r="H87" t="s">
         <v>236</v>
       </c>
       <c r="I87" t="s">
-        <v>244</v>
+        <v>357</v>
       </c>
       <c r="J87" t="s">
         <v>238</v>
@@ -6608,13 +6608,13 @@
         <v>14</v>
       </c>
       <c r="E88" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F88" t="s">
         <v>234</v>
       </c>
       <c r="G88" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="H88" t="s">
         <v>236</v>
@@ -6643,13 +6643,13 @@
         <v>14</v>
       </c>
       <c r="E89" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F89" t="s">
         <v>234</v>
       </c>
       <c r="G89" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="H89" t="s">
         <v>236</v>
@@ -6678,13 +6678,13 @@
         <v>14</v>
       </c>
       <c r="E90" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="F90" t="s">
         <v>234</v>
       </c>
       <c r="G90" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="H90" t="s">
         <v>254</v>
@@ -6713,13 +6713,13 @@
         <v>14</v>
       </c>
       <c r="E91" t="s">
-        <v>233</v>
+        <v>377</v>
       </c>
       <c r="F91" t="s">
         <v>234</v>
       </c>
       <c r="G91" t="s">
-        <v>377</v>
+        <v>235</v>
       </c>
       <c r="H91" t="s">
         <v>378</v>
@@ -6748,13 +6748,13 @@
         <v>14</v>
       </c>
       <c r="E92" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="F92" t="s">
         <v>234</v>
       </c>
       <c r="G92" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="H92" t="s">
         <v>254</v>
@@ -6783,13 +6783,13 @@
         <v>14</v>
       </c>
       <c r="E93" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="F93" t="s">
         <v>234</v>
       </c>
       <c r="G93" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="H93" t="s">
         <v>236</v>
@@ -6818,13 +6818,13 @@
         <v>14</v>
       </c>
       <c r="E94" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="F94" t="s">
         <v>234</v>
       </c>
       <c r="G94" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="H94" t="s">
         <v>254</v>
@@ -6853,13 +6853,13 @@
         <v>14</v>
       </c>
       <c r="E95" t="s">
-        <v>233</v>
+        <v>392</v>
       </c>
       <c r="F95" t="s">
         <v>234</v>
       </c>
       <c r="G95" t="s">
-        <v>392</v>
+        <v>235</v>
       </c>
       <c r="H95" t="s">
         <v>236</v>
@@ -6888,13 +6888,13 @@
         <v>14</v>
       </c>
       <c r="E96" t="s">
+        <v>253</v>
+      </c>
+      <c r="F96" t="s">
         <v>397</v>
       </c>
-      <c r="F96" t="s">
-        <v>234</v>
-      </c>
       <c r="G96" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="H96" t="s">
         <v>254</v>
@@ -6923,13 +6923,13 @@
         <v>14</v>
       </c>
       <c r="E97" t="s">
+        <v>253</v>
+      </c>
+      <c r="F97" t="s">
         <v>397</v>
       </c>
-      <c r="F97" t="s">
-        <v>234</v>
-      </c>
       <c r="G97" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="H97" t="s">
         <v>254</v>
@@ -6958,13 +6958,13 @@
         <v>14</v>
       </c>
       <c r="E98" t="s">
+        <v>405</v>
+      </c>
+      <c r="F98" t="s">
         <v>397</v>
       </c>
-      <c r="F98" t="s">
-        <v>234</v>
-      </c>
       <c r="G98" t="s">
-        <v>405</v>
+        <v>235</v>
       </c>
       <c r="H98" t="s">
         <v>406</v>
@@ -6993,13 +6993,13 @@
         <v>14</v>
       </c>
       <c r="E99" t="s">
+        <v>253</v>
+      </c>
+      <c r="F99" t="s">
         <v>397</v>
       </c>
-      <c r="F99" t="s">
-        <v>234</v>
-      </c>
       <c r="G99" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="H99" t="s">
         <v>254</v>
@@ -7028,13 +7028,13 @@
         <v>14</v>
       </c>
       <c r="E100" t="s">
+        <v>319</v>
+      </c>
+      <c r="F100" t="s">
         <v>397</v>
       </c>
-      <c r="F100" t="s">
-        <v>234</v>
-      </c>
       <c r="G100" t="s">
-        <v>319</v>
+        <v>235</v>
       </c>
       <c r="H100" t="s">
         <v>254</v>
@@ -7063,13 +7063,13 @@
         <v>14</v>
       </c>
       <c r="E101" t="s">
+        <v>253</v>
+      </c>
+      <c r="F101" t="s">
         <v>397</v>
       </c>
-      <c r="F101" t="s">
-        <v>234</v>
-      </c>
       <c r="G101" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="H101" t="s">
         <v>254</v>
@@ -7097,7 +7097,7 @@
       <c r="D102" t="s">
         <v>14</v>
       </c>
-      <c r="F102" t="s">
+      <c r="E102" t="s">
         <v>420</v>
       </c>
       <c r="G102" t="s">
@@ -7126,7 +7126,7 @@
       <c r="D103" t="s">
         <v>14</v>
       </c>
-      <c r="F103" t="s">
+      <c r="E103" t="s">
         <v>420</v>
       </c>
       <c r="G103" t="s">
@@ -7155,7 +7155,7 @@
       <c r="D104" t="s">
         <v>14</v>
       </c>
-      <c r="F104" t="s">
+      <c r="E104" t="s">
         <v>420</v>
       </c>
       <c r="G104" t="s">
@@ -7184,11 +7184,11 @@
       <c r="D105" t="s">
         <v>14</v>
       </c>
-      <c r="F105" t="s">
-        <v>420</v>
+      <c r="E105" t="s">
+        <v>433</v>
       </c>
       <c r="G105" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="H105" t="s">
         <v>378</v>
@@ -7213,7 +7213,7 @@
       <c r="D106" t="s">
         <v>14</v>
       </c>
-      <c r="F106" t="s">
+      <c r="E106" t="s">
         <v>420</v>
       </c>
       <c r="G106" t="s">
@@ -7242,11 +7242,11 @@
       <c r="D107" t="s">
         <v>14</v>
       </c>
-      <c r="F107" t="s">
-        <v>420</v>
+      <c r="E107" t="s">
+        <v>377</v>
       </c>
       <c r="G107" t="s">
-        <v>377</v>
+        <v>421</v>
       </c>
       <c r="H107" t="s">
         <v>378</v>
@@ -7271,11 +7271,11 @@
       <c r="D108" t="s">
         <v>14</v>
       </c>
-      <c r="F108" t="s">
-        <v>420</v>
+      <c r="E108" t="s">
+        <v>444</v>
       </c>
       <c r="G108" t="s">
-        <v>444</v>
+        <v>421</v>
       </c>
       <c r="H108" t="s">
         <v>378</v>
@@ -7300,11 +7300,11 @@
       <c r="D109" t="s">
         <v>14</v>
       </c>
-      <c r="F109" t="s">
-        <v>420</v>
+      <c r="E109" t="s">
+        <v>449</v>
       </c>
       <c r="G109" t="s">
-        <v>449</v>
+        <v>421</v>
       </c>
       <c r="H109" t="s">
         <v>190</v>
@@ -7329,11 +7329,11 @@
       <c r="D110" t="s">
         <v>14</v>
       </c>
-      <c r="F110" t="s">
-        <v>420</v>
+      <c r="E110" t="s">
+        <v>454</v>
       </c>
       <c r="G110" t="s">
-        <v>454</v>
+        <v>421</v>
       </c>
       <c r="H110" t="s">
         <v>190</v>
@@ -7358,7 +7358,7 @@
       <c r="D111" t="s">
         <v>14</v>
       </c>
-      <c r="F111" t="s">
+      <c r="E111" t="s">
         <v>420</v>
       </c>
       <c r="G111" t="s">
@@ -7387,11 +7387,11 @@
       <c r="D112" t="s">
         <v>14</v>
       </c>
-      <c r="F112" t="s">
-        <v>420</v>
+      <c r="E112" t="s">
+        <v>462</v>
       </c>
       <c r="G112" t="s">
-        <v>462</v>
+        <v>421</v>
       </c>
       <c r="H112" t="s">
         <v>463</v>
@@ -7416,17 +7416,17 @@
       <c r="D113" t="s">
         <v>14</v>
       </c>
-      <c r="F113" t="s">
-        <v>420</v>
+      <c r="E113" t="s">
+        <v>233</v>
       </c>
       <c r="G113" t="s">
-        <v>296</v>
+        <v>421</v>
       </c>
       <c r="H113" t="s">
         <v>236</v>
       </c>
       <c r="I113" t="s">
-        <v>237</v>
+        <v>296</v>
       </c>
       <c r="K113" t="s">
         <v>423</v>
@@ -7445,11 +7445,11 @@
       <c r="D114" t="s">
         <v>14</v>
       </c>
-      <c r="F114" t="s">
-        <v>420</v>
+      <c r="E114" t="s">
+        <v>314</v>
       </c>
       <c r="G114" t="s">
-        <v>314</v>
+        <v>421</v>
       </c>
       <c r="H114" t="s">
         <v>254</v>
@@ -7474,11 +7474,11 @@
       <c r="D115" t="s">
         <v>14</v>
       </c>
-      <c r="F115" t="s">
-        <v>420</v>
+      <c r="E115" t="s">
+        <v>377</v>
       </c>
       <c r="G115" t="s">
-        <v>377</v>
+        <v>421</v>
       </c>
       <c r="H115" t="s">
         <v>378</v>
@@ -7500,11 +7500,11 @@
       <c r="D116" t="s">
         <v>14</v>
       </c>
-      <c r="F116" t="s">
-        <v>420</v>
+      <c r="E116" t="s">
+        <v>476</v>
       </c>
       <c r="G116" t="s">
-        <v>476</v>
+        <v>421</v>
       </c>
       <c r="H116" t="s">
         <v>463</v>
@@ -7526,11 +7526,11 @@
       <c r="D117" t="s">
         <v>14</v>
       </c>
-      <c r="F117" t="s">
-        <v>420</v>
+      <c r="E117" t="s">
+        <v>462</v>
       </c>
       <c r="G117" t="s">
-        <v>462</v>
+        <v>421</v>
       </c>
       <c r="H117" t="s">
         <v>463</v>
@@ -7555,17 +7555,17 @@
       <c r="D118" t="s">
         <v>14</v>
       </c>
-      <c r="F118" t="s">
-        <v>420</v>
+      <c r="E118" t="s">
+        <v>337</v>
       </c>
       <c r="G118" t="s">
-        <v>483</v>
+        <v>421</v>
       </c>
       <c r="H118" t="s">
         <v>338</v>
       </c>
       <c r="I118" t="s">
-        <v>339</v>
+        <v>483</v>
       </c>
       <c r="K118" t="s">
         <v>423</v>
@@ -7584,11 +7584,11 @@
       <c r="D119" t="s">
         <v>14</v>
       </c>
-      <c r="F119" t="s">
-        <v>420</v>
+      <c r="E119" t="s">
+        <v>377</v>
       </c>
       <c r="G119" t="s">
-        <v>377</v>
+        <v>421</v>
       </c>
       <c r="H119" t="s">
         <v>378</v>
@@ -7613,11 +7613,11 @@
       <c r="D120" t="s">
         <v>14</v>
       </c>
-      <c r="F120" t="s">
+      <c r="E120" t="s">
+        <v>352</v>
+      </c>
+      <c r="G120" t="s">
         <v>490</v>
-      </c>
-      <c r="G120" t="s">
-        <v>352</v>
       </c>
       <c r="H120" t="s">
         <v>236</v>
@@ -7642,17 +7642,17 @@
       <c r="D121" t="s">
         <v>14</v>
       </c>
-      <c r="F121" t="s">
+      <c r="E121" t="s">
+        <v>233</v>
+      </c>
+      <c r="G121" t="s">
         <v>490</v>
-      </c>
-      <c r="G121" t="s">
-        <v>296</v>
       </c>
       <c r="H121" t="s">
         <v>236</v>
       </c>
       <c r="I121" t="s">
-        <v>237</v>
+        <v>296</v>
       </c>
       <c r="K121" t="s">
         <v>491</v>
@@ -7671,11 +7671,11 @@
       <c r="D122" t="s">
         <v>14</v>
       </c>
-      <c r="F122" t="s">
+      <c r="E122" t="s">
+        <v>352</v>
+      </c>
+      <c r="G122" t="s">
         <v>490</v>
-      </c>
-      <c r="G122" t="s">
-        <v>352</v>
       </c>
       <c r="H122" t="s">
         <v>236</v>
@@ -7700,11 +7700,11 @@
       <c r="D123" t="s">
         <v>14</v>
       </c>
-      <c r="F123" t="s">
+      <c r="E123" t="s">
+        <v>352</v>
+      </c>
+      <c r="G123" t="s">
         <v>490</v>
-      </c>
-      <c r="G123" t="s">
-        <v>352</v>
       </c>
       <c r="H123" t="s">
         <v>236</v>
@@ -7729,11 +7729,11 @@
       <c r="D124" t="s">
         <v>14</v>
       </c>
-      <c r="F124" t="s">
+      <c r="E124" t="s">
+        <v>504</v>
+      </c>
+      <c r="G124" t="s">
         <v>490</v>
-      </c>
-      <c r="G124" t="s">
-        <v>504</v>
       </c>
       <c r="H124" t="s">
         <v>338</v>
@@ -7758,11 +7758,11 @@
       <c r="D125" t="s">
         <v>14</v>
       </c>
-      <c r="F125" t="s">
+      <c r="E125" t="s">
+        <v>504</v>
+      </c>
+      <c r="G125" t="s">
         <v>490</v>
-      </c>
-      <c r="G125" t="s">
-        <v>504</v>
       </c>
       <c r="H125" t="s">
         <v>338</v>
@@ -7787,11 +7787,11 @@
       <c r="D126" t="s">
         <v>14</v>
       </c>
-      <c r="F126" t="s">
+      <c r="E126" t="s">
+        <v>504</v>
+      </c>
+      <c r="G126" t="s">
         <v>490</v>
-      </c>
-      <c r="G126" t="s">
-        <v>504</v>
       </c>
       <c r="H126" t="s">
         <v>338</v>
@@ -7816,11 +7816,11 @@
       <c r="D127" t="s">
         <v>14</v>
       </c>
-      <c r="F127" t="s">
+      <c r="E127" t="s">
+        <v>504</v>
+      </c>
+      <c r="G127" t="s">
         <v>490</v>
-      </c>
-      <c r="G127" t="s">
-        <v>504</v>
       </c>
       <c r="H127" t="s">
         <v>338</v>
@@ -7845,11 +7845,11 @@
       <c r="D128" t="s">
         <v>14</v>
       </c>
-      <c r="F128" t="s">
+      <c r="E128" t="s">
+        <v>504</v>
+      </c>
+      <c r="G128" t="s">
         <v>490</v>
-      </c>
-      <c r="G128" t="s">
-        <v>504</v>
       </c>
       <c r="H128" t="s">
         <v>338</v>
@@ -7874,17 +7874,17 @@
       <c r="D129" t="s">
         <v>14</v>
       </c>
-      <c r="F129" t="s">
+      <c r="E129" t="s">
+        <v>504</v>
+      </c>
+      <c r="G129" t="s">
         <v>490</v>
-      </c>
-      <c r="G129" t="s">
-        <v>521</v>
       </c>
       <c r="H129" t="s">
         <v>338</v>
       </c>
       <c r="I129" t="s">
-        <v>505</v>
+        <v>521</v>
       </c>
       <c r="K129" t="s">
         <v>491</v>
@@ -7903,17 +7903,17 @@
       <c r="D130" t="s">
         <v>14</v>
       </c>
-      <c r="F130" t="s">
+      <c r="E130" t="s">
+        <v>504</v>
+      </c>
+      <c r="G130" t="s">
         <v>490</v>
-      </c>
-      <c r="G130" t="s">
-        <v>525</v>
       </c>
       <c r="H130" t="s">
         <v>338</v>
       </c>
       <c r="I130" t="s">
-        <v>505</v>
+        <v>525</v>
       </c>
       <c r="K130" t="s">
         <v>491</v>
@@ -7932,17 +7932,17 @@
       <c r="D131" t="s">
         <v>14</v>
       </c>
-      <c r="F131" t="s">
+      <c r="E131" t="s">
+        <v>504</v>
+      </c>
+      <c r="G131" t="s">
         <v>490</v>
-      </c>
-      <c r="G131" t="s">
-        <v>529</v>
       </c>
       <c r="H131" t="s">
         <v>338</v>
       </c>
       <c r="I131" t="s">
-        <v>505</v>
+        <v>529</v>
       </c>
       <c r="K131" t="s">
         <v>491</v>
@@ -7961,11 +7961,11 @@
       <c r="D132" t="s">
         <v>14</v>
       </c>
-      <c r="F132" t="s">
+      <c r="E132" t="s">
+        <v>533</v>
+      </c>
+      <c r="G132" t="s">
         <v>490</v>
-      </c>
-      <c r="G132" t="s">
-        <v>533</v>
       </c>
       <c r="H132" t="s">
         <v>338</v>
@@ -7987,11 +7987,11 @@
       <c r="D133" t="s">
         <v>14</v>
       </c>
-      <c r="F133" t="s">
+      <c r="E133" t="s">
+        <v>392</v>
+      </c>
+      <c r="G133" t="s">
         <v>490</v>
-      </c>
-      <c r="G133" t="s">
-        <v>392</v>
       </c>
       <c r="H133" t="s">
         <v>236</v>
@@ -8016,11 +8016,11 @@
       <c r="D134" t="s">
         <v>14</v>
       </c>
-      <c r="F134" t="s">
+      <c r="E134" t="s">
+        <v>361</v>
+      </c>
+      <c r="G134" t="s">
         <v>540</v>
-      </c>
-      <c r="G134" t="s">
-        <v>361</v>
       </c>
       <c r="H134" t="s">
         <v>338</v>
@@ -8042,11 +8042,11 @@
       <c r="D135" t="s">
         <v>14</v>
       </c>
-      <c r="F135" t="s">
+      <c r="E135" t="s">
+        <v>361</v>
+      </c>
+      <c r="G135" t="s">
         <v>540</v>
-      </c>
-      <c r="G135" t="s">
-        <v>361</v>
       </c>
       <c r="H135" t="s">
         <v>338</v>
@@ -8071,11 +8071,11 @@
       <c r="D136" t="s">
         <v>14</v>
       </c>
-      <c r="F136" t="s">
+      <c r="E136" t="s">
+        <v>361</v>
+      </c>
+      <c r="G136" t="s">
         <v>540</v>
-      </c>
-      <c r="G136" t="s">
-        <v>361</v>
       </c>
       <c r="H136" t="s">
         <v>338</v>
@@ -8100,11 +8100,11 @@
       <c r="D137" t="s">
         <v>14</v>
       </c>
-      <c r="F137" t="s">
+      <c r="E137" t="s">
+        <v>361</v>
+      </c>
+      <c r="G137" t="s">
         <v>540</v>
-      </c>
-      <c r="G137" t="s">
-        <v>361</v>
       </c>
       <c r="H137" t="s">
         <v>338</v>
@@ -8129,11 +8129,11 @@
       <c r="D138" t="s">
         <v>14</v>
       </c>
-      <c r="F138" t="s">
+      <c r="E138" t="s">
+        <v>361</v>
+      </c>
+      <c r="G138" t="s">
         <v>540</v>
-      </c>
-      <c r="G138" t="s">
-        <v>361</v>
       </c>
       <c r="H138" t="s">
         <v>338</v>
@@ -8158,11 +8158,11 @@
       <c r="D139" t="s">
         <v>14</v>
       </c>
-      <c r="F139" t="s">
+      <c r="E139" t="s">
+        <v>556</v>
+      </c>
+      <c r="G139" t="s">
         <v>540</v>
-      </c>
-      <c r="G139" t="s">
-        <v>556</v>
       </c>
       <c r="H139" t="s">
         <v>463</v>
@@ -8187,11 +8187,11 @@
       <c r="D140" t="s">
         <v>14</v>
       </c>
-      <c r="F140" t="s">
+      <c r="E140" t="s">
+        <v>361</v>
+      </c>
+      <c r="G140" t="s">
         <v>540</v>
-      </c>
-      <c r="G140" t="s">
-        <v>361</v>
       </c>
       <c r="H140" t="s">
         <v>338</v>
@@ -8284,13 +8284,13 @@
         <v>14</v>
       </c>
       <c r="E143" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="F143" t="s">
         <v>565</v>
       </c>
       <c r="G143" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="H143" t="s">
         <v>338</v>
@@ -8319,13 +8319,13 @@
         <v>14</v>
       </c>
       <c r="E144" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="F144" t="s">
         <v>565</v>
       </c>
       <c r="G144" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="H144" t="s">
         <v>338</v>
@@ -8354,13 +8354,13 @@
         <v>14</v>
       </c>
       <c r="E145" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="F145" t="s">
         <v>565</v>
       </c>
       <c r="G145" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="H145" t="s">
         <v>338</v>
@@ -8424,10 +8424,10 @@
         <v>14</v>
       </c>
       <c r="E147" t="s">
+        <v>564</v>
+      </c>
+      <c r="F147" t="s">
         <v>589</v>
-      </c>
-      <c r="F147" t="s">
-        <v>565</v>
       </c>
       <c r="G147" t="s">
         <v>566</v>
@@ -8459,10 +8459,10 @@
         <v>14</v>
       </c>
       <c r="E148" t="s">
+        <v>564</v>
+      </c>
+      <c r="F148" t="s">
         <v>589</v>
-      </c>
-      <c r="F148" t="s">
-        <v>565</v>
       </c>
       <c r="G148" t="s">
         <v>566</v>
@@ -8494,10 +8494,10 @@
         <v>14</v>
       </c>
       <c r="E149" t="s">
+        <v>564</v>
+      </c>
+      <c r="F149" t="s">
         <v>589</v>
-      </c>
-      <c r="F149" t="s">
-        <v>565</v>
       </c>
       <c r="G149" t="s">
         <v>566</v>
@@ -8529,10 +8529,10 @@
         <v>14</v>
       </c>
       <c r="E150" t="s">
+        <v>564</v>
+      </c>
+      <c r="F150" t="s">
         <v>589</v>
-      </c>
-      <c r="F150" t="s">
-        <v>565</v>
       </c>
       <c r="G150" t="s">
         <v>566</v>
@@ -8564,10 +8564,10 @@
         <v>14</v>
       </c>
       <c r="E151" t="s">
+        <v>564</v>
+      </c>
+      <c r="F151" t="s">
         <v>589</v>
-      </c>
-      <c r="F151" t="s">
-        <v>565</v>
       </c>
       <c r="G151" t="s">
         <v>566</v>
@@ -8599,10 +8599,10 @@
         <v>14</v>
       </c>
       <c r="E152" t="s">
+        <v>564</v>
+      </c>
+      <c r="F152" t="s">
         <v>589</v>
-      </c>
-      <c r="F152" t="s">
-        <v>565</v>
       </c>
       <c r="G152" t="s">
         <v>566</v>
@@ -8634,10 +8634,10 @@
         <v>14</v>
       </c>
       <c r="E153" t="s">
+        <v>564</v>
+      </c>
+      <c r="F153" t="s">
         <v>589</v>
-      </c>
-      <c r="F153" t="s">
-        <v>565</v>
       </c>
       <c r="G153" t="s">
         <v>566</v>
@@ -8669,10 +8669,10 @@
         <v>14</v>
       </c>
       <c r="E154" t="s">
+        <v>564</v>
+      </c>
+      <c r="F154" t="s">
         <v>589</v>
-      </c>
-      <c r="F154" t="s">
-        <v>565</v>
       </c>
       <c r="G154" t="s">
         <v>566</v>
@@ -8704,10 +8704,10 @@
         <v>14</v>
       </c>
       <c r="E155" t="s">
+        <v>564</v>
+      </c>
+      <c r="F155" t="s">
         <v>589</v>
-      </c>
-      <c r="F155" t="s">
-        <v>565</v>
       </c>
       <c r="G155" t="s">
         <v>566</v>
@@ -8739,10 +8739,10 @@
         <v>14</v>
       </c>
       <c r="E156" t="s">
+        <v>564</v>
+      </c>
+      <c r="F156" t="s">
         <v>618</v>
-      </c>
-      <c r="F156" t="s">
-        <v>565</v>
       </c>
       <c r="G156" t="s">
         <v>566</v>
@@ -8774,19 +8774,19 @@
         <v>14</v>
       </c>
       <c r="E157" t="s">
+        <v>564</v>
+      </c>
+      <c r="F157" t="s">
         <v>618</v>
       </c>
-      <c r="F157" t="s">
-        <v>565</v>
-      </c>
       <c r="G157" t="s">
-        <v>623</v>
+        <v>566</v>
       </c>
       <c r="H157" t="s">
         <v>338</v>
       </c>
       <c r="I157" t="s">
-        <v>567</v>
+        <v>623</v>
       </c>
       <c r="J157" t="s">
         <v>619</v>
@@ -8809,10 +8809,10 @@
         <v>14</v>
       </c>
       <c r="E158" t="s">
+        <v>564</v>
+      </c>
+      <c r="F158" t="s">
         <v>618</v>
-      </c>
-      <c r="F158" t="s">
-        <v>565</v>
       </c>
       <c r="G158" t="s">
         <v>566</v>
@@ -8844,10 +8844,10 @@
         <v>14</v>
       </c>
       <c r="E159" t="s">
+        <v>564</v>
+      </c>
+      <c r="F159" t="s">
         <v>618</v>
-      </c>
-      <c r="F159" t="s">
-        <v>565</v>
       </c>
       <c r="G159" t="s">
         <v>566</v>
@@ -8879,10 +8879,10 @@
         <v>14</v>
       </c>
       <c r="E160" t="s">
+        <v>564</v>
+      </c>
+      <c r="F160" t="s">
         <v>618</v>
-      </c>
-      <c r="F160" t="s">
-        <v>565</v>
       </c>
       <c r="G160" t="s">
         <v>566</v>
@@ -8914,10 +8914,10 @@
         <v>14</v>
       </c>
       <c r="E161" t="s">
+        <v>564</v>
+      </c>
+      <c r="F161" t="s">
         <v>618</v>
-      </c>
-      <c r="F161" t="s">
-        <v>565</v>
       </c>
       <c r="G161" t="s">
         <v>566</v>
@@ -8949,10 +8949,10 @@
         <v>14</v>
       </c>
       <c r="E162" t="s">
+        <v>564</v>
+      </c>
+      <c r="F162" t="s">
         <v>639</v>
-      </c>
-      <c r="F162" t="s">
-        <v>565</v>
       </c>
       <c r="G162" t="s">
         <v>566</v>
@@ -8984,19 +8984,19 @@
         <v>14</v>
       </c>
       <c r="E163" t="s">
+        <v>564</v>
+      </c>
+      <c r="F163" t="s">
         <v>644</v>
       </c>
-      <c r="F163" t="s">
-        <v>565</v>
-      </c>
       <c r="G163" t="s">
-        <v>645</v>
+        <v>566</v>
       </c>
       <c r="H163" t="s">
         <v>338</v>
       </c>
       <c r="I163" t="s">
-        <v>567</v>
+        <v>645</v>
       </c>
       <c r="J163" t="s">
         <v>642</v>
@@ -9019,10 +9019,10 @@
         <v>14</v>
       </c>
       <c r="E164" t="s">
+        <v>564</v>
+      </c>
+      <c r="F164" t="s">
         <v>649</v>
-      </c>
-      <c r="F164" t="s">
-        <v>565</v>
       </c>
       <c r="G164" t="s">
         <v>566</v>
@@ -9054,10 +9054,10 @@
         <v>14</v>
       </c>
       <c r="E165" t="s">
+        <v>564</v>
+      </c>
+      <c r="F165" t="s">
         <v>649</v>
-      </c>
-      <c r="F165" t="s">
-        <v>565</v>
       </c>
       <c r="G165" t="s">
         <v>566</v>
@@ -9089,10 +9089,10 @@
         <v>14</v>
       </c>
       <c r="E166" t="s">
+        <v>564</v>
+      </c>
+      <c r="F166" t="s">
         <v>649</v>
-      </c>
-      <c r="F166" t="s">
-        <v>565</v>
       </c>
       <c r="G166" t="s">
         <v>566</v>
@@ -9124,10 +9124,10 @@
         <v>14</v>
       </c>
       <c r="E167" t="s">
+        <v>564</v>
+      </c>
+      <c r="F167" t="s">
         <v>649</v>
-      </c>
-      <c r="F167" t="s">
-        <v>565</v>
       </c>
       <c r="G167" t="s">
         <v>566</v>
@@ -9159,19 +9159,19 @@
         <v>14</v>
       </c>
       <c r="E168" t="s">
+        <v>564</v>
+      </c>
+      <c r="F168" t="s">
         <v>649</v>
       </c>
-      <c r="F168" t="s">
-        <v>565</v>
-      </c>
       <c r="G168" t="s">
-        <v>663</v>
+        <v>566</v>
       </c>
       <c r="H168" t="s">
         <v>338</v>
       </c>
       <c r="I168" t="s">
-        <v>567</v>
+        <v>663</v>
       </c>
       <c r="J168" t="s">
         <v>650</v>
@@ -9191,19 +9191,19 @@
         <v>14</v>
       </c>
       <c r="E169" t="s">
+        <v>564</v>
+      </c>
+      <c r="F169" t="s">
         <v>649</v>
       </c>
-      <c r="F169" t="s">
-        <v>565</v>
-      </c>
       <c r="G169" t="s">
-        <v>663</v>
+        <v>566</v>
       </c>
       <c r="H169" t="s">
         <v>338</v>
       </c>
       <c r="I169" t="s">
-        <v>567</v>
+        <v>663</v>
       </c>
       <c r="J169" t="s">
         <v>650</v>
@@ -9226,10 +9226,10 @@
         <v>14</v>
       </c>
       <c r="E170" t="s">
+        <v>564</v>
+      </c>
+      <c r="F170" t="s">
         <v>649</v>
-      </c>
-      <c r="F170" t="s">
-        <v>565</v>
       </c>
       <c r="G170" t="s">
         <v>566</v>
@@ -9260,11 +9260,11 @@
       <c r="D171" t="s">
         <v>14</v>
       </c>
-      <c r="F171" t="s">
+      <c r="E171" t="s">
+        <v>337</v>
+      </c>
+      <c r="G171" t="s">
         <v>672</v>
-      </c>
-      <c r="G171" t="s">
-        <v>337</v>
       </c>
       <c r="H171" t="s">
         <v>338</v>
@@ -9289,11 +9289,11 @@
       <c r="D172" t="s">
         <v>14</v>
       </c>
-      <c r="F172" t="s">
+      <c r="E172" t="s">
+        <v>243</v>
+      </c>
+      <c r="G172" t="s">
         <v>672</v>
-      </c>
-      <c r="G172" t="s">
-        <v>243</v>
       </c>
       <c r="H172" t="s">
         <v>236</v>
@@ -9318,11 +9318,11 @@
       <c r="D173" t="s">
         <v>14</v>
       </c>
-      <c r="F173" t="s">
+      <c r="E173" t="s">
+        <v>337</v>
+      </c>
+      <c r="G173" t="s">
         <v>672</v>
-      </c>
-      <c r="G173" t="s">
-        <v>337</v>
       </c>
       <c r="H173" t="s">
         <v>338</v>
@@ -9347,11 +9347,11 @@
       <c r="D174" t="s">
         <v>14</v>
       </c>
-      <c r="F174" t="s">
+      <c r="E174" t="s">
+        <v>337</v>
+      </c>
+      <c r="G174" t="s">
         <v>672</v>
-      </c>
-      <c r="G174" t="s">
-        <v>337</v>
       </c>
       <c r="H174" t="s">
         <v>338</v>
@@ -9376,11 +9376,11 @@
       <c r="D175" t="s">
         <v>14</v>
       </c>
-      <c r="F175" t="s">
+      <c r="E175" t="s">
+        <v>337</v>
+      </c>
+      <c r="G175" t="s">
         <v>672</v>
-      </c>
-      <c r="G175" t="s">
-        <v>337</v>
       </c>
       <c r="H175" t="s">
         <v>338</v>
@@ -9402,11 +9402,11 @@
       <c r="D176" t="s">
         <v>14</v>
       </c>
-      <c r="F176" t="s">
+      <c r="E176" t="s">
+        <v>337</v>
+      </c>
+      <c r="G176" t="s">
         <v>672</v>
-      </c>
-      <c r="G176" t="s">
-        <v>337</v>
       </c>
       <c r="H176" t="s">
         <v>338</v>
@@ -9431,11 +9431,11 @@
       <c r="D177" t="s">
         <v>14</v>
       </c>
-      <c r="F177" t="s">
+      <c r="E177" t="s">
+        <v>337</v>
+      </c>
+      <c r="G177" t="s">
         <v>691</v>
-      </c>
-      <c r="G177" t="s">
-        <v>337</v>
       </c>
       <c r="H177" t="s">
         <v>338</v>
@@ -9460,11 +9460,11 @@
       <c r="D178" t="s">
         <v>14</v>
       </c>
-      <c r="F178" t="s">
+      <c r="E178" t="s">
+        <v>337</v>
+      </c>
+      <c r="G178" t="s">
         <v>691</v>
-      </c>
-      <c r="G178" t="s">
-        <v>337</v>
       </c>
       <c r="H178" t="s">
         <v>338</v>
@@ -9489,11 +9489,11 @@
       <c r="D179" t="s">
         <v>14</v>
       </c>
-      <c r="F179" t="s">
+      <c r="E179" t="s">
+        <v>337</v>
+      </c>
+      <c r="G179" t="s">
         <v>691</v>
-      </c>
-      <c r="G179" t="s">
-        <v>337</v>
       </c>
       <c r="H179" t="s">
         <v>338</v>
@@ -9518,11 +9518,11 @@
       <c r="D180" t="s">
         <v>14</v>
       </c>
-      <c r="F180" t="s">
+      <c r="E180" t="s">
+        <v>337</v>
+      </c>
+      <c r="G180" t="s">
         <v>691</v>
-      </c>
-      <c r="G180" t="s">
-        <v>337</v>
       </c>
       <c r="H180" t="s">
         <v>338</v>
@@ -9965,19 +9965,19 @@
         <v>14</v>
       </c>
       <c r="E193" t="s">
-        <v>705</v>
+        <v>575</v>
       </c>
       <c r="F193" t="s">
         <v>706</v>
       </c>
       <c r="G193" t="s">
-        <v>746</v>
+        <v>707</v>
       </c>
       <c r="H193" t="s">
         <v>338</v>
       </c>
       <c r="I193" t="s">
-        <v>576</v>
+        <v>746</v>
       </c>
       <c r="J193" t="s">
         <v>709</v>
@@ -10175,19 +10175,19 @@
         <v>14</v>
       </c>
       <c r="E199" t="s">
+        <v>705</v>
+      </c>
+      <c r="F199" t="s">
         <v>765</v>
       </c>
-      <c r="F199" t="s">
-        <v>706</v>
-      </c>
       <c r="G199" t="s">
-        <v>766</v>
+        <v>707</v>
       </c>
       <c r="H199" t="s">
         <v>338</v>
       </c>
       <c r="I199" t="s">
-        <v>708</v>
+        <v>766</v>
       </c>
       <c r="J199" t="s">
         <v>767</v>
@@ -10210,19 +10210,19 @@
         <v>14</v>
       </c>
       <c r="E200" t="s">
+        <v>705</v>
+      </c>
+      <c r="F200" t="s">
         <v>765</v>
       </c>
-      <c r="F200" t="s">
-        <v>706</v>
-      </c>
       <c r="G200" t="s">
-        <v>766</v>
+        <v>707</v>
       </c>
       <c r="H200" t="s">
         <v>338</v>
       </c>
       <c r="I200" t="s">
-        <v>708</v>
+        <v>766</v>
       </c>
       <c r="J200" t="s">
         <v>767</v>
@@ -10245,19 +10245,19 @@
         <v>14</v>
       </c>
       <c r="E201" t="s">
+        <v>705</v>
+      </c>
+      <c r="F201" t="s">
         <v>765</v>
       </c>
-      <c r="F201" t="s">
-        <v>706</v>
-      </c>
       <c r="G201" t="s">
-        <v>766</v>
+        <v>707</v>
       </c>
       <c r="H201" t="s">
         <v>338</v>
       </c>
       <c r="I201" t="s">
-        <v>708</v>
+        <v>766</v>
       </c>
       <c r="J201" t="s">
         <v>767</v>
@@ -10277,19 +10277,19 @@
         <v>14</v>
       </c>
       <c r="E202" t="s">
+        <v>705</v>
+      </c>
+      <c r="F202" t="s">
         <v>765</v>
       </c>
-      <c r="F202" t="s">
-        <v>706</v>
-      </c>
       <c r="G202" t="s">
-        <v>766</v>
+        <v>707</v>
       </c>
       <c r="H202" t="s">
         <v>338</v>
       </c>
       <c r="I202" t="s">
-        <v>708</v>
+        <v>766</v>
       </c>
       <c r="J202" t="s">
         <v>767</v>
@@ -10312,19 +10312,19 @@
         <v>14</v>
       </c>
       <c r="E203" t="s">
+        <v>575</v>
+      </c>
+      <c r="F203" t="s">
         <v>765</v>
       </c>
-      <c r="F203" t="s">
-        <v>706</v>
-      </c>
       <c r="G203" t="s">
-        <v>746</v>
+        <v>707</v>
       </c>
       <c r="H203" t="s">
         <v>338</v>
       </c>
       <c r="I203" t="s">
-        <v>576</v>
+        <v>746</v>
       </c>
       <c r="J203" t="s">
         <v>767</v>
@@ -10344,19 +10344,19 @@
         <v>14</v>
       </c>
       <c r="E204" t="s">
+        <v>705</v>
+      </c>
+      <c r="F204" t="s">
         <v>765</v>
       </c>
-      <c r="F204" t="s">
-        <v>706</v>
-      </c>
       <c r="G204" t="s">
-        <v>766</v>
+        <v>707</v>
       </c>
       <c r="H204" t="s">
         <v>338</v>
       </c>
       <c r="I204" t="s">
-        <v>708</v>
+        <v>766</v>
       </c>
       <c r="J204" t="s">
         <v>767</v>
@@ -10379,19 +10379,19 @@
         <v>14</v>
       </c>
       <c r="E205" t="s">
+        <v>705</v>
+      </c>
+      <c r="F205" t="s">
         <v>784</v>
       </c>
-      <c r="F205" t="s">
-        <v>706</v>
-      </c>
       <c r="G205" t="s">
-        <v>785</v>
+        <v>707</v>
       </c>
       <c r="H205" t="s">
         <v>338</v>
       </c>
       <c r="I205" t="s">
-        <v>708</v>
+        <v>785</v>
       </c>
       <c r="J205" t="s">
         <v>786</v>
@@ -10414,19 +10414,19 @@
         <v>14</v>
       </c>
       <c r="E206" t="s">
+        <v>705</v>
+      </c>
+      <c r="F206" t="s">
         <v>784</v>
       </c>
-      <c r="F206" t="s">
-        <v>706</v>
-      </c>
       <c r="G206" t="s">
-        <v>785</v>
+        <v>707</v>
       </c>
       <c r="H206" t="s">
         <v>338</v>
       </c>
       <c r="I206" t="s">
-        <v>708</v>
+        <v>785</v>
       </c>
       <c r="J206" t="s">
         <v>786</v>
@@ -10446,19 +10446,19 @@
         <v>14</v>
       </c>
       <c r="E207" t="s">
+        <v>705</v>
+      </c>
+      <c r="F207" t="s">
         <v>784</v>
       </c>
-      <c r="F207" t="s">
-        <v>706</v>
-      </c>
       <c r="G207" t="s">
-        <v>785</v>
+        <v>707</v>
       </c>
       <c r="H207" t="s">
         <v>338</v>
       </c>
       <c r="I207" t="s">
-        <v>708</v>
+        <v>785</v>
       </c>
       <c r="J207" t="s">
         <v>786</v>
@@ -10481,19 +10481,19 @@
         <v>14</v>
       </c>
       <c r="E208" t="s">
+        <v>575</v>
+      </c>
+      <c r="F208" t="s">
         <v>784</v>
       </c>
-      <c r="F208" t="s">
-        <v>706</v>
-      </c>
       <c r="G208" t="s">
-        <v>746</v>
+        <v>707</v>
       </c>
       <c r="H208" t="s">
         <v>338</v>
       </c>
       <c r="I208" t="s">
-        <v>576</v>
+        <v>746</v>
       </c>
       <c r="J208" t="s">
         <v>786</v>
@@ -10516,19 +10516,19 @@
         <v>14</v>
       </c>
       <c r="E209" t="s">
+        <v>705</v>
+      </c>
+      <c r="F209" t="s">
         <v>784</v>
       </c>
-      <c r="F209" t="s">
-        <v>706</v>
-      </c>
       <c r="G209" t="s">
-        <v>785</v>
+        <v>707</v>
       </c>
       <c r="H209" t="s">
         <v>338</v>
       </c>
       <c r="I209" t="s">
-        <v>708</v>
+        <v>785</v>
       </c>
       <c r="J209" t="s">
         <v>786</v>
@@ -10720,19 +10720,19 @@
         <v>14</v>
       </c>
       <c r="E215" t="s">
-        <v>801</v>
+        <v>705</v>
       </c>
       <c r="F215" t="s">
         <v>802</v>
       </c>
       <c r="G215" t="s">
-        <v>766</v>
+        <v>803</v>
       </c>
       <c r="H215" t="s">
         <v>338</v>
       </c>
       <c r="I215" t="s">
-        <v>708</v>
+        <v>766</v>
       </c>
       <c r="J215" t="s">
         <v>805</v>
@@ -10889,19 +10889,19 @@
         <v>14</v>
       </c>
       <c r="E220" t="s">
-        <v>801</v>
+        <v>564</v>
       </c>
       <c r="F220" t="s">
         <v>802</v>
       </c>
       <c r="G220" t="s">
-        <v>663</v>
+        <v>803</v>
       </c>
       <c r="H220" t="s">
         <v>338</v>
       </c>
       <c r="I220" t="s">
-        <v>567</v>
+        <v>663</v>
       </c>
       <c r="J220" t="s">
         <v>805</v>
@@ -11096,13 +11096,13 @@
         <v>14</v>
       </c>
       <c r="E226" t="s">
-        <v>801</v>
+        <v>575</v>
       </c>
       <c r="F226" t="s">
         <v>802</v>
       </c>
       <c r="G226" t="s">
-        <v>575</v>
+        <v>803</v>
       </c>
       <c r="H226" t="s">
         <v>338</v>
@@ -11166,13 +11166,13 @@
         <v>14</v>
       </c>
       <c r="E228" t="s">
-        <v>801</v>
+        <v>337</v>
       </c>
       <c r="F228" t="s">
         <v>802</v>
       </c>
       <c r="G228" t="s">
-        <v>337</v>
+        <v>803</v>
       </c>
       <c r="H228" t="s">
         <v>338</v>
@@ -11201,19 +11201,19 @@
         <v>14</v>
       </c>
       <c r="E229" t="s">
+        <v>801</v>
+      </c>
+      <c r="F229" t="s">
         <v>859</v>
       </c>
-      <c r="F229" t="s">
-        <v>802</v>
-      </c>
       <c r="G229" t="s">
-        <v>860</v>
+        <v>803</v>
       </c>
       <c r="H229" t="s">
         <v>338</v>
       </c>
       <c r="I229" t="s">
-        <v>804</v>
+        <v>860</v>
       </c>
       <c r="J229" t="s">
         <v>861</v>
@@ -11236,19 +11236,19 @@
         <v>14</v>
       </c>
       <c r="E230" t="s">
+        <v>801</v>
+      </c>
+      <c r="F230" t="s">
         <v>859</v>
       </c>
-      <c r="F230" t="s">
-        <v>802</v>
-      </c>
       <c r="G230" t="s">
-        <v>860</v>
+        <v>803</v>
       </c>
       <c r="H230" t="s">
         <v>338</v>
       </c>
       <c r="I230" t="s">
-        <v>804</v>
+        <v>860</v>
       </c>
       <c r="J230" t="s">
         <v>861</v>
@@ -11271,19 +11271,19 @@
         <v>14</v>
       </c>
       <c r="E231" t="s">
+        <v>564</v>
+      </c>
+      <c r="F231" t="s">
         <v>859</v>
       </c>
-      <c r="F231" t="s">
-        <v>802</v>
-      </c>
       <c r="G231" t="s">
-        <v>623</v>
+        <v>803</v>
       </c>
       <c r="H231" t="s">
         <v>338</v>
       </c>
       <c r="I231" t="s">
-        <v>567</v>
+        <v>623</v>
       </c>
       <c r="J231" t="s">
         <v>861</v>
@@ -11306,19 +11306,19 @@
         <v>14</v>
       </c>
       <c r="E232" t="s">
+        <v>564</v>
+      </c>
+      <c r="F232" t="s">
         <v>859</v>
       </c>
-      <c r="F232" t="s">
-        <v>802</v>
-      </c>
       <c r="G232" t="s">
-        <v>663</v>
+        <v>803</v>
       </c>
       <c r="H232" t="s">
         <v>338</v>
       </c>
       <c r="I232" t="s">
-        <v>567</v>
+        <v>663</v>
       </c>
       <c r="J232" t="s">
         <v>861</v>
@@ -11341,19 +11341,19 @@
         <v>14</v>
       </c>
       <c r="E233" t="s">
+        <v>801</v>
+      </c>
+      <c r="F233" t="s">
         <v>859</v>
       </c>
-      <c r="F233" t="s">
-        <v>802</v>
-      </c>
       <c r="G233" t="s">
-        <v>860</v>
+        <v>803</v>
       </c>
       <c r="H233" t="s">
         <v>338</v>
       </c>
       <c r="I233" t="s">
-        <v>804</v>
+        <v>860</v>
       </c>
       <c r="J233" t="s">
         <v>861</v>
@@ -11376,19 +11376,19 @@
         <v>14</v>
       </c>
       <c r="E234" t="s">
+        <v>801</v>
+      </c>
+      <c r="F234" t="s">
         <v>859</v>
       </c>
-      <c r="F234" t="s">
-        <v>802</v>
-      </c>
       <c r="G234" t="s">
-        <v>860</v>
+        <v>803</v>
       </c>
       <c r="H234" t="s">
         <v>338</v>
       </c>
       <c r="I234" t="s">
-        <v>804</v>
+        <v>860</v>
       </c>
       <c r="J234" t="s">
         <v>861</v>
@@ -11411,19 +11411,19 @@
         <v>14</v>
       </c>
       <c r="E235" t="s">
+        <v>801</v>
+      </c>
+      <c r="F235" t="s">
         <v>859</v>
       </c>
-      <c r="F235" t="s">
-        <v>802</v>
-      </c>
       <c r="G235" t="s">
-        <v>860</v>
+        <v>803</v>
       </c>
       <c r="H235" t="s">
         <v>338</v>
       </c>
       <c r="I235" t="s">
-        <v>804</v>
+        <v>860</v>
       </c>
       <c r="J235" t="s">
         <v>861</v>
@@ -11446,19 +11446,19 @@
         <v>14</v>
       </c>
       <c r="E236" t="s">
+        <v>801</v>
+      </c>
+      <c r="F236" t="s">
         <v>859</v>
       </c>
-      <c r="F236" t="s">
-        <v>802</v>
-      </c>
       <c r="G236" t="s">
-        <v>860</v>
+        <v>803</v>
       </c>
       <c r="H236" t="s">
         <v>338</v>
       </c>
       <c r="I236" t="s">
-        <v>804</v>
+        <v>860</v>
       </c>
       <c r="J236" t="s">
         <v>861</v>
@@ -11481,19 +11481,19 @@
         <v>14</v>
       </c>
       <c r="E237" t="s">
+        <v>801</v>
+      </c>
+      <c r="F237" t="s">
         <v>859</v>
       </c>
-      <c r="F237" t="s">
-        <v>802</v>
-      </c>
       <c r="G237" t="s">
-        <v>860</v>
+        <v>803</v>
       </c>
       <c r="H237" t="s">
         <v>338</v>
       </c>
       <c r="I237" t="s">
-        <v>804</v>
+        <v>860</v>
       </c>
       <c r="J237" t="s">
         <v>861</v>
@@ -11516,19 +11516,19 @@
         <v>14</v>
       </c>
       <c r="E238" t="s">
+        <v>801</v>
+      </c>
+      <c r="F238" t="s">
         <v>859</v>
       </c>
-      <c r="F238" t="s">
-        <v>802</v>
-      </c>
       <c r="G238" t="s">
-        <v>860</v>
+        <v>803</v>
       </c>
       <c r="H238" t="s">
         <v>338</v>
       </c>
       <c r="I238" t="s">
-        <v>804</v>
+        <v>860</v>
       </c>
       <c r="J238" t="s">
         <v>861</v>
@@ -11551,19 +11551,19 @@
         <v>14</v>
       </c>
       <c r="E239" t="s">
+        <v>801</v>
+      </c>
+      <c r="F239" t="s">
         <v>892</v>
       </c>
-      <c r="F239" t="s">
-        <v>802</v>
-      </c>
       <c r="G239" t="s">
-        <v>893</v>
+        <v>803</v>
       </c>
       <c r="H239" t="s">
         <v>338</v>
       </c>
       <c r="I239" t="s">
-        <v>804</v>
+        <v>893</v>
       </c>
       <c r="J239" t="s">
         <v>894</v>
@@ -11586,13 +11586,13 @@
         <v>14</v>
       </c>
       <c r="E240" t="s">
+        <v>337</v>
+      </c>
+      <c r="F240" t="s">
         <v>898</v>
       </c>
-      <c r="F240" t="s">
+      <c r="G240" t="s">
         <v>899</v>
-      </c>
-      <c r="G240" t="s">
-        <v>337</v>
       </c>
       <c r="H240" t="s">
         <v>338</v>
@@ -11621,13 +11621,13 @@
         <v>14</v>
       </c>
       <c r="E241" t="s">
+        <v>337</v>
+      </c>
+      <c r="F241" t="s">
         <v>898</v>
       </c>
-      <c r="F241" t="s">
+      <c r="G241" t="s">
         <v>899</v>
-      </c>
-      <c r="G241" t="s">
-        <v>337</v>
       </c>
       <c r="H241" t="s">
         <v>338</v>
@@ -11656,13 +11656,13 @@
         <v>14</v>
       </c>
       <c r="E242" t="s">
+        <v>337</v>
+      </c>
+      <c r="F242" t="s">
         <v>898</v>
       </c>
-      <c r="F242" t="s">
+      <c r="G242" t="s">
         <v>899</v>
-      </c>
-      <c r="G242" t="s">
-        <v>337</v>
       </c>
       <c r="H242" t="s">
         <v>338</v>
@@ -11691,13 +11691,13 @@
         <v>14</v>
       </c>
       <c r="E243" t="s">
+        <v>337</v>
+      </c>
+      <c r="F243" t="s">
         <v>898</v>
       </c>
-      <c r="F243" t="s">
+      <c r="G243" t="s">
         <v>899</v>
-      </c>
-      <c r="G243" t="s">
-        <v>337</v>
       </c>
       <c r="H243" t="s">
         <v>338</v>
@@ -11726,13 +11726,13 @@
         <v>14</v>
       </c>
       <c r="E244" t="s">
+        <v>337</v>
+      </c>
+      <c r="F244" t="s">
         <v>898</v>
       </c>
-      <c r="F244" t="s">
+      <c r="G244" t="s">
         <v>899</v>
-      </c>
-      <c r="G244" t="s">
-        <v>337</v>
       </c>
       <c r="H244" t="s">
         <v>338</v>
@@ -11761,13 +11761,13 @@
         <v>14</v>
       </c>
       <c r="E245" t="s">
+        <v>337</v>
+      </c>
+      <c r="F245" t="s">
         <v>898</v>
       </c>
-      <c r="F245" t="s">
+      <c r="G245" t="s">
         <v>899</v>
-      </c>
-      <c r="G245" t="s">
-        <v>337</v>
       </c>
       <c r="H245" t="s">
         <v>338</v>
@@ -11793,19 +11793,19 @@
         <v>14</v>
       </c>
       <c r="E246" t="s">
+        <v>533</v>
+      </c>
+      <c r="F246" t="s">
         <v>918</v>
       </c>
-      <c r="F246" t="s">
+      <c r="G246" t="s">
         <v>899</v>
-      </c>
-      <c r="G246" t="s">
-        <v>919</v>
       </c>
       <c r="H246" t="s">
         <v>338</v>
       </c>
       <c r="I246" t="s">
-        <v>534</v>
+        <v>919</v>
       </c>
       <c r="J246" t="s">
         <v>920</v>
@@ -11827,11 +11827,11 @@
       <c r="D247" t="s">
         <v>14</v>
       </c>
-      <c r="F247" t="s">
+      <c r="E247" t="s">
+        <v>196</v>
+      </c>
+      <c r="G247" t="s">
         <v>924</v>
-      </c>
-      <c r="G247" t="s">
-        <v>196</v>
       </c>
       <c r="H247" t="s">
         <v>197</v>
@@ -11856,11 +11856,11 @@
       <c r="D248" t="s">
         <v>14</v>
       </c>
-      <c r="F248" t="s">
+      <c r="E248" t="s">
+        <v>196</v>
+      </c>
+      <c r="G248" t="s">
         <v>924</v>
-      </c>
-      <c r="G248" t="s">
-        <v>196</v>
       </c>
       <c r="H248" t="s">
         <v>197</v>
@@ -11885,11 +11885,11 @@
       <c r="D249" t="s">
         <v>14</v>
       </c>
-      <c r="F249" t="s">
+      <c r="E249" t="s">
+        <v>932</v>
+      </c>
+      <c r="G249" t="s">
         <v>924</v>
-      </c>
-      <c r="G249" t="s">
-        <v>932</v>
       </c>
       <c r="H249" t="s">
         <v>197</v>
@@ -11914,11 +11914,11 @@
       <c r="D250" t="s">
         <v>14</v>
       </c>
-      <c r="F250" t="s">
+      <c r="E250" t="s">
+        <v>196</v>
+      </c>
+      <c r="G250" t="s">
         <v>924</v>
-      </c>
-      <c r="G250" t="s">
-        <v>196</v>
       </c>
       <c r="H250" t="s">
         <v>197</v>
@@ -11940,11 +11940,11 @@
       <c r="D251" t="s">
         <v>14</v>
       </c>
-      <c r="F251" t="s">
+      <c r="E251" t="s">
+        <v>196</v>
+      </c>
+      <c r="G251" t="s">
         <v>924</v>
-      </c>
-      <c r="G251" t="s">
-        <v>196</v>
       </c>
       <c r="H251" t="s">
         <v>197</v>
@@ -11969,11 +11969,11 @@
       <c r="D252" t="s">
         <v>14</v>
       </c>
-      <c r="F252" t="s">
+      <c r="E252" t="s">
+        <v>196</v>
+      </c>
+      <c r="G252" t="s">
         <v>924</v>
-      </c>
-      <c r="G252" t="s">
-        <v>196</v>
       </c>
       <c r="H252" t="s">
         <v>197</v>
@@ -11995,7 +11995,7 @@
       <c r="D253" t="s">
         <v>14</v>
       </c>
-      <c r="F253" t="s">
+      <c r="E253" t="s">
         <v>944</v>
       </c>
       <c r="G253" t="s">
@@ -12024,11 +12024,11 @@
       <c r="D254" t="s">
         <v>14</v>
       </c>
-      <c r="F254" t="s">
-        <v>944</v>
+      <c r="E254" t="s">
+        <v>454</v>
       </c>
       <c r="G254" t="s">
-        <v>454</v>
+        <v>945</v>
       </c>
       <c r="H254" t="s">
         <v>190</v>
@@ -12053,11 +12053,11 @@
       <c r="D255" t="s">
         <v>14</v>
       </c>
-      <c r="F255" t="s">
-        <v>944</v>
+      <c r="E255" t="s">
+        <v>954</v>
       </c>
       <c r="G255" t="s">
-        <v>954</v>
+        <v>945</v>
       </c>
       <c r="H255" t="s">
         <v>190</v>
@@ -12082,11 +12082,11 @@
       <c r="D256" t="s">
         <v>14</v>
       </c>
-      <c r="F256" t="s">
-        <v>944</v>
+      <c r="E256" t="s">
+        <v>954</v>
       </c>
       <c r="G256" t="s">
-        <v>954</v>
+        <v>945</v>
       </c>
       <c r="H256" t="s">
         <v>190</v>
@@ -12111,11 +12111,11 @@
       <c r="D257" t="s">
         <v>14</v>
       </c>
-      <c r="F257" t="s">
-        <v>944</v>
+      <c r="E257" t="s">
+        <v>954</v>
       </c>
       <c r="G257" t="s">
-        <v>954</v>
+        <v>945</v>
       </c>
       <c r="H257" t="s">
         <v>190</v>
@@ -12140,11 +12140,11 @@
       <c r="D258" t="s">
         <v>14</v>
       </c>
-      <c r="F258" t="s">
-        <v>944</v>
+      <c r="E258" t="s">
+        <v>705</v>
       </c>
       <c r="G258" t="s">
-        <v>707</v>
+        <v>945</v>
       </c>
       <c r="H258" t="s">
         <v>338</v>
@@ -12169,11 +12169,11 @@
       <c r="D259" t="s">
         <v>14</v>
       </c>
-      <c r="F259" t="s">
-        <v>944</v>
+      <c r="E259" t="s">
+        <v>954</v>
       </c>
       <c r="G259" t="s">
-        <v>954</v>
+        <v>945</v>
       </c>
       <c r="H259" t="s">
         <v>190</v>
@@ -12198,11 +12198,11 @@
       <c r="D260" t="s">
         <v>14</v>
       </c>
-      <c r="F260" t="s">
-        <v>944</v>
+      <c r="E260" t="s">
+        <v>337</v>
       </c>
       <c r="G260" t="s">
-        <v>337</v>
+        <v>945</v>
       </c>
       <c r="H260" t="s">
         <v>338</v>
@@ -12227,11 +12227,11 @@
       <c r="D261" t="s">
         <v>14</v>
       </c>
-      <c r="F261" t="s">
-        <v>944</v>
+      <c r="E261" t="s">
+        <v>973</v>
       </c>
       <c r="G261" t="s">
-        <v>973</v>
+        <v>945</v>
       </c>
       <c r="H261" t="s">
         <v>406</v>
@@ -12256,11 +12256,11 @@
       <c r="D262" t="s">
         <v>14</v>
       </c>
-      <c r="F262" t="s">
-        <v>944</v>
+      <c r="E262" t="s">
+        <v>337</v>
       </c>
       <c r="G262" t="s">
-        <v>337</v>
+        <v>945</v>
       </c>
       <c r="H262" t="s">
         <v>338</v>
@@ -12285,11 +12285,11 @@
       <c r="D263" t="s">
         <v>14</v>
       </c>
-      <c r="F263" t="s">
-        <v>944</v>
+      <c r="E263" t="s">
+        <v>981</v>
       </c>
       <c r="G263" t="s">
-        <v>981</v>
+        <v>945</v>
       </c>
       <c r="H263" t="s">
         <v>378</v>
@@ -12314,11 +12314,11 @@
       <c r="D264" t="s">
         <v>14</v>
       </c>
-      <c r="F264" t="s">
-        <v>944</v>
+      <c r="E264" t="s">
+        <v>58</v>
       </c>
       <c r="G264" t="s">
-        <v>58</v>
+        <v>945</v>
       </c>
       <c r="H264" t="s">
         <v>59</v>
@@ -12343,11 +12343,11 @@
       <c r="D265" t="s">
         <v>14</v>
       </c>
-      <c r="F265" t="s">
-        <v>944</v>
+      <c r="E265" t="s">
+        <v>15</v>
       </c>
       <c r="G265" t="s">
-        <v>17</v>
+        <v>945</v>
       </c>
       <c r="H265" t="s">
         <v>18</v>
@@ -12372,11 +12372,11 @@
       <c r="D266" t="s">
         <v>14</v>
       </c>
-      <c r="F266" t="s">
-        <v>944</v>
+      <c r="E266" t="s">
+        <v>992</v>
       </c>
       <c r="G266" t="s">
-        <v>992</v>
+        <v>945</v>
       </c>
       <c r="H266" t="s">
         <v>236</v>
@@ -12401,11 +12401,11 @@
       <c r="D267" t="s">
         <v>14</v>
       </c>
-      <c r="F267" t="s">
+      <c r="E267" t="s">
+        <v>243</v>
+      </c>
+      <c r="G267" t="s">
         <v>997</v>
-      </c>
-      <c r="G267" t="s">
-        <v>243</v>
       </c>
       <c r="H267" t="s">
         <v>236</v>
@@ -12430,11 +12430,11 @@
       <c r="D268" t="s">
         <v>14</v>
       </c>
-      <c r="F268" t="s">
+      <c r="E268" t="s">
+        <v>420</v>
+      </c>
+      <c r="G268" t="s">
         <v>1002</v>
-      </c>
-      <c r="G268" t="s">
-        <v>421</v>
       </c>
       <c r="H268" t="s">
         <v>378</v>
@@ -12459,11 +12459,11 @@
       <c r="D269" t="s">
         <v>14</v>
       </c>
-      <c r="F269" t="s">
+      <c r="E269" t="s">
+        <v>243</v>
+      </c>
+      <c r="G269" t="s">
         <v>1007</v>
-      </c>
-      <c r="G269" t="s">
-        <v>243</v>
       </c>
       <c r="H269" t="s">
         <v>236</v>
@@ -12488,11 +12488,11 @@
       <c r="D270" t="s">
         <v>14</v>
       </c>
-      <c r="F270" t="s">
+      <c r="E270" t="s">
+        <v>243</v>
+      </c>
+      <c r="G270" t="s">
         <v>1007</v>
-      </c>
-      <c r="G270" t="s">
-        <v>243</v>
       </c>
       <c r="H270" t="s">
         <v>236</v>
@@ -12517,7 +12517,7 @@
       <c r="D271" t="s">
         <v>14</v>
       </c>
-      <c r="F271" t="s">
+      <c r="E271" t="s">
         <v>1015</v>
       </c>
       <c r="G271" t="s">
@@ -12543,7 +12543,7 @@
       <c r="D272" t="s">
         <v>14</v>
       </c>
-      <c r="F272" t="s">
+      <c r="E272" t="s">
         <v>1015</v>
       </c>
       <c r="G272" t="s">
@@ -12572,7 +12572,7 @@
       <c r="D273" t="s">
         <v>14</v>
       </c>
-      <c r="F273" t="s">
+      <c r="E273" t="s">
         <v>1015</v>
       </c>
       <c r="G273" t="s">
@@ -12598,7 +12598,7 @@
       <c r="D274" t="s">
         <v>14</v>
       </c>
-      <c r="F274" t="s">
+      <c r="E274" t="s">
         <v>1015</v>
       </c>
       <c r="G274" t="s">
@@ -12627,7 +12627,7 @@
       <c r="D275" t="s">
         <v>14</v>
       </c>
-      <c r="F275" t="s">
+      <c r="E275" t="s">
         <v>1015</v>
       </c>
       <c r="G275" t="s">
@@ -12656,7 +12656,7 @@
       <c r="D276" t="s">
         <v>14</v>
       </c>
-      <c r="F276" t="s">
+      <c r="E276" t="s">
         <v>1015</v>
       </c>
       <c r="G276" t="s">
@@ -12685,7 +12685,7 @@
       <c r="D277" t="s">
         <v>14</v>
       </c>
-      <c r="F277" t="s">
+      <c r="E277" t="s">
         <v>1015</v>
       </c>
       <c r="G277" t="s">
@@ -12714,11 +12714,11 @@
       <c r="D278" t="s">
         <v>14</v>
       </c>
-      <c r="F278" t="s">
+      <c r="E278" t="s">
+        <v>420</v>
+      </c>
+      <c r="G278" t="s">
         <v>1038</v>
-      </c>
-      <c r="G278" t="s">
-        <v>421</v>
       </c>
       <c r="H278" t="s">
         <v>378</v>
@@ -12743,11 +12743,11 @@
       <c r="D279" t="s">
         <v>14</v>
       </c>
-      <c r="F279" t="s">
+      <c r="E279" t="s">
+        <v>92</v>
+      </c>
+      <c r="G279" t="s">
         <v>1038</v>
-      </c>
-      <c r="G279" t="s">
-        <v>94</v>
       </c>
       <c r="H279" t="s">
         <v>59</v>
@@ -12772,11 +12772,11 @@
       <c r="D280" t="s">
         <v>14</v>
       </c>
-      <c r="F280" t="s">
+      <c r="E280" t="s">
+        <v>15</v>
+      </c>
+      <c r="G280" t="s">
         <v>1038</v>
-      </c>
-      <c r="G280" t="s">
-        <v>17</v>
       </c>
       <c r="H280" t="s">
         <v>18</v>
@@ -12801,11 +12801,11 @@
       <c r="D281" t="s">
         <v>14</v>
       </c>
-      <c r="F281" t="s">
+      <c r="E281" t="s">
+        <v>352</v>
+      </c>
+      <c r="G281" t="s">
         <v>1038</v>
-      </c>
-      <c r="G281" t="s">
-        <v>352</v>
       </c>
       <c r="H281" t="s">
         <v>236</v>
@@ -12830,11 +12830,11 @@
       <c r="D282" t="s">
         <v>14</v>
       </c>
-      <c r="F282" t="s">
+      <c r="E282" t="s">
+        <v>253</v>
+      </c>
+      <c r="G282" t="s">
         <v>1038</v>
-      </c>
-      <c r="G282" t="s">
-        <v>253</v>
       </c>
       <c r="H282" t="s">
         <v>254</v>
@@ -12859,17 +12859,17 @@
       <c r="D283" t="s">
         <v>14</v>
       </c>
-      <c r="F283" t="s">
+      <c r="E283" t="s">
+        <v>801</v>
+      </c>
+      <c r="G283" t="s">
         <v>1055</v>
-      </c>
-      <c r="G283" t="s">
-        <v>893</v>
       </c>
       <c r="H283" t="s">
         <v>338</v>
       </c>
       <c r="I283" t="s">
-        <v>804</v>
+        <v>893</v>
       </c>
       <c r="K283" t="s">
         <v>1056</v>
@@ -12888,11 +12888,11 @@
       <c r="D284" t="s">
         <v>14</v>
       </c>
-      <c r="F284" t="s">
+      <c r="E284" t="s">
+        <v>253</v>
+      </c>
+      <c r="G284" t="s">
         <v>1060</v>
-      </c>
-      <c r="G284" t="s">
-        <v>253</v>
       </c>
       <c r="H284" t="s">
         <v>254</v>
@@ -12914,11 +12914,11 @@
       <c r="D285" t="s">
         <v>14</v>
       </c>
-      <c r="F285" t="s">
+      <c r="E285" t="s">
+        <v>352</v>
+      </c>
+      <c r="G285" t="s">
         <v>1064</v>
-      </c>
-      <c r="G285" t="s">
-        <v>352</v>
       </c>
       <c r="H285" t="s">
         <v>236</v>
@@ -12943,11 +12943,11 @@
       <c r="D286" t="s">
         <v>14</v>
       </c>
-      <c r="F286" t="s">
+      <c r="E286" t="s">
+        <v>981</v>
+      </c>
+      <c r="G286" t="s">
         <v>1069</v>
-      </c>
-      <c r="G286" t="s">
-        <v>981</v>
       </c>
       <c r="H286" t="s">
         <v>378</v>
@@ -12972,11 +12972,11 @@
       <c r="D287" t="s">
         <v>14</v>
       </c>
-      <c r="F287" t="s">
+      <c r="E287" t="s">
+        <v>981</v>
+      </c>
+      <c r="G287" t="s">
         <v>1069</v>
-      </c>
-      <c r="G287" t="s">
-        <v>981</v>
       </c>
       <c r="H287" t="s">
         <v>378</v>
@@ -13001,11 +13001,11 @@
       <c r="D288" t="s">
         <v>14</v>
       </c>
-      <c r="F288" t="s">
+      <c r="E288" t="s">
+        <v>75</v>
+      </c>
+      <c r="G288" t="s">
         <v>1069</v>
-      </c>
-      <c r="G288" t="s">
-        <v>75</v>
       </c>
       <c r="H288" t="s">
         <v>18</v>
@@ -13030,11 +13030,11 @@
       <c r="D289" t="s">
         <v>14</v>
       </c>
-      <c r="F289" t="s">
+      <c r="E289" t="s">
+        <v>58</v>
+      </c>
+      <c r="G289" t="s">
         <v>1069</v>
-      </c>
-      <c r="G289" t="s">
-        <v>58</v>
       </c>
       <c r="H289" t="s">
         <v>59</v>
@@ -13059,11 +13059,11 @@
       <c r="D290" t="s">
         <v>14</v>
       </c>
-      <c r="F290" t="s">
+      <c r="E290" t="s">
+        <v>58</v>
+      </c>
+      <c r="G290" t="s">
         <v>1069</v>
-      </c>
-      <c r="G290" t="s">
-        <v>58</v>
       </c>
       <c r="H290" t="s">
         <v>59</v>
@@ -13088,11 +13088,11 @@
       <c r="D291" t="s">
         <v>14</v>
       </c>
-      <c r="F291" t="s">
+      <c r="E291" t="s">
+        <v>352</v>
+      </c>
+      <c r="G291" t="s">
         <v>1069</v>
-      </c>
-      <c r="G291" t="s">
-        <v>352</v>
       </c>
       <c r="H291" t="s">
         <v>236</v>
@@ -13117,11 +13117,11 @@
       <c r="D292" t="s">
         <v>14</v>
       </c>
-      <c r="F292" t="s">
+      <c r="E292" t="s">
+        <v>352</v>
+      </c>
+      <c r="G292" t="s">
         <v>1069</v>
-      </c>
-      <c r="G292" t="s">
-        <v>352</v>
       </c>
       <c r="H292" t="s">
         <v>236</v>
@@ -13146,11 +13146,11 @@
       <c r="D293" t="s">
         <v>14</v>
       </c>
-      <c r="F293" t="s">
+      <c r="E293" t="s">
+        <v>352</v>
+      </c>
+      <c r="G293" t="s">
         <v>1069</v>
-      </c>
-      <c r="G293" t="s">
-        <v>352</v>
       </c>
       <c r="H293" t="s">
         <v>236</v>
@@ -13175,11 +13175,11 @@
       <c r="D294" t="s">
         <v>14</v>
       </c>
-      <c r="F294" t="s">
+      <c r="E294" t="s">
+        <v>352</v>
+      </c>
+      <c r="G294" t="s">
         <v>1069</v>
-      </c>
-      <c r="G294" t="s">
-        <v>352</v>
       </c>
       <c r="H294" t="s">
         <v>236</v>
@@ -13204,11 +13204,11 @@
       <c r="D295" t="s">
         <v>14</v>
       </c>
-      <c r="F295" t="s">
+      <c r="E295" t="s">
+        <v>352</v>
+      </c>
+      <c r="G295" t="s">
         <v>1098</v>
-      </c>
-      <c r="G295" t="s">
-        <v>352</v>
       </c>
       <c r="H295" t="s">
         <v>236</v>
@@ -13233,11 +13233,11 @@
       <c r="D296" t="s">
         <v>14</v>
       </c>
-      <c r="F296" t="s">
+      <c r="E296" t="s">
+        <v>352</v>
+      </c>
+      <c r="G296" t="s">
         <v>1098</v>
-      </c>
-      <c r="G296" t="s">
-        <v>352</v>
       </c>
       <c r="H296" t="s">
         <v>236</v>

--- a/api/2/clv2/xlsx/en/SectorCOFOG.xlsx
+++ b/api/2/clv2/xlsx/en/SectorCOFOG.xlsx
@@ -28,27 +28,27 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-group</t>
   </si>
   <si>
+    <t>codeforiati:cofog-division</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-class</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -61,27 +61,27 @@
     <t>active</t>
   </si>
   <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>09.8 - Education n.e.c.</t>
   </si>
   <si>
+    <t>09 - Education</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -91,12 +91,12 @@
     <t>Educational buildings, equipment, materials; subsidiary services to education (boarding facilities, staff housing); language training; colloquia, seminars, lectures, etc.</t>
   </si>
   <si>
+    <t>09.6.0 - Subsidiary services to education (IS)</t>
+  </si>
+  <si>
     <t>09.6 - Subsidiary services to education</t>
   </si>
   <si>
-    <t>09.6.0 - Subsidiary services to education (IS)</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
@@ -115,12 +115,12 @@
     <t>Research and studies on education effectiveness, relevance and quality; systematic evaluation and monitoring.</t>
   </si>
   <si>
+    <t>09.7.0 - R&amp;D Education (CS)</t>
+  </si>
+  <si>
     <t>09.7 - R&amp;D Education</t>
   </si>
   <si>
-    <t>09.7.0 - R&amp;D Education (CS)</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
@@ -130,18 +130,18 @@
     <t>Formal and non-formal primary education for children; all elementary and first cycle systematic instruction; provision of learning materials.</t>
   </si>
   <si>
+    <t>09.1.2 - Primary education (IS)</t>
+  </si>
+  <si>
+    <t>Basic Education</t>
+  </si>
+  <si>
     <t>09.1 - Pre‐primary and primary education</t>
   </si>
   <si>
     <t>112</t>
   </si>
   <si>
-    <t>09.1.2 - Primary education (IS)</t>
-  </si>
-  <si>
-    <t>Basic Education</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -190,15 +190,15 @@
     <t>Provision of meals or snacks at school; other uses of food for the achievement of educational outcomes including 'take-home' food rations provided as economic incentives to families (or foster families, or other child care institutions) in return for a child's regular attendance at school; food provided to adults or youth who attend literacy or vocational training programmes; food for pre-school activities with an educational component. These activities may help reduce children's hunger during the school day if provision of food/meals contains bioavailable nutrients to address specific nutrition needs and have nutrition expected outcomes in school children, or if the rationale mainstream nutrition or expected outcome is nutrition-linked.</t>
   </si>
   <si>
+    <t>07.4.0 - Public health services (IS)</t>
+  </si>
+  <si>
     <t>07.4 - Public health services</t>
   </si>
   <si>
     <t>07 - Health</t>
   </si>
   <si>
-    <t>07.4.0 - Public health services (IS)</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
@@ -208,12 +208,12 @@
     <t>Second cycle systematic instruction at junior level.</t>
   </si>
   <si>
+    <t>09.2.1 - Lower‐secondary education (IS)</t>
+  </si>
+  <si>
     <t>09.2 - Secondary education</t>
   </si>
   <si>
-    <t>09.2.1 - Lower‐secondary education (IS)</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
@@ -223,15 +223,15 @@
     <t>Second cycle systematic instruction at senior levels.</t>
   </si>
   <si>
+    <t>09.2.2 - Upper‐secondary education (IS)</t>
+  </si>
+  <si>
+    <t>Secondary Education</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>09.2.2 - Upper‐secondary education (IS)</t>
-  </si>
-  <si>
-    <t>Secondary Education</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -241,12 +241,12 @@
     <t>Elementary vocational training and secondary level technical education; on-the job training; apprenticeships; including informal vocational training.</t>
   </si>
   <si>
+    <t>09.5.0 - Education not definable by level (IS)</t>
+  </si>
+  <si>
     <t>09.5 - Education not definable by level</t>
   </si>
   <si>
-    <t>09.5.0 - Education not definable by level (IS)</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
@@ -256,18 +256,18 @@
     <t>Degree and diploma programmes at universities, colleges and polytechnics; scholarships.</t>
   </si>
   <si>
+    <t>09.4.1 - First stage of tertiary education (IS)</t>
+  </si>
+  <si>
+    <t>Post-Secondary Education</t>
+  </si>
+  <si>
     <t>09.4 - Tertiary education</t>
   </si>
   <si>
     <t>114</t>
   </si>
   <si>
-    <t>09.4.1 - First stage of tertiary education (IS)</t>
-  </si>
-  <si>
-    <t>Post-Secondary Education</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -277,12 +277,12 @@
     <t>Professional-level vocational training programmes and in-service training.</t>
   </si>
   <si>
+    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
+  </si>
+  <si>
     <t>09.3 - Post‐secondary non‐tertiary education</t>
   </si>
   <si>
-    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
@@ -292,24 +292,24 @@
     <t>Health sector policy, planning and programmes; aid to health ministries, public health administration; institution capacity building and advice; medical insurance programmes; including health system strengthening and health governance; unspecified health activities.</t>
   </si>
   <si>
+    <t>07.6.0 - Health n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Health, General</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
     <t>07.6 - Health n.e.c.</t>
   </si>
   <si>
     <t>121</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>07.6.0 - Health n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>Health, General</t>
-  </si>
-  <si>
-    <t>Health</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -328,12 +328,12 @@
     <t>General medical research (excluding basic health research and research for prevention and control of NCDs (12382)).</t>
   </si>
   <si>
+    <t>07.5.0 - R&amp;D Health (CS)</t>
+  </si>
+  <si>
     <t>07.5 - R&amp;D Health</t>
   </si>
   <si>
-    <t>07.5.0 - R&amp;D Health (CS)</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
@@ -343,12 +343,12 @@
     <t>Laboratories, specialised clinics and hospitals (including equipment and supplies); ambulances; dental services; medical rehabilitation. Excludes noncommunicable diseases (123xx).</t>
   </si>
   <si>
+    <t>07.2.1 - General medical services (IS)</t>
+  </si>
+  <si>
     <t>07.2 - Outpatient services</t>
   </si>
   <si>
-    <t>07.2.1 - General medical services (IS)</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -367,12 +367,12 @@
     <t>Basic and primary health care programmes; paramedical and nursing care programmes; supply of drugs, medicines and vaccines related to basic health care; activities aimed at achieving universal health coverage.</t>
   </si>
   <si>
+    <t>Basic Health</t>
+  </si>
+  <si>
     <t>122</t>
   </si>
   <si>
-    <t>Basic Health</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -382,12 +382,12 @@
     <t>District-level hospitals, clinics and dispensaries and related medical equipment; excluding specialised hospitals and clinics (12191).</t>
   </si>
   <si>
+    <t>07.3.1 - General hospital services (IS)</t>
+  </si>
+  <si>
     <t>07.3 - Hospital services</t>
   </si>
   <si>
-    <t>07.3.1 - General hospital services (IS)</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -460,12 +460,12 @@
     <t>Programmes for the prevention and control of NCDs which cannot be broken down into the codes below.</t>
   </si>
   <si>
+    <t>Non-communicable diseases (NCDs)</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>Non-communicable diseases (NCDs)</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -580,21 +580,21 @@
     <t>Water sector policy and governance, including legislation, regulation, planning and management as well as transboundary management of water; institutional capacity development; activities supporting the Integrated Water Resource Management approach (IWRM: see box below).</t>
   </si>
   <si>
+    <t>06.3.0 - Water supply (CS)</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>Water Supply &amp; Sanitation</t>
+  </si>
+  <si>
     <t>06.3 - Water supply</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
-    <t>06.3.0 - Water supply (CS)</t>
-  </si>
-  <si>
-    <t>Water Supply &amp; Sanitation</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -604,15 +604,15 @@
     <t>Collection and usage of quantitative and qualitative data on water resources; creation and sharing of water knowledge; conservation and rehabilitation of inland surface waters (rivers, lakes etc.), ground water and coastal waters; prevention of water contamination.</t>
   </si>
   <si>
+    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>05.6 - Environmental protection n.e.c.</t>
   </si>
   <si>
     <t>05 - Environmental protection</t>
   </si>
   <si>
-    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>Large scale sewerage including trunk sewers and sewage pumping stations; domestic and industrial waste water treatment plants.</t>
   </si>
   <si>
+    <t>05.2.0 - Waste water management (CS)</t>
+  </si>
+  <si>
     <t>05.2 - Waste water management</t>
   </si>
   <si>
-    <t>05.2.0 - Waste water management (CS)</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -691,12 +691,12 @@
     <t>Municipal and industrial solid waste management, including hazardous and toxic waste; collection, disposal and treatment; landfill areas; composting and reuse.</t>
   </si>
   <si>
+    <t>05.1.0 - Waste management (CS)</t>
+  </si>
+  <si>
     <t>05.1 - Waste management</t>
   </si>
   <si>
-    <t>05.1.0 - Waste management (CS)</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
@@ -715,27 +715,27 @@
     <t>Institution-building assistance to strengthen core public sector management systems and capacities. This includes general public policy management, co-ordination, planning and reform; human resource management; organisational development; civil service reform; e-government; development planning, monitoring and evaluation; support to ministries involved in aid co-ordination; other ministries and government departments when sector cannot be specified. (Use specific sector codes for development of systems and capacities in sector ministries. For macro-economic policy use code 15142. For public procurement use code 15125.)</t>
   </si>
   <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
     <t>01.3 - General services</t>
   </si>
   <si>
+    <t>01 - General public services</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
-    <t>01.3.1 - General personnel services (CS)</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -745,12 +745,12 @@
     <t>Fiscal policy and planning; support to ministries of finance; strengthening financial and managerial accountability; public expenditure management; improving financial management systems; budget drafting; inter-governmental fiscal relations, public audit, public debt. (Use code 15114 for domestic revenue mobilisation and code 33120 for customs).</t>
   </si>
   <si>
+    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
+  </si>
+  <si>
     <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
   </si>
   <si>
-    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
@@ -760,12 +760,12 @@
     <t>Decentralisation processes (including political, administrative and fiscal dimensions); intergovernmental relations and federalism; strengthening departments of regional and local government, regional and local authorities and their national associations. (Use specific sector codes for decentralisation of sector management and services.)</t>
   </si>
   <si>
+    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
+  </si>
+  <si>
     <t>01.8 - Transfers of a general character between different levels of government</t>
   </si>
   <si>
-    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
@@ -775,15 +775,15 @@
     <t>Specialised organisations, institutions and frameworks for the prevention of and combat against corruption, bribery, money-laundering and other aspects of organised crime, with or without law enforcement powers, e.g. anti-corruption commissions and monitoring bodies, special investigation services, institutions and initiatives of integrity and ethics oversight, specialised NGOs, other civil society and citizens' organisations directly concerned with corruption.</t>
   </si>
   <si>
+    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>03.6 - Public order and safety n.e.c.</t>
   </si>
   <si>
     <t>03 - Public order and safety</t>
   </si>
   <si>
-    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -859,12 +859,12 @@
     <t>Support to administration of developing countries' foreign aid (including triangular and south-south cooperation).</t>
   </si>
   <si>
+    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
+  </si>
+  <si>
     <t>01.2 - Foreign economic aid</t>
   </si>
   <si>
-    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -943,12 +943,12 @@
     <t>Judicial law and order sectors; policy development within ministries of justice or equivalents.</t>
   </si>
   <si>
+    <t>03.3.0 - Law courts (CS)</t>
+  </si>
+  <si>
     <t>03.3 - Law courts</t>
   </si>
   <si>
-    <t>03.3.0 - Law courts (CS)</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
@@ -958,12 +958,12 @@
     <t>Police affairs and services.</t>
   </si>
   <si>
+    <t>03.1.0 - Police services (CS)</t>
+  </si>
+  <si>
     <t>03.1 - Police services</t>
   </si>
   <si>
-    <t>03.1.0 - Police services (CS)</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
@@ -973,12 +973,12 @@
     <t>Fire-prevention and fire-fighting affairs and services.</t>
   </si>
   <si>
+    <t>03.2.0 - Fire‐protection services (CS)</t>
+  </si>
+  <si>
     <t>03.2 - Fire‐protection services</t>
   </si>
   <si>
-    <t>03.2.0 - Fire‐protection services (CS)</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -1012,12 +1012,12 @@
     <t>Prisons</t>
   </si>
   <si>
+    <t>03.4.0 - Prisons (CS)</t>
+  </si>
+  <si>
     <t>03.4 - Prisons</t>
   </si>
   <si>
-    <t>03.4.0 - Prisons (CS)</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
@@ -1027,15 +1027,15 @@
     <t>Support to macroeconomic stability, debt sustainability and structural reforms. Includes technical assistance for strategic formulation of policies, laws and regulation; capacity building to enhance public sector development; policy-based funding. For fiscal policy and domestic revenue mobilisation use codes 15111 and 15114.</t>
   </si>
   <si>
+    <t>04.1.1 - General economic and commercial affairs (CS)</t>
+  </si>
+  <si>
     <t>04.1 - General economic, commercial and labour affairs</t>
   </si>
   <si>
     <t>04 - Economic affairs</t>
   </si>
   <si>
-    <t>04.1.1 - General economic and commercial affairs (CS)</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -1072,12 +1072,12 @@
     <t>Electoral management bodies and processes, election observation, voters' education. (Use code 15230 when in the context of an international peacekeeping operation.)</t>
   </si>
   <si>
+    <t>01.6.0 - General public services n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>01.6 - General public services n.e.c.</t>
   </si>
   <si>
-    <t>01.6.0 - General public services n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -1099,12 +1099,12 @@
     <t>Activities that support free and uncensored flow of information on public issues; activities that increase the editorial and technical skills and the integrity of the print and broadcast media, e.g. training of journalists. (Use codes 22010-22040 for provision of equipment and capital assistance to media.)</t>
   </si>
   <si>
+    <t>04.6.0 - Communication (CS)</t>
+  </si>
+  <si>
     <t>04.6 - Communication</t>
   </si>
   <si>
-    <t>04.6.0 - Communication (CS)</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -1147,15 +1147,15 @@
     <t>Support for feminist, women-led and women's rights organisations and movements, and institutions (governmental and non-govermental) at all levels to enhance their effectiveness, influence and substainability (activities and core-funding). These organisations exist to bring about transformative change for gender equality and/or the rights of women and girls in developing countries. Their activities include agenda-setting, advocacy, policy dialogue, capacity development, awareness raising and prevention, service provision, conflict-prevention and peacebuilding, research, organising, and alliance and network building</t>
   </si>
   <si>
+    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
+  </si>
+  <si>
     <t>10.7 - Social exclusion n.e.c.</t>
   </si>
   <si>
     <t>10 - Social protection</t>
   </si>
   <si>
-    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -1192,12 +1192,12 @@
     <t>Collection, production, management and dissemination of statistics and data related to Government &amp; Civil Society. Includes macroeconomic statistics, government finance, fiscal and public sector statistics, support to development of administrative data infrastructure, civil society surveys.</t>
   </si>
   <si>
+    <t>01.5.0 - R&amp;D General public services (CS)</t>
+  </si>
+  <si>
     <t>01.5 - R&amp;D General public services</t>
   </si>
   <si>
-    <t>01.5.0 - R&amp;D General public services (CS)</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -1207,12 +1207,12 @@
     <t>Technical co-operation provided to parliament, government ministries, law enforcement agencies and the judiciary to assist review and reform of the security system to improve democratic governance and civilian control; technical co-operation provided to government to improve civilian oversight and democratic control of budgeting, management, accountability and auditing of security expenditure, including military budgets, as part of a public expenditure management programme; assistance to civil society to enhance its competence and capacity to scrutinise the security system so that it is managed in accordance with democratic norms and principles of accountability, transparency and good governance. [Other than in the context of an international peacekeeping operation (15230)].</t>
   </si>
   <si>
+    <t>Conflict, Peace &amp; Security</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
-    <t>Conflict, Peace &amp; Security</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -1231,15 +1231,15 @@
     <t>Bilateral participation in peacekeeping operations mandated or authorised by the United Nations (UN) through Security Council resolutions, and conducted by international organisations, e.g. UN, NATO, the European Union (Security and Defence Policy security-related operations), or regional groupings of developing countries. Direct contributions to the UN Department for Peacekeeping Operations (UNDPKO) budget are excluded from bilateral ODA (they are reportable in part as multilateral ODA, see Annex 9). The activities that can be reported as bilateral ODA under this code are limited to: human rights and election monitoring; reintegration of demobilised soldiers; rehabilitation of basic national infrastructure; monitoring or retraining of civil administrators and police forces; security sector reform and other rule of law-related activities; training in customs and border control procedures; advice or training in fiscal or macroeconomic stabilisation policy; repatriation and demobilisation of armed factions, and disposal of their weapons; explosive mine removal. The enforcement aspects of international peacekeeping operations are not reportable as ODA. ODA-eligible bilateral participation in peacekeeping operations can take the form of financing or provision of equipment or military or civilian personnel (e.g. police officers). The reportable cost is calculated as the excess over what the personnel and equipment would have cost to maintain had they not been assigned to take part in a peace operation. Costs for military contingents participating in UNDPKO peacekeeping operations are not reportable as ODA. International peacekeeping operations may include humanitarian-type activities (contributions to the form of equipment or personnel), as described in codes 7xxxx. These should be included under code 15230 if they are an integrated part of the activities above, otherwise they should be reported as humanitarian aid. NB: When using this code, indicate the name of the operation in the short description of the activity reported.</t>
   </si>
   <si>
+    <t>02.3.0 - Foreign military aid (CS)</t>
+  </si>
+  <si>
     <t>02.3 - Foreign military aid</t>
   </si>
   <si>
     <t>02 - Defence</t>
   </si>
   <si>
-    <t>02.3.0 - Foreign military aid (CS)</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -1276,18 +1276,18 @@
     <t>Social protection or social security strategies, legislation and administration; institution capacity building and advice; social security and other social schemes; support programmes, cash benefits, pensions and special programmes for older persons, orphans, persons with disabilities, children, mothers with newborns, those living in poverty, without jobs and other vulnerable groups; social dimensions of structural adjustment.</t>
   </si>
   <si>
+    <t>10.9.0 - Social protection n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>Other Social Infrastructure &amp; Services</t>
+  </si>
+  <si>
     <t>10.9 - Social protection n.e.c.</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>10.9.0 - Social protection n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>Other Social Infrastructure &amp; Services</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -1315,12 +1315,12 @@
     <t>Social protection schemes in the form of cash or in-kind benefits, including pensions, against the risks linked to old age.</t>
   </si>
   <si>
+    <t>10.2.0 - Old age (IS)</t>
+  </si>
+  <si>
     <t>10.2 - Old age</t>
   </si>
   <si>
-    <t>10.2.0 - Old age (IS)</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -1348,12 +1348,12 @@
     <t>Employment policy and planning; institution capacity building and advice; employment creation and income generation programmes; including activities specifically designed for the needs of vulnerable groups.</t>
   </si>
   <si>
+    <t>10.5.0 - Unemployment (IS)</t>
+  </si>
+  <si>
     <t>10.5 - Unemployment</t>
   </si>
   <si>
-    <t>10.5.0 - Unemployment (IS)</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
@@ -1363,12 +1363,12 @@
     <t>Housing sector policy, planning and programmes; excluding low-cost housing and slum clearance (16040).</t>
   </si>
   <si>
+    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>06.6 - Housing and community amenities n.e.c.</t>
   </si>
   <si>
-    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
@@ -1378,12 +1378,12 @@
     <t>Including slum clearance.</t>
   </si>
   <si>
+    <t>06.1.0 - Housing development (CS)</t>
+  </si>
+  <si>
     <t>06.1 - Housing development</t>
   </si>
   <si>
-    <t>06.1.0 - Housing development (CS)</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
@@ -1402,15 +1402,15 @@
     <t>Including libraries and museums.</t>
   </si>
   <si>
+    <t>08.2.0 - Cultural services (IS)</t>
+  </si>
+  <si>
     <t>08.2 - Cultural services</t>
   </si>
   <si>
     <t>08 - Recreation, culture and religion</t>
   </si>
   <si>
-    <t>08.2.0 - Cultural services (IS)</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -1444,12 +1444,12 @@
     <t>Recreation and sport</t>
   </si>
   <si>
+    <t>08.1.0 - Recreational and sporting services (IS)</t>
+  </si>
+  <si>
     <t>08.1 - Recreational and sporting services</t>
   </si>
   <si>
-    <t>08.1.0 - Recreational and sporting services (IS)</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -1528,12 +1528,12 @@
     <t>Road infrastructure, road vehicles; passenger road transport, motor passenger cars.</t>
   </si>
   <si>
+    <t>04.5.1 - Road transport (CS)</t>
+  </si>
+  <si>
     <t>04.5 - Transport</t>
   </si>
   <si>
-    <t>04.5.1 - Road transport (CS)</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -1615,12 +1615,12 @@
     <t>Whether or not related to transportation. Whenever possible, report storage projects under the sector of the resource being stored.</t>
   </si>
   <si>
+    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
+  </si>
+  <si>
     <t>04.7 - Other industries</t>
   </si>
   <si>
-    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -1684,12 +1684,12 @@
     <t>Radio and TV links, equipment; newspapers; printing and publishing.</t>
   </si>
   <si>
+    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
+  </si>
+  <si>
     <t>08.3 - Broadcasting and publishing services</t>
   </si>
   <si>
-    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
@@ -1708,24 +1708,24 @@
     <t>Energy sector policy, planning; aid to energy ministries and other governmental or nongovernmental institutions for activities related to the SDG7; institution capacity building and advice; tariffs, market building, unspecified energy activities; energy activities for which a more specific code cannot be assigned.</t>
   </si>
   <si>
+    <t>04.3.5 - Electricity (CS)</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
     <t>04.3 - Fuel and energy</t>
   </si>
   <si>
     <t>231</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>04.3.5 - Electricity (CS)</t>
-  </si>
-  <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
@@ -1741,12 +1741,12 @@
     <t>Regulation of the energy sector, including wholesale and retail electricity provision.</t>
   </si>
   <si>
+    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
+  </si>
+  <si>
     <t>04.8 - R&amp;D Economic affairs</t>
   </si>
   <si>
-    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -1783,12 +1783,12 @@
     <t>Renewable energy generation programmes that cannot be attributed to one single technology (codes 23220 through 23280 below). Fuelwood/charcoal production should be included under forestry 31261.</t>
   </si>
   <si>
+    <t>Energy generation, renewable sources</t>
+  </si>
+  <si>
     <t>232</t>
   </si>
   <si>
-    <t>Energy generation, renewable sources</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -1870,12 +1870,12 @@
     <t>Thermal power plants including when energy source cannot be determined; combined gas-coal power plants.</t>
   </si>
   <si>
+    <t>Energy generation, non-renewable sources</t>
+  </si>
+  <si>
     <t>233</t>
   </si>
   <si>
-    <t>Energy generation, non-renewable sources</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -1933,12 +1933,12 @@
     <t>Electric power plants that make use of both non-renewable and renewable energy sources.</t>
   </si>
   <si>
+    <t>Hybrid energy plants</t>
+  </si>
+  <si>
     <t>234</t>
   </si>
   <si>
-    <t>Hybrid energy plants</t>
-  </si>
-  <si>
     <t>23510</t>
   </si>
   <si>
@@ -1948,12 +1948,12 @@
     <t>See note regarding ODA eligibility of nuclear energy.</t>
   </si>
   <si>
+    <t>04.3.3 - Nuclear fuel (CS)</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>04.3.3 - Nuclear fuel (CS)</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
@@ -1963,12 +1963,12 @@
     <t>Power plants which are designed to produce heat only.</t>
   </si>
   <si>
+    <t>Energy distribution</t>
+  </si>
+  <si>
     <t>236</t>
   </si>
   <si>
-    <t>Energy distribution</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -2131,24 +2131,24 @@
     <t>Agricultural sector policy, planning and programmes; aid to agricultural ministries; institution capacity building and advice; unspecified agriculture.</t>
   </si>
   <si>
+    <t>04.2.1 - Agriculture (CS)</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
     <t>04.2 - Agriculture, forestry, fishing and hunting</t>
   </si>
   <si>
     <t>311</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>04.2.1 - Agriculture (CS)</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -2311,15 +2311,15 @@
     <t>Forestry sector policy, planning and programmes; institution capacity building and advice; forest surveys; unspecified forestry and agro-forestry activities.</t>
   </si>
   <si>
+    <t>04.2.2 - Forestry (CS)</t>
+  </si>
+  <si>
+    <t>Forestry</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>04.2.2 - Forestry (CS)</t>
-  </si>
-  <si>
-    <t>Forestry</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -2368,15 +2368,15 @@
     <t>Fishing sector policy, planning and programmes; institution capacity building and advice; ocean and coastal fishing; marine and freshwater fish surveys and prospecting; fishing boats/equipment; unspecified fishing activities.</t>
   </si>
   <si>
+    <t>04.2.3 - Fishing and hunting (CS)</t>
+  </si>
+  <si>
+    <t>Fishing</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>04.2.3 - Fishing and hunting (CS)</t>
-  </si>
-  <si>
-    <t>Fishing</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -2419,24 +2419,24 @@
     <t>Industrial sector policy, planning and programmes; institution capacity building and advice; unspecified industrial activities; manufacturing of goods not specified below.</t>
   </si>
   <si>
+    <t>04.4.2 - Manufacturing (CS)</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
     <t>04.4 - Mining, manufacturing and construction</t>
   </si>
   <si>
     <t>321</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>04.4.2 - Manufacturing (CS)</t>
-  </si>
-  <si>
-    <t>Industry</t>
-  </si>
-  <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -2593,15 +2593,15 @@
     <t>Mineral and mining sector policy, planning and programmes; mining legislation, mining cadastre, mineral resources inventory, information systems, institution capacity building and advice; unspecified mineral resources exploitation.</t>
   </si>
   <si>
+    <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
+  </si>
+  <si>
+    <t>Mineral Resources &amp; Mining</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
-  </si>
-  <si>
-    <t>Mineral Resources &amp; Mining</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -2692,15 +2692,15 @@
     <t>Construction sector policy and planning; excluding construction activities within specific sectors (e.g., hospital or school construction).</t>
   </si>
   <si>
+    <t>04.4.3 - Construction (CS)</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
     <t>323</t>
   </si>
   <si>
-    <t>04.4.3 - Construction (CS)</t>
-  </si>
-  <si>
-    <t>Construction</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
@@ -2710,15 +2710,15 @@
     <t>Trade policy and planning; support to ministries and departments responsible for trade policy; trade-related legislation and regulatory reforms; policy analysis and implementation of multilateral trade agreements e.g. technical barriers to trade and sanitary and phytosanitary measures (TBT/SPS) except at regional level (see 33130); mainstreaming trade in national development strategies (e.g. poverty reduction strategy papers); wholesale/retail trade; unspecified trade and trade promotion activities.</t>
   </si>
   <si>
+    <t>330</t>
+  </si>
+  <si>
+    <t>Trade Policies &amp; Regulations</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>330</t>
-  </si>
-  <si>
-    <t>Trade Policies &amp; Regulations</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -2770,15 +2770,15 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>04.7.3 - Tourism (CS)</t>
+  </si>
+  <si>
+    <t>Tourism</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>04.7.3 - Tourism (CS)</t>
-  </si>
-  <si>
-    <t>Tourism</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
@@ -2812,12 +2812,12 @@
     <t>Including natural reserves and actions in the surrounding areas; other measures to protect endangered or vulnerable species and their habitats (e.g. wetlands preservation).</t>
   </si>
   <si>
+    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
+  </si>
+  <si>
     <t>05.4 - Protection of biodiversity and landscape</t>
   </si>
   <si>
-    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -2848,18 +2848,18 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>430</t>
+  </si>
+  <si>
+    <t>Other Multisector</t>
+  </si>
+  <si>
     <t>04.9 - Economic affairs n.e.c.</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
-    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>Other Multisector</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -2878,12 +2878,12 @@
     <t>Urban development and planning; urban management, land information systems.</t>
   </si>
   <si>
+    <t>06.2.0 - Community development (CS)</t>
+  </si>
+  <si>
     <t>06.2 - Community development</t>
   </si>
   <si>
-    <t>06.2.0 - Community development (CS)</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -2935,12 +2935,12 @@
     <t>Disaster risk reduction activities if not sector specific. Comprises risk assessments, structural prevention measures (e.g. flood prevention infrastructure), preparedness measures (e.g. early warning systems) normative prevention measures (e.g. building codes, land-use planning), and risk transfer systems (e.g. insurance schemes, risk funds). Also includes building local and national capacities and supporting the establishment of efficient and sustainable national structures able to promote disaster risk reduction.</t>
   </si>
   <si>
+    <t>02.2.0 - Civil defence (CS)</t>
+  </si>
+  <si>
     <t>02.2 - Civil defence</t>
   </si>
   <si>
-    <t>02.2.0 - Civil defence (CS)</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
@@ -2959,12 +2959,12 @@
     <t>Short or longer term household food security programmes and activities that improve the access of households to nutritionally adequate diets (excluding any cash transfers within broader social welfare programmes that do not have a specific food security, food acquisition or nutrition focus which should be reported under code 16010).</t>
   </si>
   <si>
+    <t>10.4.0 - Family and children (IS)</t>
+  </si>
+  <si>
     <t>10.4 - Family and children</t>
   </si>
   <si>
-    <t>10.4.0 - Family and children (IS)</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -2992,12 +2992,12 @@
     <t>When sector cannot be identified.</t>
   </si>
   <si>
+    <t>01.4.0 - Basic research (CS)</t>
+  </si>
+  <si>
     <t>01.4 - Basic research</t>
   </si>
   <si>
-    <t>01.4.0 - Basic research (CS)</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -3061,16 +3061,16 @@
     <t>Actions falling outside the code headings below.</t>
   </si>
   <si>
+    <t>01.7.0 - Public debt transactions (CS)</t>
+  </si>
+  <si>
+    <t>600</t>
+  </si>
+  <si>
+    <t>Action Relating to Debt</t>
+  </si>
+  <si>
     <t>01.7 - Public debt transactions</t>
-  </si>
-  <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>01.7.0 - Public debt transactions (CS)</t>
-  </si>
-  <si>
-    <t>Action Relating to Debt</t>
   </si>
   <si>
     <t>60020</t>
@@ -3849,10 +3849,10 @@
         <v>38</v>
       </c>
       <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" t="s">
         <v>39</v>
-      </c>
-      <c r="G6" t="s">
-        <v>17</v>
       </c>
       <c r="H6" t="s">
         <v>18</v>
@@ -3861,10 +3861,10 @@
         <v>40</v>
       </c>
       <c r="J6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" t="s">
         <v>41</v>
-      </c>
-      <c r="K6" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3884,10 +3884,10 @@
         <v>15</v>
       </c>
       <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" t="s">
         <v>39</v>
-      </c>
-      <c r="G7" t="s">
-        <v>17</v>
       </c>
       <c r="H7" t="s">
         <v>18</v>
@@ -3896,10 +3896,10 @@
         <v>19</v>
       </c>
       <c r="J7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" t="s">
         <v>41</v>
-      </c>
-      <c r="K7" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -3919,10 +3919,10 @@
         <v>38</v>
       </c>
       <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" t="s">
         <v>39</v>
-      </c>
-      <c r="G8" t="s">
-        <v>17</v>
       </c>
       <c r="H8" t="s">
         <v>18</v>
@@ -3931,10 +3931,10 @@
         <v>40</v>
       </c>
       <c r="J8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" t="s">
         <v>41</v>
-      </c>
-      <c r="K8" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -3954,10 +3954,10 @@
         <v>38</v>
       </c>
       <c r="F9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" t="s">
         <v>39</v>
-      </c>
-      <c r="G9" t="s">
-        <v>17</v>
       </c>
       <c r="H9" t="s">
         <v>18</v>
@@ -3966,10 +3966,10 @@
         <v>40</v>
       </c>
       <c r="J9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" t="s">
         <v>41</v>
-      </c>
-      <c r="K9" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3986,25 +3986,25 @@
         <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" t="s">
         <v>39</v>
-      </c>
-      <c r="G10" t="s">
-        <v>17</v>
       </c>
       <c r="H10" t="s">
         <v>18</v>
       </c>
       <c r="I10" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="J10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" t="s">
         <v>41</v>
-      </c>
-      <c r="K10" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -4024,22 +4024,22 @@
         <v>58</v>
       </c>
       <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" t="s">
         <v>39</v>
       </c>
-      <c r="G11" t="s">
-        <v>17</v>
-      </c>
       <c r="H11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" t="s">
         <v>59</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>60</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>41</v>
-      </c>
-      <c r="K11" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -4059,10 +4059,10 @@
         <v>64</v>
       </c>
       <c r="F12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" t="s">
         <v>39</v>
-      </c>
-      <c r="G12" t="s">
-        <v>17</v>
       </c>
       <c r="H12" t="s">
         <v>18</v>
@@ -4071,10 +4071,10 @@
         <v>65</v>
       </c>
       <c r="J12" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" t="s">
         <v>41</v>
-      </c>
-      <c r="K12" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -4091,25 +4091,25 @@
         <v>14</v>
       </c>
       <c r="E13" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F13" t="s">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="G13" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="H13" t="s">
         <v>18</v>
       </c>
       <c r="I13" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13" t="s">
         <v>71</v>
-      </c>
-      <c r="K13" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -4129,10 +4129,10 @@
         <v>75</v>
       </c>
       <c r="F14" t="s">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="G14" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="H14" t="s">
         <v>18</v>
@@ -4141,10 +4141,10 @@
         <v>76</v>
       </c>
       <c r="J14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K14" t="s">
         <v>71</v>
-      </c>
-      <c r="K14" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -4164,10 +4164,10 @@
         <v>80</v>
       </c>
       <c r="F15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" t="s">
         <v>81</v>
-      </c>
-      <c r="G15" t="s">
-        <v>17</v>
       </c>
       <c r="H15" t="s">
         <v>18</v>
@@ -4176,10 +4176,10 @@
         <v>82</v>
       </c>
       <c r="J15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K15" t="s">
         <v>83</v>
-      </c>
-      <c r="K15" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -4199,10 +4199,10 @@
         <v>87</v>
       </c>
       <c r="F16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" t="s">
         <v>81</v>
-      </c>
-      <c r="G16" t="s">
-        <v>17</v>
       </c>
       <c r="H16" t="s">
         <v>18</v>
@@ -4211,10 +4211,10 @@
         <v>88</v>
       </c>
       <c r="J16" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" t="s">
         <v>83</v>
-      </c>
-      <c r="K16" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -4240,13 +4240,13 @@
         <v>94</v>
       </c>
       <c r="H17" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="I17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J17" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="K17" t="s">
         <v>97</v>
@@ -4275,13 +4275,13 @@
         <v>94</v>
       </c>
       <c r="H18" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="I18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J18" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="K18" t="s">
         <v>97</v>
@@ -4310,13 +4310,13 @@
         <v>94</v>
       </c>
       <c r="H19" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="I19" t="s">
         <v>105</v>
       </c>
       <c r="J19" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="K19" t="s">
         <v>97</v>
@@ -4345,13 +4345,13 @@
         <v>94</v>
       </c>
       <c r="H20" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="I20" t="s">
         <v>110</v>
       </c>
       <c r="J20" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="K20" t="s">
         <v>97</v>
@@ -4380,13 +4380,13 @@
         <v>94</v>
       </c>
       <c r="H21" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="I21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J21" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="K21" t="s">
         <v>97</v>
@@ -4409,22 +4409,22 @@
         <v>58</v>
       </c>
       <c r="F22" t="s">
+        <v>93</v>
+      </c>
+      <c r="G22" t="s">
         <v>117</v>
       </c>
-      <c r="G22" t="s">
-        <v>94</v>
-      </c>
       <c r="H22" t="s">
+        <v>95</v>
+      </c>
+      <c r="I22" t="s">
         <v>59</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>60</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>118</v>
-      </c>
-      <c r="K22" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -4444,22 +4444,22 @@
         <v>122</v>
       </c>
       <c r="F23" t="s">
+        <v>93</v>
+      </c>
+      <c r="G23" t="s">
         <v>117</v>
       </c>
-      <c r="G23" t="s">
-        <v>94</v>
-      </c>
       <c r="H23" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="I23" t="s">
         <v>123</v>
       </c>
       <c r="J23" t="s">
+        <v>60</v>
+      </c>
+      <c r="K23" t="s">
         <v>118</v>
-      </c>
-      <c r="K23" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -4479,22 +4479,22 @@
         <v>58</v>
       </c>
       <c r="F24" t="s">
+        <v>93</v>
+      </c>
+      <c r="G24" t="s">
         <v>117</v>
       </c>
-      <c r="G24" t="s">
-        <v>94</v>
-      </c>
       <c r="H24" t="s">
+        <v>95</v>
+      </c>
+      <c r="I24" t="s">
         <v>59</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>60</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>118</v>
-      </c>
-      <c r="K24" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -4514,22 +4514,22 @@
         <v>58</v>
       </c>
       <c r="F25" t="s">
+        <v>93</v>
+      </c>
+      <c r="G25" t="s">
         <v>117</v>
       </c>
-      <c r="G25" t="s">
-        <v>94</v>
-      </c>
       <c r="H25" t="s">
+        <v>95</v>
+      </c>
+      <c r="I25" t="s">
         <v>59</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>60</v>
       </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
         <v>118</v>
-      </c>
-      <c r="K25" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -4549,22 +4549,22 @@
         <v>58</v>
       </c>
       <c r="F26" t="s">
+        <v>93</v>
+      </c>
+      <c r="G26" t="s">
         <v>117</v>
       </c>
-      <c r="G26" t="s">
-        <v>94</v>
-      </c>
       <c r="H26" t="s">
+        <v>95</v>
+      </c>
+      <c r="I26" t="s">
         <v>59</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>60</v>
       </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
         <v>118</v>
-      </c>
-      <c r="K26" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -4584,22 +4584,22 @@
         <v>58</v>
       </c>
       <c r="F27" t="s">
+        <v>93</v>
+      </c>
+      <c r="G27" t="s">
         <v>117</v>
       </c>
-      <c r="G27" t="s">
-        <v>94</v>
-      </c>
       <c r="H27" t="s">
+        <v>95</v>
+      </c>
+      <c r="I27" t="s">
         <v>59</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>60</v>
       </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
         <v>118</v>
-      </c>
-      <c r="K27" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -4619,22 +4619,22 @@
         <v>58</v>
       </c>
       <c r="F28" t="s">
+        <v>93</v>
+      </c>
+      <c r="G28" t="s">
         <v>117</v>
       </c>
-      <c r="G28" t="s">
-        <v>94</v>
-      </c>
       <c r="H28" t="s">
+        <v>95</v>
+      </c>
+      <c r="I28" t="s">
         <v>59</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>60</v>
       </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>118</v>
-      </c>
-      <c r="K28" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -4654,22 +4654,22 @@
         <v>58</v>
       </c>
       <c r="F29" t="s">
+        <v>93</v>
+      </c>
+      <c r="G29" t="s">
         <v>117</v>
       </c>
-      <c r="G29" t="s">
-        <v>94</v>
-      </c>
       <c r="H29" t="s">
+        <v>95</v>
+      </c>
+      <c r="I29" t="s">
         <v>59</v>
       </c>
-      <c r="I29" t="s">
+      <c r="J29" t="s">
         <v>60</v>
       </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
         <v>118</v>
-      </c>
-      <c r="K29" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -4689,22 +4689,22 @@
         <v>92</v>
       </c>
       <c r="F30" t="s">
+        <v>93</v>
+      </c>
+      <c r="G30" t="s">
         <v>117</v>
       </c>
-      <c r="G30" t="s">
-        <v>94</v>
-      </c>
       <c r="H30" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="I30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J30" t="s">
+        <v>60</v>
+      </c>
+      <c r="K30" t="s">
         <v>118</v>
-      </c>
-      <c r="K30" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -4724,22 +4724,22 @@
         <v>58</v>
       </c>
       <c r="F31" t="s">
+        <v>93</v>
+      </c>
+      <c r="G31" t="s">
         <v>148</v>
       </c>
-      <c r="G31" t="s">
-        <v>94</v>
-      </c>
       <c r="H31" t="s">
+        <v>95</v>
+      </c>
+      <c r="I31" t="s">
         <v>59</v>
       </c>
-      <c r="I31" t="s">
+      <c r="J31" t="s">
         <v>60</v>
       </c>
-      <c r="J31" t="s">
+      <c r="K31" t="s">
         <v>149</v>
-      </c>
-      <c r="K31" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -4759,22 +4759,22 @@
         <v>58</v>
       </c>
       <c r="F32" t="s">
+        <v>93</v>
+      </c>
+      <c r="G32" t="s">
         <v>148</v>
       </c>
-      <c r="G32" t="s">
-        <v>94</v>
-      </c>
       <c r="H32" t="s">
+        <v>95</v>
+      </c>
+      <c r="I32" t="s">
         <v>59</v>
       </c>
-      <c r="I32" t="s">
+      <c r="J32" t="s">
         <v>60</v>
       </c>
-      <c r="J32" t="s">
+      <c r="K32" t="s">
         <v>149</v>
-      </c>
-      <c r="K32" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -4794,22 +4794,22 @@
         <v>58</v>
       </c>
       <c r="F33" t="s">
+        <v>93</v>
+      </c>
+      <c r="G33" t="s">
         <v>148</v>
       </c>
-      <c r="G33" t="s">
-        <v>94</v>
-      </c>
       <c r="H33" t="s">
+        <v>95</v>
+      </c>
+      <c r="I33" t="s">
         <v>59</v>
       </c>
-      <c r="I33" t="s">
+      <c r="J33" t="s">
         <v>60</v>
       </c>
-      <c r="J33" t="s">
+      <c r="K33" t="s">
         <v>149</v>
-      </c>
-      <c r="K33" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -4829,22 +4829,22 @@
         <v>58</v>
       </c>
       <c r="F34" t="s">
+        <v>93</v>
+      </c>
+      <c r="G34" t="s">
         <v>148</v>
       </c>
-      <c r="G34" t="s">
-        <v>94</v>
-      </c>
       <c r="H34" t="s">
+        <v>95</v>
+      </c>
+      <c r="I34" t="s">
         <v>59</v>
       </c>
-      <c r="I34" t="s">
+      <c r="J34" t="s">
         <v>60</v>
       </c>
-      <c r="J34" t="s">
+      <c r="K34" t="s">
         <v>149</v>
-      </c>
-      <c r="K34" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -4864,22 +4864,22 @@
         <v>58</v>
       </c>
       <c r="F35" t="s">
+        <v>93</v>
+      </c>
+      <c r="G35" t="s">
         <v>148</v>
       </c>
-      <c r="G35" t="s">
-        <v>94</v>
-      </c>
       <c r="H35" t="s">
+        <v>95</v>
+      </c>
+      <c r="I35" t="s">
         <v>59</v>
       </c>
-      <c r="I35" t="s">
+      <c r="J35" t="s">
         <v>60</v>
       </c>
-      <c r="J35" t="s">
+      <c r="K35" t="s">
         <v>149</v>
-      </c>
-      <c r="K35" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -4899,22 +4899,22 @@
         <v>104</v>
       </c>
       <c r="F36" t="s">
+        <v>93</v>
+      </c>
+      <c r="G36" t="s">
         <v>148</v>
       </c>
-      <c r="G36" t="s">
-        <v>94</v>
-      </c>
       <c r="H36" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="I36" t="s">
         <v>105</v>
       </c>
       <c r="J36" t="s">
+        <v>60</v>
+      </c>
+      <c r="K36" t="s">
         <v>149</v>
-      </c>
-      <c r="K36" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -4933,17 +4933,17 @@
       <c r="E37" t="s">
         <v>58</v>
       </c>
-      <c r="G37" t="s">
+      <c r="F37" t="s">
         <v>168</v>
       </c>
       <c r="H37" t="s">
+        <v>169</v>
+      </c>
+      <c r="I37" t="s">
         <v>59</v>
       </c>
-      <c r="I37" t="s">
+      <c r="J37" t="s">
         <v>60</v>
-      </c>
-      <c r="K37" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -4962,17 +4962,17 @@
       <c r="E38" t="s">
         <v>58</v>
       </c>
-      <c r="G38" t="s">
+      <c r="F38" t="s">
         <v>168</v>
       </c>
       <c r="H38" t="s">
+        <v>169</v>
+      </c>
+      <c r="I38" t="s">
         <v>59</v>
       </c>
-      <c r="I38" t="s">
+      <c r="J38" t="s">
         <v>60</v>
-      </c>
-      <c r="K38" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -4991,17 +4991,17 @@
       <c r="E39" t="s">
         <v>58</v>
       </c>
-      <c r="G39" t="s">
+      <c r="F39" t="s">
         <v>168</v>
       </c>
       <c r="H39" t="s">
+        <v>169</v>
+      </c>
+      <c r="I39" t="s">
         <v>59</v>
       </c>
-      <c r="I39" t="s">
+      <c r="J39" t="s">
         <v>60</v>
-      </c>
-      <c r="K39" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -5020,17 +5020,17 @@
       <c r="E40" t="s">
         <v>58</v>
       </c>
-      <c r="G40" t="s">
+      <c r="F40" t="s">
         <v>168</v>
       </c>
       <c r="H40" t="s">
+        <v>169</v>
+      </c>
+      <c r="I40" t="s">
         <v>59</v>
       </c>
-      <c r="I40" t="s">
+      <c r="J40" t="s">
         <v>60</v>
-      </c>
-      <c r="K40" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -5049,17 +5049,17 @@
       <c r="E41" t="s">
         <v>92</v>
       </c>
-      <c r="G41" t="s">
+      <c r="F41" t="s">
         <v>168</v>
       </c>
       <c r="H41" t="s">
-        <v>59</v>
+        <v>169</v>
       </c>
       <c r="I41" t="s">
-        <v>95</v>
-      </c>
-      <c r="K41" t="s">
-        <v>169</v>
+        <v>96</v>
+      </c>
+      <c r="J41" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -5078,17 +5078,17 @@
       <c r="E42" t="s">
         <v>104</v>
       </c>
-      <c r="G42" t="s">
+      <c r="F42" t="s">
         <v>168</v>
       </c>
       <c r="H42" t="s">
-        <v>59</v>
+        <v>169</v>
       </c>
       <c r="I42" t="s">
         <v>105</v>
       </c>
-      <c r="K42" t="s">
-        <v>169</v>
+      <c r="J42" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -5107,7 +5107,7 @@
       <c r="E43" t="s">
         <v>188</v>
       </c>
-      <c r="G43" t="s">
+      <c r="F43" t="s">
         <v>189</v>
       </c>
       <c r="H43" t="s">
@@ -5116,7 +5116,7 @@
       <c r="I43" t="s">
         <v>191</v>
       </c>
-      <c r="K43" t="s">
+      <c r="J43" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5136,17 +5136,17 @@
       <c r="E44" t="s">
         <v>196</v>
       </c>
-      <c r="G44" t="s">
+      <c r="F44" t="s">
         <v>189</v>
       </c>
       <c r="H44" t="s">
+        <v>190</v>
+      </c>
+      <c r="I44" t="s">
         <v>197</v>
       </c>
-      <c r="I44" t="s">
+      <c r="J44" t="s">
         <v>198</v>
-      </c>
-      <c r="K44" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -5165,7 +5165,7 @@
       <c r="E45" t="s">
         <v>188</v>
       </c>
-      <c r="G45" t="s">
+      <c r="F45" t="s">
         <v>189</v>
       </c>
       <c r="H45" t="s">
@@ -5174,7 +5174,7 @@
       <c r="I45" t="s">
         <v>191</v>
       </c>
-      <c r="K45" t="s">
+      <c r="J45" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5194,7 +5194,7 @@
       <c r="E46" t="s">
         <v>188</v>
       </c>
-      <c r="G46" t="s">
+      <c r="F46" t="s">
         <v>189</v>
       </c>
       <c r="H46" t="s">
@@ -5203,7 +5203,7 @@
       <c r="I46" t="s">
         <v>191</v>
       </c>
-      <c r="K46" t="s">
+      <c r="J46" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5223,17 +5223,17 @@
       <c r="E47" t="s">
         <v>208</v>
       </c>
-      <c r="G47" t="s">
+      <c r="F47" t="s">
         <v>189</v>
       </c>
       <c r="H47" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="I47" t="s">
         <v>209</v>
       </c>
-      <c r="K47" t="s">
-        <v>192</v>
+      <c r="J47" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -5252,7 +5252,7 @@
       <c r="E48" t="s">
         <v>188</v>
       </c>
-      <c r="G48" t="s">
+      <c r="F48" t="s">
         <v>189</v>
       </c>
       <c r="H48" t="s">
@@ -5261,7 +5261,7 @@
       <c r="I48" t="s">
         <v>191</v>
       </c>
-      <c r="K48" t="s">
+      <c r="J48" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       <c r="E49" t="s">
         <v>188</v>
       </c>
-      <c r="G49" t="s">
+      <c r="F49" t="s">
         <v>189</v>
       </c>
       <c r="H49" t="s">
@@ -5290,7 +5290,7 @@
       <c r="I49" t="s">
         <v>191</v>
       </c>
-      <c r="K49" t="s">
+      <c r="J49" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5310,17 +5310,17 @@
       <c r="E50" t="s">
         <v>208</v>
       </c>
-      <c r="G50" t="s">
+      <c r="F50" t="s">
         <v>189</v>
       </c>
       <c r="H50" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="I50" t="s">
         <v>209</v>
       </c>
-      <c r="K50" t="s">
-        <v>192</v>
+      <c r="J50" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -5339,7 +5339,7 @@
       <c r="E51" t="s">
         <v>188</v>
       </c>
-      <c r="G51" t="s">
+      <c r="F51" t="s">
         <v>189</v>
       </c>
       <c r="H51" t="s">
@@ -5348,7 +5348,7 @@
       <c r="I51" t="s">
         <v>191</v>
       </c>
-      <c r="K51" t="s">
+      <c r="J51" t="s">
         <v>192</v>
       </c>
     </row>
@@ -5368,17 +5368,17 @@
       <c r="E52" t="s">
         <v>225</v>
       </c>
-      <c r="G52" t="s">
+      <c r="F52" t="s">
         <v>189</v>
       </c>
       <c r="H52" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="I52" t="s">
         <v>226</v>
       </c>
-      <c r="K52" t="s">
-        <v>192</v>
+      <c r="J52" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -5397,17 +5397,17 @@
       <c r="E53" t="s">
         <v>15</v>
       </c>
-      <c r="G53" t="s">
+      <c r="F53" t="s">
         <v>189</v>
       </c>
       <c r="H53" t="s">
-        <v>18</v>
+        <v>190</v>
       </c>
       <c r="I53" t="s">
         <v>19</v>
       </c>
-      <c r="K53" t="s">
-        <v>192</v>
+      <c r="J53" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -5538,13 +5538,13 @@
         <v>235</v>
       </c>
       <c r="H57" t="s">
+        <v>236</v>
+      </c>
+      <c r="I57" t="s">
         <v>254</v>
       </c>
-      <c r="I57" t="s">
+      <c r="J57" t="s">
         <v>255</v>
-      </c>
-      <c r="J57" t="s">
-        <v>238</v>
       </c>
       <c r="K57" t="s">
         <v>239</v>
@@ -5739,7 +5739,7 @@
         <v>14</v>
       </c>
       <c r="E63" t="s">
-        <v>243</v>
+        <v>274</v>
       </c>
       <c r="F63" t="s">
         <v>234</v>
@@ -5751,7 +5751,7 @@
         <v>236</v>
       </c>
       <c r="I63" t="s">
-        <v>274</v>
+        <v>244</v>
       </c>
       <c r="J63" t="s">
         <v>238</v>
@@ -5774,7 +5774,7 @@
         <v>14</v>
       </c>
       <c r="E64" t="s">
-        <v>243</v>
+        <v>274</v>
       </c>
       <c r="F64" t="s">
         <v>234</v>
@@ -5786,7 +5786,7 @@
         <v>236</v>
       </c>
       <c r="I64" t="s">
-        <v>274</v>
+        <v>244</v>
       </c>
       <c r="J64" t="s">
         <v>238</v>
@@ -5914,7 +5914,7 @@
         <v>14</v>
       </c>
       <c r="E68" t="s">
-        <v>233</v>
+        <v>292</v>
       </c>
       <c r="F68" t="s">
         <v>234</v>
@@ -5926,7 +5926,7 @@
         <v>236</v>
       </c>
       <c r="I68" t="s">
-        <v>292</v>
+        <v>237</v>
       </c>
       <c r="J68" t="s">
         <v>238</v>
@@ -5949,7 +5949,7 @@
         <v>14</v>
       </c>
       <c r="E69" t="s">
-        <v>233</v>
+        <v>296</v>
       </c>
       <c r="F69" t="s">
         <v>234</v>
@@ -5961,7 +5961,7 @@
         <v>236</v>
       </c>
       <c r="I69" t="s">
-        <v>296</v>
+        <v>237</v>
       </c>
       <c r="J69" t="s">
         <v>238</v>
@@ -6098,13 +6098,13 @@
         <v>235</v>
       </c>
       <c r="H73" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="I73" t="s">
         <v>310</v>
       </c>
       <c r="J73" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="K73" t="s">
         <v>239</v>
@@ -6133,13 +6133,13 @@
         <v>235</v>
       </c>
       <c r="H74" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="I74" t="s">
         <v>315</v>
       </c>
       <c r="J74" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="K74" t="s">
         <v>239</v>
@@ -6168,13 +6168,13 @@
         <v>235</v>
       </c>
       <c r="H75" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="I75" t="s">
         <v>320</v>
       </c>
       <c r="J75" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="K75" t="s">
         <v>239</v>
@@ -6203,13 +6203,13 @@
         <v>235</v>
       </c>
       <c r="H76" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="I76" t="s">
         <v>310</v>
       </c>
       <c r="J76" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="K76" t="s">
         <v>239</v>
@@ -6238,13 +6238,13 @@
         <v>235</v>
       </c>
       <c r="H77" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="I77" t="s">
         <v>310</v>
       </c>
       <c r="J77" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="K77" t="s">
         <v>239</v>
@@ -6273,13 +6273,13 @@
         <v>235</v>
       </c>
       <c r="H78" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="I78" t="s">
         <v>315</v>
       </c>
       <c r="J78" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="K78" t="s">
         <v>239</v>
@@ -6305,13 +6305,13 @@
         <v>235</v>
       </c>
       <c r="H79" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="I79" t="s">
         <v>333</v>
       </c>
       <c r="J79" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="K79" t="s">
         <v>239</v>
@@ -6340,13 +6340,13 @@
         <v>235</v>
       </c>
       <c r="H80" t="s">
+        <v>236</v>
+      </c>
+      <c r="I80" t="s">
         <v>338</v>
       </c>
-      <c r="I80" t="s">
+      <c r="J80" t="s">
         <v>339</v>
-      </c>
-      <c r="J80" t="s">
-        <v>238</v>
       </c>
       <c r="K80" t="s">
         <v>239</v>
@@ -6375,13 +6375,13 @@
         <v>235</v>
       </c>
       <c r="H81" t="s">
+        <v>236</v>
+      </c>
+      <c r="I81" t="s">
         <v>338</v>
       </c>
-      <c r="I81" t="s">
+      <c r="J81" t="s">
         <v>339</v>
-      </c>
-      <c r="J81" t="s">
-        <v>238</v>
       </c>
       <c r="K81" t="s">
         <v>239</v>
@@ -6410,13 +6410,13 @@
         <v>235</v>
       </c>
       <c r="H82" t="s">
+        <v>236</v>
+      </c>
+      <c r="I82" t="s">
         <v>338</v>
       </c>
-      <c r="I82" t="s">
+      <c r="J82" t="s">
         <v>339</v>
-      </c>
-      <c r="J82" t="s">
-        <v>238</v>
       </c>
       <c r="K82" t="s">
         <v>239</v>
@@ -6436,7 +6436,7 @@
         <v>14</v>
       </c>
       <c r="E83" t="s">
-        <v>233</v>
+        <v>296</v>
       </c>
       <c r="F83" t="s">
         <v>234</v>
@@ -6448,7 +6448,7 @@
         <v>236</v>
       </c>
       <c r="I83" t="s">
-        <v>296</v>
+        <v>237</v>
       </c>
       <c r="J83" t="s">
         <v>238</v>
@@ -6506,7 +6506,7 @@
         <v>14</v>
       </c>
       <c r="E85" t="s">
-        <v>243</v>
+        <v>357</v>
       </c>
       <c r="F85" t="s">
         <v>234</v>
@@ -6518,7 +6518,7 @@
         <v>236</v>
       </c>
       <c r="I85" t="s">
-        <v>357</v>
+        <v>244</v>
       </c>
       <c r="J85" t="s">
         <v>238</v>
@@ -6550,13 +6550,13 @@
         <v>235</v>
       </c>
       <c r="H86" t="s">
-        <v>338</v>
+        <v>236</v>
       </c>
       <c r="I86" t="s">
         <v>362</v>
       </c>
       <c r="J86" t="s">
-        <v>238</v>
+        <v>339</v>
       </c>
       <c r="K86" t="s">
         <v>239</v>
@@ -6576,7 +6576,7 @@
         <v>14</v>
       </c>
       <c r="E87" t="s">
-        <v>243</v>
+        <v>357</v>
       </c>
       <c r="F87" t="s">
         <v>234</v>
@@ -6588,7 +6588,7 @@
         <v>236</v>
       </c>
       <c r="I87" t="s">
-        <v>357</v>
+        <v>244</v>
       </c>
       <c r="J87" t="s">
         <v>238</v>
@@ -6687,13 +6687,13 @@
         <v>235</v>
       </c>
       <c r="H90" t="s">
+        <v>236</v>
+      </c>
+      <c r="I90" t="s">
         <v>254</v>
       </c>
-      <c r="I90" t="s">
+      <c r="J90" t="s">
         <v>255</v>
-      </c>
-      <c r="J90" t="s">
-        <v>238</v>
       </c>
       <c r="K90" t="s">
         <v>239</v>
@@ -6722,13 +6722,13 @@
         <v>235</v>
       </c>
       <c r="H91" t="s">
+        <v>236</v>
+      </c>
+      <c r="I91" t="s">
         <v>378</v>
       </c>
-      <c r="I91" t="s">
+      <c r="J91" t="s">
         <v>379</v>
-      </c>
-      <c r="J91" t="s">
-        <v>238</v>
       </c>
       <c r="K91" t="s">
         <v>239</v>
@@ -6757,13 +6757,13 @@
         <v>235</v>
       </c>
       <c r="H92" t="s">
+        <v>236</v>
+      </c>
+      <c r="I92" t="s">
         <v>254</v>
       </c>
-      <c r="I92" t="s">
+      <c r="J92" t="s">
         <v>255</v>
-      </c>
-      <c r="J92" t="s">
-        <v>238</v>
       </c>
       <c r="K92" t="s">
         <v>239</v>
@@ -6827,13 +6827,13 @@
         <v>235</v>
       </c>
       <c r="H94" t="s">
+        <v>236</v>
+      </c>
+      <c r="I94" t="s">
         <v>254</v>
       </c>
-      <c r="I94" t="s">
+      <c r="J94" t="s">
         <v>255</v>
-      </c>
-      <c r="J94" t="s">
-        <v>238</v>
       </c>
       <c r="K94" t="s">
         <v>239</v>
@@ -6891,22 +6891,22 @@
         <v>253</v>
       </c>
       <c r="F96" t="s">
+        <v>234</v>
+      </c>
+      <c r="G96" t="s">
         <v>397</v>
       </c>
-      <c r="G96" t="s">
-        <v>235</v>
-      </c>
       <c r="H96" t="s">
+        <v>236</v>
+      </c>
+      <c r="I96" t="s">
         <v>254</v>
       </c>
-      <c r="I96" t="s">
+      <c r="J96" t="s">
         <v>255</v>
       </c>
-      <c r="J96" t="s">
+      <c r="K96" t="s">
         <v>398</v>
-      </c>
-      <c r="K96" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -6926,22 +6926,22 @@
         <v>253</v>
       </c>
       <c r="F97" t="s">
+        <v>234</v>
+      </c>
+      <c r="G97" t="s">
         <v>397</v>
       </c>
-      <c r="G97" t="s">
-        <v>235</v>
-      </c>
       <c r="H97" t="s">
+        <v>236</v>
+      </c>
+      <c r="I97" t="s">
         <v>254</v>
       </c>
-      <c r="I97" t="s">
+      <c r="J97" t="s">
         <v>255</v>
       </c>
-      <c r="J97" t="s">
+      <c r="K97" t="s">
         <v>398</v>
-      </c>
-      <c r="K97" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -6961,22 +6961,22 @@
         <v>405</v>
       </c>
       <c r="F98" t="s">
+        <v>234</v>
+      </c>
+      <c r="G98" t="s">
         <v>397</v>
       </c>
-      <c r="G98" t="s">
-        <v>235</v>
-      </c>
       <c r="H98" t="s">
+        <v>236</v>
+      </c>
+      <c r="I98" t="s">
         <v>406</v>
       </c>
-      <c r="I98" t="s">
+      <c r="J98" t="s">
         <v>407</v>
       </c>
-      <c r="J98" t="s">
+      <c r="K98" t="s">
         <v>398</v>
-      </c>
-      <c r="K98" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -6996,22 +6996,22 @@
         <v>253</v>
       </c>
       <c r="F99" t="s">
+        <v>234</v>
+      </c>
+      <c r="G99" t="s">
         <v>397</v>
       </c>
-      <c r="G99" t="s">
-        <v>235</v>
-      </c>
       <c r="H99" t="s">
+        <v>236</v>
+      </c>
+      <c r="I99" t="s">
         <v>254</v>
       </c>
-      <c r="I99" t="s">
+      <c r="J99" t="s">
         <v>255</v>
       </c>
-      <c r="J99" t="s">
+      <c r="K99" t="s">
         <v>398</v>
-      </c>
-      <c r="K99" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -7031,22 +7031,22 @@
         <v>319</v>
       </c>
       <c r="F100" t="s">
+        <v>234</v>
+      </c>
+      <c r="G100" t="s">
         <v>397</v>
       </c>
-      <c r="G100" t="s">
-        <v>235</v>
-      </c>
       <c r="H100" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="I100" t="s">
         <v>320</v>
       </c>
       <c r="J100" t="s">
+        <v>255</v>
+      </c>
+      <c r="K100" t="s">
         <v>398</v>
-      </c>
-      <c r="K100" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -7066,22 +7066,22 @@
         <v>253</v>
       </c>
       <c r="F101" t="s">
+        <v>234</v>
+      </c>
+      <c r="G101" t="s">
         <v>397</v>
       </c>
-      <c r="G101" t="s">
-        <v>235</v>
-      </c>
       <c r="H101" t="s">
+        <v>236</v>
+      </c>
+      <c r="I101" t="s">
         <v>254</v>
       </c>
-      <c r="I101" t="s">
+      <c r="J101" t="s">
         <v>255</v>
       </c>
-      <c r="J101" t="s">
+      <c r="K101" t="s">
         <v>398</v>
-      </c>
-      <c r="K101" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -7100,17 +7100,17 @@
       <c r="E102" t="s">
         <v>420</v>
       </c>
-      <c r="G102" t="s">
+      <c r="F102" t="s">
         <v>421</v>
       </c>
       <c r="H102" t="s">
-        <v>378</v>
+        <v>422</v>
       </c>
       <c r="I102" t="s">
-        <v>422</v>
-      </c>
-      <c r="K102" t="s">
         <v>423</v>
+      </c>
+      <c r="J102" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -7129,17 +7129,17 @@
       <c r="E103" t="s">
         <v>420</v>
       </c>
-      <c r="G103" t="s">
+      <c r="F103" t="s">
         <v>421</v>
       </c>
       <c r="H103" t="s">
-        <v>378</v>
+        <v>422</v>
       </c>
       <c r="I103" t="s">
-        <v>422</v>
-      </c>
-      <c r="K103" t="s">
         <v>423</v>
+      </c>
+      <c r="J103" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -7158,17 +7158,17 @@
       <c r="E104" t="s">
         <v>420</v>
       </c>
-      <c r="G104" t="s">
+      <c r="F104" t="s">
         <v>421</v>
       </c>
       <c r="H104" t="s">
-        <v>378</v>
+        <v>422</v>
       </c>
       <c r="I104" t="s">
-        <v>422</v>
-      </c>
-      <c r="K104" t="s">
         <v>423</v>
+      </c>
+      <c r="J104" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -7187,17 +7187,17 @@
       <c r="E105" t="s">
         <v>433</v>
       </c>
-      <c r="G105" t="s">
+      <c r="F105" t="s">
         <v>421</v>
       </c>
       <c r="H105" t="s">
-        <v>378</v>
+        <v>422</v>
       </c>
       <c r="I105" t="s">
         <v>434</v>
       </c>
-      <c r="K105" t="s">
-        <v>423</v>
+      <c r="J105" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -7216,17 +7216,17 @@
       <c r="E106" t="s">
         <v>420</v>
       </c>
-      <c r="G106" t="s">
+      <c r="F106" t="s">
         <v>421</v>
       </c>
       <c r="H106" t="s">
-        <v>378</v>
+        <v>422</v>
       </c>
       <c r="I106" t="s">
-        <v>422</v>
-      </c>
-      <c r="K106" t="s">
         <v>423</v>
+      </c>
+      <c r="J106" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -7245,17 +7245,17 @@
       <c r="E107" t="s">
         <v>377</v>
       </c>
-      <c r="G107" t="s">
+      <c r="F107" t="s">
         <v>421</v>
       </c>
       <c r="H107" t="s">
+        <v>422</v>
+      </c>
+      <c r="I107" t="s">
         <v>378</v>
       </c>
-      <c r="I107" t="s">
+      <c r="J107" t="s">
         <v>379</v>
-      </c>
-      <c r="K107" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -7274,17 +7274,17 @@
       <c r="E108" t="s">
         <v>444</v>
       </c>
-      <c r="G108" t="s">
+      <c r="F108" t="s">
         <v>421</v>
       </c>
       <c r="H108" t="s">
-        <v>378</v>
+        <v>422</v>
       </c>
       <c r="I108" t="s">
         <v>445</v>
       </c>
-      <c r="K108" t="s">
-        <v>423</v>
+      <c r="J108" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -7303,17 +7303,17 @@
       <c r="E109" t="s">
         <v>449</v>
       </c>
-      <c r="G109" t="s">
+      <c r="F109" t="s">
         <v>421</v>
       </c>
       <c r="H109" t="s">
-        <v>190</v>
+        <v>422</v>
       </c>
       <c r="I109" t="s">
         <v>450</v>
       </c>
-      <c r="K109" t="s">
-        <v>423</v>
+      <c r="J109" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -7332,17 +7332,17 @@
       <c r="E110" t="s">
         <v>454</v>
       </c>
-      <c r="G110" t="s">
+      <c r="F110" t="s">
         <v>421</v>
       </c>
       <c r="H110" t="s">
-        <v>190</v>
+        <v>422</v>
       </c>
       <c r="I110" t="s">
         <v>455</v>
       </c>
-      <c r="K110" t="s">
-        <v>423</v>
+      <c r="J110" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -7361,17 +7361,17 @@
       <c r="E111" t="s">
         <v>420</v>
       </c>
-      <c r="G111" t="s">
+      <c r="F111" t="s">
         <v>421</v>
       </c>
       <c r="H111" t="s">
-        <v>378</v>
+        <v>422</v>
       </c>
       <c r="I111" t="s">
-        <v>422</v>
-      </c>
-      <c r="K111" t="s">
         <v>423</v>
+      </c>
+      <c r="J111" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -7390,20 +7390,20 @@
       <c r="E112" t="s">
         <v>462</v>
       </c>
-      <c r="G112" t="s">
+      <c r="F112" t="s">
         <v>421</v>
       </c>
       <c r="H112" t="s">
+        <v>422</v>
+      </c>
+      <c r="I112" t="s">
         <v>463</v>
       </c>
-      <c r="I112" t="s">
+      <c r="J112" t="s">
         <v>464</v>
       </c>
-      <c r="K112" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11">
+    </row>
+    <row r="113" spans="1:10">
       <c r="A113" t="s">
         <v>465</v>
       </c>
@@ -7417,22 +7417,22 @@
         <v>14</v>
       </c>
       <c r="E113" t="s">
-        <v>233</v>
-      </c>
-      <c r="G113" t="s">
+        <v>296</v>
+      </c>
+      <c r="F113" t="s">
         <v>421</v>
       </c>
       <c r="H113" t="s">
-        <v>236</v>
+        <v>422</v>
       </c>
       <c r="I113" t="s">
-        <v>296</v>
-      </c>
-      <c r="K113" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11">
+        <v>237</v>
+      </c>
+      <c r="J113" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10">
       <c r="A114" t="s">
         <v>468</v>
       </c>
@@ -7448,20 +7448,20 @@
       <c r="E114" t="s">
         <v>314</v>
       </c>
-      <c r="G114" t="s">
+      <c r="F114" t="s">
         <v>421</v>
       </c>
       <c r="H114" t="s">
-        <v>254</v>
+        <v>422</v>
       </c>
       <c r="I114" t="s">
         <v>315</v>
       </c>
-      <c r="K114" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11">
+      <c r="J114" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10">
       <c r="A115" t="s">
         <v>471</v>
       </c>
@@ -7477,20 +7477,20 @@
       <c r="E115" t="s">
         <v>377</v>
       </c>
-      <c r="G115" t="s">
+      <c r="F115" t="s">
         <v>421</v>
       </c>
       <c r="H115" t="s">
+        <v>422</v>
+      </c>
+      <c r="I115" t="s">
         <v>378</v>
       </c>
-      <c r="I115" t="s">
+      <c r="J115" t="s">
         <v>379</v>
       </c>
-      <c r="K115" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11">
+    </row>
+    <row r="116" spans="1:10">
       <c r="A116" t="s">
         <v>474</v>
       </c>
@@ -7503,20 +7503,20 @@
       <c r="E116" t="s">
         <v>476</v>
       </c>
-      <c r="G116" t="s">
+      <c r="F116" t="s">
         <v>421</v>
       </c>
       <c r="H116" t="s">
-        <v>463</v>
+        <v>422</v>
       </c>
       <c r="I116" t="s">
         <v>477</v>
       </c>
-      <c r="K116" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11">
+      <c r="J116" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10">
       <c r="A117" t="s">
         <v>478</v>
       </c>
@@ -7529,20 +7529,20 @@
       <c r="E117" t="s">
         <v>462</v>
       </c>
-      <c r="G117" t="s">
+      <c r="F117" t="s">
         <v>421</v>
       </c>
       <c r="H117" t="s">
+        <v>422</v>
+      </c>
+      <c r="I117" t="s">
         <v>463</v>
       </c>
-      <c r="I117" t="s">
+      <c r="J117" t="s">
         <v>464</v>
       </c>
-      <c r="K117" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11">
+    </row>
+    <row r="118" spans="1:10">
       <c r="A118" t="s">
         <v>480</v>
       </c>
@@ -7556,22 +7556,22 @@
         <v>14</v>
       </c>
       <c r="E118" t="s">
-        <v>337</v>
-      </c>
-      <c r="G118" t="s">
+        <v>483</v>
+      </c>
+      <c r="F118" t="s">
         <v>421</v>
       </c>
       <c r="H118" t="s">
+        <v>422</v>
+      </c>
+      <c r="I118" t="s">
         <v>338</v>
       </c>
-      <c r="I118" t="s">
-        <v>483</v>
-      </c>
-      <c r="K118" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11">
+      <c r="J118" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10">
       <c r="A119" t="s">
         <v>484</v>
       </c>
@@ -7587,20 +7587,20 @@
       <c r="E119" t="s">
         <v>377</v>
       </c>
-      <c r="G119" t="s">
+      <c r="F119" t="s">
         <v>421</v>
       </c>
       <c r="H119" t="s">
+        <v>422</v>
+      </c>
+      <c r="I119" t="s">
         <v>378</v>
       </c>
-      <c r="I119" t="s">
+      <c r="J119" t="s">
         <v>379</v>
       </c>
-      <c r="K119" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11">
+    </row>
+    <row r="120" spans="1:10">
       <c r="A120" t="s">
         <v>487</v>
       </c>
@@ -7616,20 +7616,20 @@
       <c r="E120" t="s">
         <v>352</v>
       </c>
-      <c r="G120" t="s">
+      <c r="F120" t="s">
         <v>490</v>
       </c>
       <c r="H120" t="s">
-        <v>236</v>
+        <v>491</v>
       </c>
       <c r="I120" t="s">
         <v>353</v>
       </c>
-      <c r="K120" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11">
+      <c r="J120" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10">
       <c r="A121" t="s">
         <v>492</v>
       </c>
@@ -7643,22 +7643,22 @@
         <v>14</v>
       </c>
       <c r="E121" t="s">
-        <v>233</v>
-      </c>
-      <c r="G121" t="s">
+        <v>296</v>
+      </c>
+      <c r="F121" t="s">
         <v>490</v>
       </c>
       <c r="H121" t="s">
-        <v>236</v>
+        <v>491</v>
       </c>
       <c r="I121" t="s">
-        <v>296</v>
-      </c>
-      <c r="K121" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11">
+        <v>237</v>
+      </c>
+      <c r="J121" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10">
       <c r="A122" t="s">
         <v>495</v>
       </c>
@@ -7674,20 +7674,20 @@
       <c r="E122" t="s">
         <v>352</v>
       </c>
-      <c r="G122" t="s">
+      <c r="F122" t="s">
         <v>490</v>
       </c>
       <c r="H122" t="s">
-        <v>236</v>
+        <v>491</v>
       </c>
       <c r="I122" t="s">
         <v>353</v>
       </c>
-      <c r="K122" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11">
+      <c r="J122" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10">
       <c r="A123" t="s">
         <v>498</v>
       </c>
@@ -7703,20 +7703,20 @@
       <c r="E123" t="s">
         <v>352</v>
       </c>
-      <c r="G123" t="s">
+      <c r="F123" t="s">
         <v>490</v>
       </c>
       <c r="H123" t="s">
-        <v>236</v>
+        <v>491</v>
       </c>
       <c r="I123" t="s">
         <v>353</v>
       </c>
-      <c r="K123" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11">
+      <c r="J123" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10">
       <c r="A124" t="s">
         <v>501</v>
       </c>
@@ -7732,20 +7732,20 @@
       <c r="E124" t="s">
         <v>504</v>
       </c>
-      <c r="G124" t="s">
+      <c r="F124" t="s">
         <v>490</v>
       </c>
       <c r="H124" t="s">
-        <v>338</v>
+        <v>491</v>
       </c>
       <c r="I124" t="s">
         <v>505</v>
       </c>
-      <c r="K124" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11">
+      <c r="J124" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10">
       <c r="A125" t="s">
         <v>506</v>
       </c>
@@ -7761,20 +7761,20 @@
       <c r="E125" t="s">
         <v>504</v>
       </c>
-      <c r="G125" t="s">
+      <c r="F125" t="s">
         <v>490</v>
       </c>
       <c r="H125" t="s">
-        <v>338</v>
+        <v>491</v>
       </c>
       <c r="I125" t="s">
         <v>505</v>
       </c>
-      <c r="K125" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11">
+      <c r="J125" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10">
       <c r="A126" t="s">
         <v>509</v>
       </c>
@@ -7790,20 +7790,20 @@
       <c r="E126" t="s">
         <v>504</v>
       </c>
-      <c r="G126" t="s">
+      <c r="F126" t="s">
         <v>490</v>
       </c>
       <c r="H126" t="s">
-        <v>338</v>
+        <v>491</v>
       </c>
       <c r="I126" t="s">
         <v>505</v>
       </c>
-      <c r="K126" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11">
+      <c r="J126" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10">
       <c r="A127" t="s">
         <v>512</v>
       </c>
@@ -7819,20 +7819,20 @@
       <c r="E127" t="s">
         <v>504</v>
       </c>
-      <c r="G127" t="s">
+      <c r="F127" t="s">
         <v>490</v>
       </c>
       <c r="H127" t="s">
-        <v>338</v>
+        <v>491</v>
       </c>
       <c r="I127" t="s">
         <v>505</v>
       </c>
-      <c r="K127" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11">
+      <c r="J127" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10">
       <c r="A128" t="s">
         <v>515</v>
       </c>
@@ -7848,17 +7848,17 @@
       <c r="E128" t="s">
         <v>504</v>
       </c>
-      <c r="G128" t="s">
+      <c r="F128" t="s">
         <v>490</v>
       </c>
       <c r="H128" t="s">
-        <v>338</v>
+        <v>491</v>
       </c>
       <c r="I128" t="s">
         <v>505</v>
       </c>
-      <c r="K128" t="s">
-        <v>491</v>
+      <c r="J128" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -7875,19 +7875,19 @@
         <v>14</v>
       </c>
       <c r="E129" t="s">
-        <v>504</v>
-      </c>
-      <c r="G129" t="s">
+        <v>521</v>
+      </c>
+      <c r="F129" t="s">
         <v>490</v>
       </c>
       <c r="H129" t="s">
-        <v>338</v>
+        <v>491</v>
       </c>
       <c r="I129" t="s">
-        <v>521</v>
-      </c>
-      <c r="K129" t="s">
-        <v>491</v>
+        <v>505</v>
+      </c>
+      <c r="J129" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -7904,19 +7904,19 @@
         <v>14</v>
       </c>
       <c r="E130" t="s">
-        <v>504</v>
-      </c>
-      <c r="G130" t="s">
+        <v>525</v>
+      </c>
+      <c r="F130" t="s">
         <v>490</v>
       </c>
       <c r="H130" t="s">
-        <v>338</v>
+        <v>491</v>
       </c>
       <c r="I130" t="s">
-        <v>525</v>
-      </c>
-      <c r="K130" t="s">
-        <v>491</v>
+        <v>505</v>
+      </c>
+      <c r="J130" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="131" spans="1:11">
@@ -7933,19 +7933,19 @@
         <v>14</v>
       </c>
       <c r="E131" t="s">
-        <v>504</v>
-      </c>
-      <c r="G131" t="s">
+        <v>529</v>
+      </c>
+      <c r="F131" t="s">
         <v>490</v>
       </c>
       <c r="H131" t="s">
-        <v>338</v>
+        <v>491</v>
       </c>
       <c r="I131" t="s">
-        <v>529</v>
-      </c>
-      <c r="K131" t="s">
-        <v>491</v>
+        <v>505</v>
+      </c>
+      <c r="J131" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -7964,17 +7964,17 @@
       <c r="E132" t="s">
         <v>533</v>
       </c>
-      <c r="G132" t="s">
+      <c r="F132" t="s">
         <v>490</v>
       </c>
       <c r="H132" t="s">
-        <v>338</v>
+        <v>491</v>
       </c>
       <c r="I132" t="s">
         <v>534</v>
       </c>
-      <c r="K132" t="s">
-        <v>491</v>
+      <c r="J132" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -7990,17 +7990,17 @@
       <c r="E133" t="s">
         <v>392</v>
       </c>
-      <c r="G133" t="s">
+      <c r="F133" t="s">
         <v>490</v>
       </c>
       <c r="H133" t="s">
-        <v>236</v>
+        <v>491</v>
       </c>
       <c r="I133" t="s">
         <v>393</v>
       </c>
-      <c r="K133" t="s">
-        <v>491</v>
+      <c r="J133" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -8019,17 +8019,17 @@
       <c r="E134" t="s">
         <v>361</v>
       </c>
-      <c r="G134" t="s">
+      <c r="F134" t="s">
         <v>540</v>
       </c>
       <c r="H134" t="s">
-        <v>338</v>
+        <v>541</v>
       </c>
       <c r="I134" t="s">
         <v>362</v>
       </c>
-      <c r="K134" t="s">
-        <v>541</v>
+      <c r="J134" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -8045,17 +8045,17 @@
       <c r="E135" t="s">
         <v>361</v>
       </c>
-      <c r="G135" t="s">
+      <c r="F135" t="s">
         <v>540</v>
       </c>
       <c r="H135" t="s">
-        <v>338</v>
+        <v>541</v>
       </c>
       <c r="I135" t="s">
         <v>362</v>
       </c>
-      <c r="K135" t="s">
-        <v>541</v>
+      <c r="J135" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="136" spans="1:11">
@@ -8074,17 +8074,17 @@
       <c r="E136" t="s">
         <v>361</v>
       </c>
-      <c r="G136" t="s">
+      <c r="F136" t="s">
         <v>540</v>
       </c>
       <c r="H136" t="s">
-        <v>338</v>
+        <v>541</v>
       </c>
       <c r="I136" t="s">
         <v>362</v>
       </c>
-      <c r="K136" t="s">
-        <v>541</v>
+      <c r="J136" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -8103,17 +8103,17 @@
       <c r="E137" t="s">
         <v>361</v>
       </c>
-      <c r="G137" t="s">
+      <c r="F137" t="s">
         <v>540</v>
       </c>
       <c r="H137" t="s">
-        <v>338</v>
+        <v>541</v>
       </c>
       <c r="I137" t="s">
         <v>362</v>
       </c>
-      <c r="K137" t="s">
-        <v>541</v>
+      <c r="J137" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -8132,17 +8132,17 @@
       <c r="E138" t="s">
         <v>361</v>
       </c>
-      <c r="G138" t="s">
+      <c r="F138" t="s">
         <v>540</v>
       </c>
       <c r="H138" t="s">
-        <v>338</v>
+        <v>541</v>
       </c>
       <c r="I138" t="s">
         <v>362</v>
       </c>
-      <c r="K138" t="s">
-        <v>541</v>
+      <c r="J138" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -8161,17 +8161,17 @@
       <c r="E139" t="s">
         <v>556</v>
       </c>
-      <c r="G139" t="s">
+      <c r="F139" t="s">
         <v>540</v>
       </c>
       <c r="H139" t="s">
-        <v>463</v>
+        <v>541</v>
       </c>
       <c r="I139" t="s">
         <v>557</v>
       </c>
-      <c r="K139" t="s">
-        <v>541</v>
+      <c r="J139" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -8190,17 +8190,17 @@
       <c r="E140" t="s">
         <v>361</v>
       </c>
-      <c r="G140" t="s">
+      <c r="F140" t="s">
         <v>540</v>
       </c>
       <c r="H140" t="s">
-        <v>338</v>
+        <v>541</v>
       </c>
       <c r="I140" t="s">
         <v>362</v>
       </c>
-      <c r="K140" t="s">
-        <v>541</v>
+      <c r="J140" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -8226,13 +8226,13 @@
         <v>566</v>
       </c>
       <c r="H141" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I141" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J141" t="s">
-        <v>568</v>
+        <v>339</v>
       </c>
       <c r="K141" t="s">
         <v>569</v>
@@ -8258,13 +8258,13 @@
         <v>566</v>
       </c>
       <c r="H142" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I142" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J142" t="s">
-        <v>568</v>
+        <v>339</v>
       </c>
       <c r="K142" t="s">
         <v>569</v>
@@ -8293,13 +8293,13 @@
         <v>566</v>
       </c>
       <c r="H143" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I143" t="s">
         <v>576</v>
       </c>
       <c r="J143" t="s">
-        <v>568</v>
+        <v>339</v>
       </c>
       <c r="K143" t="s">
         <v>569</v>
@@ -8328,13 +8328,13 @@
         <v>566</v>
       </c>
       <c r="H144" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I144" t="s">
         <v>576</v>
       </c>
       <c r="J144" t="s">
-        <v>568</v>
+        <v>339</v>
       </c>
       <c r="K144" t="s">
         <v>569</v>
@@ -8363,13 +8363,13 @@
         <v>566</v>
       </c>
       <c r="H145" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I145" t="s">
         <v>576</v>
       </c>
       <c r="J145" t="s">
-        <v>568</v>
+        <v>339</v>
       </c>
       <c r="K145" t="s">
         <v>569</v>
@@ -8398,13 +8398,13 @@
         <v>566</v>
       </c>
       <c r="H146" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I146" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J146" t="s">
-        <v>568</v>
+        <v>339</v>
       </c>
       <c r="K146" t="s">
         <v>569</v>
@@ -8427,22 +8427,22 @@
         <v>564</v>
       </c>
       <c r="F147" t="s">
+        <v>565</v>
+      </c>
+      <c r="G147" t="s">
         <v>589</v>
       </c>
-      <c r="G147" t="s">
-        <v>566</v>
-      </c>
       <c r="H147" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I147" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J147" t="s">
+        <v>339</v>
+      </c>
+      <c r="K147" t="s">
         <v>590</v>
-      </c>
-      <c r="K147" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="148" spans="1:11">
@@ -8462,22 +8462,22 @@
         <v>564</v>
       </c>
       <c r="F148" t="s">
+        <v>565</v>
+      </c>
+      <c r="G148" t="s">
         <v>589</v>
       </c>
-      <c r="G148" t="s">
-        <v>566</v>
-      </c>
       <c r="H148" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I148" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J148" t="s">
+        <v>339</v>
+      </c>
+      <c r="K148" t="s">
         <v>590</v>
-      </c>
-      <c r="K148" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -8497,22 +8497,22 @@
         <v>564</v>
       </c>
       <c r="F149" t="s">
+        <v>565</v>
+      </c>
+      <c r="G149" t="s">
         <v>589</v>
       </c>
-      <c r="G149" t="s">
-        <v>566</v>
-      </c>
       <c r="H149" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I149" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J149" t="s">
+        <v>339</v>
+      </c>
+      <c r="K149" t="s">
         <v>590</v>
-      </c>
-      <c r="K149" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -8532,22 +8532,22 @@
         <v>564</v>
       </c>
       <c r="F150" t="s">
+        <v>565</v>
+      </c>
+      <c r="G150" t="s">
         <v>589</v>
       </c>
-      <c r="G150" t="s">
-        <v>566</v>
-      </c>
       <c r="H150" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I150" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J150" t="s">
+        <v>339</v>
+      </c>
+      <c r="K150" t="s">
         <v>590</v>
-      </c>
-      <c r="K150" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -8567,22 +8567,22 @@
         <v>564</v>
       </c>
       <c r="F151" t="s">
+        <v>565</v>
+      </c>
+      <c r="G151" t="s">
         <v>589</v>
       </c>
-      <c r="G151" t="s">
-        <v>566</v>
-      </c>
       <c r="H151" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I151" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J151" t="s">
+        <v>339</v>
+      </c>
+      <c r="K151" t="s">
         <v>590</v>
-      </c>
-      <c r="K151" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -8602,22 +8602,22 @@
         <v>564</v>
       </c>
       <c r="F152" t="s">
+        <v>565</v>
+      </c>
+      <c r="G152" t="s">
         <v>589</v>
       </c>
-      <c r="G152" t="s">
-        <v>566</v>
-      </c>
       <c r="H152" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I152" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J152" t="s">
+        <v>339</v>
+      </c>
+      <c r="K152" t="s">
         <v>590</v>
-      </c>
-      <c r="K152" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -8637,22 +8637,22 @@
         <v>564</v>
       </c>
       <c r="F153" t="s">
+        <v>565</v>
+      </c>
+      <c r="G153" t="s">
         <v>589</v>
       </c>
-      <c r="G153" t="s">
-        <v>566</v>
-      </c>
       <c r="H153" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I153" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J153" t="s">
+        <v>339</v>
+      </c>
+      <c r="K153" t="s">
         <v>590</v>
-      </c>
-      <c r="K153" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -8672,22 +8672,22 @@
         <v>564</v>
       </c>
       <c r="F154" t="s">
+        <v>565</v>
+      </c>
+      <c r="G154" t="s">
         <v>589</v>
       </c>
-      <c r="G154" t="s">
-        <v>566</v>
-      </c>
       <c r="H154" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I154" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J154" t="s">
+        <v>339</v>
+      </c>
+      <c r="K154" t="s">
         <v>590</v>
-      </c>
-      <c r="K154" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -8707,22 +8707,22 @@
         <v>564</v>
       </c>
       <c r="F155" t="s">
+        <v>565</v>
+      </c>
+      <c r="G155" t="s">
         <v>589</v>
       </c>
-      <c r="G155" t="s">
-        <v>566</v>
-      </c>
       <c r="H155" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I155" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J155" t="s">
+        <v>339</v>
+      </c>
+      <c r="K155" t="s">
         <v>590</v>
-      </c>
-      <c r="K155" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -8742,22 +8742,22 @@
         <v>564</v>
       </c>
       <c r="F156" t="s">
+        <v>565</v>
+      </c>
+      <c r="G156" t="s">
         <v>618</v>
       </c>
-      <c r="G156" t="s">
-        <v>566</v>
-      </c>
       <c r="H156" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I156" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J156" t="s">
+        <v>339</v>
+      </c>
+      <c r="K156" t="s">
         <v>619</v>
-      </c>
-      <c r="K156" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -8774,25 +8774,25 @@
         <v>14</v>
       </c>
       <c r="E157" t="s">
-        <v>564</v>
+        <v>623</v>
       </c>
       <c r="F157" t="s">
+        <v>565</v>
+      </c>
+      <c r="G157" t="s">
         <v>618</v>
       </c>
-      <c r="G157" t="s">
-        <v>566</v>
-      </c>
       <c r="H157" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I157" t="s">
-        <v>623</v>
+        <v>568</v>
       </c>
       <c r="J157" t="s">
+        <v>339</v>
+      </c>
+      <c r="K157" t="s">
         <v>619</v>
-      </c>
-      <c r="K157" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -8812,22 +8812,22 @@
         <v>564</v>
       </c>
       <c r="F158" t="s">
+        <v>565</v>
+      </c>
+      <c r="G158" t="s">
         <v>618</v>
       </c>
-      <c r="G158" t="s">
-        <v>566</v>
-      </c>
       <c r="H158" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I158" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J158" t="s">
+        <v>339</v>
+      </c>
+      <c r="K158" t="s">
         <v>619</v>
-      </c>
-      <c r="K158" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -8847,22 +8847,22 @@
         <v>564</v>
       </c>
       <c r="F159" t="s">
+        <v>565</v>
+      </c>
+      <c r="G159" t="s">
         <v>618</v>
       </c>
-      <c r="G159" t="s">
-        <v>566</v>
-      </c>
       <c r="H159" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I159" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J159" t="s">
+        <v>339</v>
+      </c>
+      <c r="K159" t="s">
         <v>619</v>
-      </c>
-      <c r="K159" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="160" spans="1:11">
@@ -8882,22 +8882,22 @@
         <v>564</v>
       </c>
       <c r="F160" t="s">
+        <v>565</v>
+      </c>
+      <c r="G160" t="s">
         <v>618</v>
       </c>
-      <c r="G160" t="s">
-        <v>566</v>
-      </c>
       <c r="H160" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I160" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J160" t="s">
+        <v>339</v>
+      </c>
+      <c r="K160" t="s">
         <v>619</v>
-      </c>
-      <c r="K160" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="161" spans="1:11">
@@ -8917,22 +8917,22 @@
         <v>564</v>
       </c>
       <c r="F161" t="s">
+        <v>565</v>
+      </c>
+      <c r="G161" t="s">
         <v>618</v>
       </c>
-      <c r="G161" t="s">
-        <v>566</v>
-      </c>
       <c r="H161" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I161" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J161" t="s">
+        <v>339</v>
+      </c>
+      <c r="K161" t="s">
         <v>619</v>
-      </c>
-      <c r="K161" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -8952,22 +8952,22 @@
         <v>564</v>
       </c>
       <c r="F162" t="s">
+        <v>565</v>
+      </c>
+      <c r="G162" t="s">
         <v>639</v>
       </c>
-      <c r="G162" t="s">
-        <v>566</v>
-      </c>
       <c r="H162" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I162" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J162" t="s">
+        <v>339</v>
+      </c>
+      <c r="K162" t="s">
         <v>640</v>
-      </c>
-      <c r="K162" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="163" spans="1:11">
@@ -8984,25 +8984,25 @@
         <v>14</v>
       </c>
       <c r="E163" t="s">
-        <v>564</v>
+        <v>644</v>
       </c>
       <c r="F163" t="s">
-        <v>644</v>
+        <v>565</v>
       </c>
       <c r="G163" t="s">
-        <v>566</v>
+        <v>642</v>
       </c>
       <c r="H163" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I163" t="s">
+        <v>568</v>
+      </c>
+      <c r="J163" t="s">
+        <v>339</v>
+      </c>
+      <c r="K163" t="s">
         <v>645</v>
-      </c>
-      <c r="J163" t="s">
-        <v>642</v>
-      </c>
-      <c r="K163" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="164" spans="1:11">
@@ -9022,22 +9022,22 @@
         <v>564</v>
       </c>
       <c r="F164" t="s">
+        <v>565</v>
+      </c>
+      <c r="G164" t="s">
         <v>649</v>
       </c>
-      <c r="G164" t="s">
-        <v>566</v>
-      </c>
       <c r="H164" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I164" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J164" t="s">
+        <v>339</v>
+      </c>
+      <c r="K164" t="s">
         <v>650</v>
-      </c>
-      <c r="K164" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="165" spans="1:11">
@@ -9057,22 +9057,22 @@
         <v>564</v>
       </c>
       <c r="F165" t="s">
+        <v>565</v>
+      </c>
+      <c r="G165" t="s">
         <v>649</v>
       </c>
-      <c r="G165" t="s">
-        <v>566</v>
-      </c>
       <c r="H165" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I165" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J165" t="s">
+        <v>339</v>
+      </c>
+      <c r="K165" t="s">
         <v>650</v>
-      </c>
-      <c r="K165" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="166" spans="1:11">
@@ -9092,22 +9092,22 @@
         <v>564</v>
       </c>
       <c r="F166" t="s">
+        <v>565</v>
+      </c>
+      <c r="G166" t="s">
         <v>649</v>
       </c>
-      <c r="G166" t="s">
-        <v>566</v>
-      </c>
       <c r="H166" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I166" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J166" t="s">
+        <v>339</v>
+      </c>
+      <c r="K166" t="s">
         <v>650</v>
-      </c>
-      <c r="K166" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="167" spans="1:11">
@@ -9127,22 +9127,22 @@
         <v>564</v>
       </c>
       <c r="F167" t="s">
+        <v>565</v>
+      </c>
+      <c r="G167" t="s">
         <v>649</v>
       </c>
-      <c r="G167" t="s">
-        <v>566</v>
-      </c>
       <c r="H167" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I167" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J167" t="s">
+        <v>339</v>
+      </c>
+      <c r="K167" t="s">
         <v>650</v>
-      </c>
-      <c r="K167" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="168" spans="1:11">
@@ -9159,25 +9159,25 @@
         <v>14</v>
       </c>
       <c r="E168" t="s">
-        <v>564</v>
+        <v>663</v>
       </c>
       <c r="F168" t="s">
+        <v>565</v>
+      </c>
+      <c r="G168" t="s">
         <v>649</v>
       </c>
-      <c r="G168" t="s">
-        <v>566</v>
-      </c>
       <c r="H168" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I168" t="s">
-        <v>663</v>
+        <v>568</v>
       </c>
       <c r="J168" t="s">
+        <v>339</v>
+      </c>
+      <c r="K168" t="s">
         <v>650</v>
-      </c>
-      <c r="K168" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -9191,25 +9191,25 @@
         <v>14</v>
       </c>
       <c r="E169" t="s">
-        <v>564</v>
+        <v>663</v>
       </c>
       <c r="F169" t="s">
+        <v>565</v>
+      </c>
+      <c r="G169" t="s">
         <v>649</v>
       </c>
-      <c r="G169" t="s">
-        <v>566</v>
-      </c>
       <c r="H169" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I169" t="s">
-        <v>663</v>
+        <v>568</v>
       </c>
       <c r="J169" t="s">
+        <v>339</v>
+      </c>
+      <c r="K169" t="s">
         <v>650</v>
-      </c>
-      <c r="K169" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -9229,22 +9229,22 @@
         <v>564</v>
       </c>
       <c r="F170" t="s">
+        <v>565</v>
+      </c>
+      <c r="G170" t="s">
         <v>649</v>
       </c>
-      <c r="G170" t="s">
-        <v>566</v>
-      </c>
       <c r="H170" t="s">
-        <v>338</v>
+        <v>567</v>
       </c>
       <c r="I170" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J170" t="s">
+        <v>339</v>
+      </c>
+      <c r="K170" t="s">
         <v>650</v>
-      </c>
-      <c r="K170" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -9263,17 +9263,17 @@
       <c r="E171" t="s">
         <v>337</v>
       </c>
-      <c r="G171" t="s">
+      <c r="F171" t="s">
         <v>672</v>
       </c>
       <c r="H171" t="s">
+        <v>673</v>
+      </c>
+      <c r="I171" t="s">
         <v>338</v>
       </c>
-      <c r="I171" t="s">
+      <c r="J171" t="s">
         <v>339</v>
-      </c>
-      <c r="K171" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="172" spans="1:11">
@@ -9292,17 +9292,17 @@
       <c r="E172" t="s">
         <v>243</v>
       </c>
-      <c r="G172" t="s">
+      <c r="F172" t="s">
         <v>672</v>
       </c>
       <c r="H172" t="s">
-        <v>236</v>
+        <v>673</v>
       </c>
       <c r="I172" t="s">
         <v>244</v>
       </c>
-      <c r="K172" t="s">
-        <v>673</v>
+      <c r="J172" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -9321,17 +9321,17 @@
       <c r="E173" t="s">
         <v>337</v>
       </c>
-      <c r="G173" t="s">
+      <c r="F173" t="s">
         <v>672</v>
       </c>
       <c r="H173" t="s">
+        <v>673</v>
+      </c>
+      <c r="I173" t="s">
         <v>338</v>
       </c>
-      <c r="I173" t="s">
+      <c r="J173" t="s">
         <v>339</v>
-      </c>
-      <c r="K173" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -9350,17 +9350,17 @@
       <c r="E174" t="s">
         <v>337</v>
       </c>
-      <c r="G174" t="s">
+      <c r="F174" t="s">
         <v>672</v>
       </c>
       <c r="H174" t="s">
+        <v>673</v>
+      </c>
+      <c r="I174" t="s">
         <v>338</v>
       </c>
-      <c r="I174" t="s">
+      <c r="J174" t="s">
         <v>339</v>
-      </c>
-      <c r="K174" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -9379,17 +9379,17 @@
       <c r="E175" t="s">
         <v>337</v>
       </c>
-      <c r="G175" t="s">
+      <c r="F175" t="s">
         <v>672</v>
       </c>
       <c r="H175" t="s">
+        <v>673</v>
+      </c>
+      <c r="I175" t="s">
         <v>338</v>
       </c>
-      <c r="I175" t="s">
+      <c r="J175" t="s">
         <v>339</v>
-      </c>
-      <c r="K175" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -9405,17 +9405,17 @@
       <c r="E176" t="s">
         <v>337</v>
       </c>
-      <c r="G176" t="s">
+      <c r="F176" t="s">
         <v>672</v>
       </c>
       <c r="H176" t="s">
+        <v>673</v>
+      </c>
+      <c r="I176" t="s">
         <v>338</v>
       </c>
-      <c r="I176" t="s">
+      <c r="J176" t="s">
         <v>339</v>
-      </c>
-      <c r="K176" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -9434,17 +9434,17 @@
       <c r="E177" t="s">
         <v>337</v>
       </c>
-      <c r="G177" t="s">
+      <c r="F177" t="s">
         <v>691</v>
       </c>
       <c r="H177" t="s">
+        <v>692</v>
+      </c>
+      <c r="I177" t="s">
         <v>338</v>
       </c>
-      <c r="I177" t="s">
+      <c r="J177" t="s">
         <v>339</v>
-      </c>
-      <c r="K177" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -9463,17 +9463,17 @@
       <c r="E178" t="s">
         <v>337</v>
       </c>
-      <c r="G178" t="s">
+      <c r="F178" t="s">
         <v>691</v>
       </c>
       <c r="H178" t="s">
+        <v>692</v>
+      </c>
+      <c r="I178" t="s">
         <v>338</v>
       </c>
-      <c r="I178" t="s">
+      <c r="J178" t="s">
         <v>339</v>
-      </c>
-      <c r="K178" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -9492,17 +9492,17 @@
       <c r="E179" t="s">
         <v>337</v>
       </c>
-      <c r="G179" t="s">
+      <c r="F179" t="s">
         <v>691</v>
       </c>
       <c r="H179" t="s">
+        <v>692</v>
+      </c>
+      <c r="I179" t="s">
         <v>338</v>
       </c>
-      <c r="I179" t="s">
+      <c r="J179" t="s">
         <v>339</v>
-      </c>
-      <c r="K179" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -9521,17 +9521,17 @@
       <c r="E180" t="s">
         <v>337</v>
       </c>
-      <c r="G180" t="s">
+      <c r="F180" t="s">
         <v>691</v>
       </c>
       <c r="H180" t="s">
+        <v>692</v>
+      </c>
+      <c r="I180" t="s">
         <v>338</v>
       </c>
-      <c r="I180" t="s">
+      <c r="J180" t="s">
         <v>339</v>
-      </c>
-      <c r="K180" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -9557,13 +9557,13 @@
         <v>707</v>
       </c>
       <c r="H181" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I181" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J181" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K181" t="s">
         <v>710</v>
@@ -9592,13 +9592,13 @@
         <v>707</v>
       </c>
       <c r="H182" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I182" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J182" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K182" t="s">
         <v>710</v>
@@ -9627,13 +9627,13 @@
         <v>707</v>
       </c>
       <c r="H183" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I183" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J183" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K183" t="s">
         <v>710</v>
@@ -9662,13 +9662,13 @@
         <v>707</v>
       </c>
       <c r="H184" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I184" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J184" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K184" t="s">
         <v>710</v>
@@ -9697,13 +9697,13 @@
         <v>707</v>
       </c>
       <c r="H185" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I185" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J185" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K185" t="s">
         <v>710</v>
@@ -9732,13 +9732,13 @@
         <v>707</v>
       </c>
       <c r="H186" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I186" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J186" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K186" t="s">
         <v>710</v>
@@ -9767,13 +9767,13 @@
         <v>707</v>
       </c>
       <c r="H187" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I187" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J187" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K187" t="s">
         <v>710</v>
@@ -9802,13 +9802,13 @@
         <v>707</v>
       </c>
       <c r="H188" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I188" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J188" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K188" t="s">
         <v>710</v>
@@ -9837,13 +9837,13 @@
         <v>707</v>
       </c>
       <c r="H189" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I189" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J189" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K189" t="s">
         <v>710</v>
@@ -9872,13 +9872,13 @@
         <v>707</v>
       </c>
       <c r="H190" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I190" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J190" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K190" t="s">
         <v>710</v>
@@ -9907,13 +9907,13 @@
         <v>707</v>
       </c>
       <c r="H191" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I191" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J191" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K191" t="s">
         <v>710</v>
@@ -9939,13 +9939,13 @@
         <v>707</v>
       </c>
       <c r="H192" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I192" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J192" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K192" t="s">
         <v>710</v>
@@ -9965,7 +9965,7 @@
         <v>14</v>
       </c>
       <c r="E193" t="s">
-        <v>575</v>
+        <v>746</v>
       </c>
       <c r="F193" t="s">
         <v>706</v>
@@ -9974,13 +9974,13 @@
         <v>707</v>
       </c>
       <c r="H193" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I193" t="s">
-        <v>746</v>
+        <v>576</v>
       </c>
       <c r="J193" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K193" t="s">
         <v>710</v>
@@ -10009,13 +10009,13 @@
         <v>707</v>
       </c>
       <c r="H194" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I194" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J194" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K194" t="s">
         <v>710</v>
@@ -10044,13 +10044,13 @@
         <v>707</v>
       </c>
       <c r="H195" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I195" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J195" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K195" t="s">
         <v>710</v>
@@ -10079,13 +10079,13 @@
         <v>707</v>
       </c>
       <c r="H196" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I196" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J196" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K196" t="s">
         <v>710</v>
@@ -10114,13 +10114,13 @@
         <v>707</v>
       </c>
       <c r="H197" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I197" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J197" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K197" t="s">
         <v>710</v>
@@ -10149,13 +10149,13 @@
         <v>707</v>
       </c>
       <c r="H198" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I198" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J198" t="s">
-        <v>709</v>
+        <v>339</v>
       </c>
       <c r="K198" t="s">
         <v>710</v>
@@ -10175,25 +10175,25 @@
         <v>14</v>
       </c>
       <c r="E199" t="s">
-        <v>705</v>
+        <v>765</v>
       </c>
       <c r="F199" t="s">
-        <v>765</v>
+        <v>706</v>
       </c>
       <c r="G199" t="s">
-        <v>707</v>
+        <v>766</v>
       </c>
       <c r="H199" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I199" t="s">
-        <v>766</v>
+        <v>709</v>
       </c>
       <c r="J199" t="s">
+        <v>339</v>
+      </c>
+      <c r="K199" t="s">
         <v>767</v>
-      </c>
-      <c r="K199" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="200" spans="1:11">
@@ -10210,25 +10210,25 @@
         <v>14</v>
       </c>
       <c r="E200" t="s">
-        <v>705</v>
+        <v>765</v>
       </c>
       <c r="F200" t="s">
-        <v>765</v>
+        <v>706</v>
       </c>
       <c r="G200" t="s">
-        <v>707</v>
+        <v>766</v>
       </c>
       <c r="H200" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I200" t="s">
-        <v>766</v>
+        <v>709</v>
       </c>
       <c r="J200" t="s">
+        <v>339</v>
+      </c>
+      <c r="K200" t="s">
         <v>767</v>
-      </c>
-      <c r="K200" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="201" spans="1:11">
@@ -10245,25 +10245,25 @@
         <v>14</v>
       </c>
       <c r="E201" t="s">
-        <v>705</v>
+        <v>765</v>
       </c>
       <c r="F201" t="s">
-        <v>765</v>
+        <v>706</v>
       </c>
       <c r="G201" t="s">
-        <v>707</v>
+        <v>766</v>
       </c>
       <c r="H201" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I201" t="s">
-        <v>766</v>
+        <v>709</v>
       </c>
       <c r="J201" t="s">
+        <v>339</v>
+      </c>
+      <c r="K201" t="s">
         <v>767</v>
-      </c>
-      <c r="K201" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="202" spans="1:11">
@@ -10277,25 +10277,25 @@
         <v>14</v>
       </c>
       <c r="E202" t="s">
-        <v>705</v>
+        <v>765</v>
       </c>
       <c r="F202" t="s">
-        <v>765</v>
+        <v>706</v>
       </c>
       <c r="G202" t="s">
-        <v>707</v>
+        <v>766</v>
       </c>
       <c r="H202" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I202" t="s">
-        <v>766</v>
+        <v>709</v>
       </c>
       <c r="J202" t="s">
+        <v>339</v>
+      </c>
+      <c r="K202" t="s">
         <v>767</v>
-      </c>
-      <c r="K202" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="203" spans="1:11">
@@ -10312,25 +10312,25 @@
         <v>14</v>
       </c>
       <c r="E203" t="s">
-        <v>575</v>
+        <v>746</v>
       </c>
       <c r="F203" t="s">
-        <v>765</v>
+        <v>706</v>
       </c>
       <c r="G203" t="s">
-        <v>707</v>
+        <v>766</v>
       </c>
       <c r="H203" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I203" t="s">
-        <v>746</v>
+        <v>576</v>
       </c>
       <c r="J203" t="s">
+        <v>339</v>
+      </c>
+      <c r="K203" t="s">
         <v>767</v>
-      </c>
-      <c r="K203" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -10344,25 +10344,25 @@
         <v>14</v>
       </c>
       <c r="E204" t="s">
-        <v>705</v>
+        <v>765</v>
       </c>
       <c r="F204" t="s">
-        <v>765</v>
+        <v>706</v>
       </c>
       <c r="G204" t="s">
-        <v>707</v>
+        <v>766</v>
       </c>
       <c r="H204" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I204" t="s">
-        <v>766</v>
+        <v>709</v>
       </c>
       <c r="J204" t="s">
+        <v>339</v>
+      </c>
+      <c r="K204" t="s">
         <v>767</v>
-      </c>
-      <c r="K204" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="205" spans="1:11">
@@ -10379,25 +10379,25 @@
         <v>14</v>
       </c>
       <c r="E205" t="s">
-        <v>705</v>
+        <v>784</v>
       </c>
       <c r="F205" t="s">
-        <v>784</v>
+        <v>706</v>
       </c>
       <c r="G205" t="s">
-        <v>707</v>
+        <v>785</v>
       </c>
       <c r="H205" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I205" t="s">
-        <v>785</v>
+        <v>709</v>
       </c>
       <c r="J205" t="s">
+        <v>339</v>
+      </c>
+      <c r="K205" t="s">
         <v>786</v>
-      </c>
-      <c r="K205" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="206" spans="1:11">
@@ -10414,25 +10414,25 @@
         <v>14</v>
       </c>
       <c r="E206" t="s">
-        <v>705</v>
+        <v>784</v>
       </c>
       <c r="F206" t="s">
-        <v>784</v>
+        <v>706</v>
       </c>
       <c r="G206" t="s">
-        <v>707</v>
+        <v>785</v>
       </c>
       <c r="H206" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I206" t="s">
-        <v>785</v>
+        <v>709</v>
       </c>
       <c r="J206" t="s">
+        <v>339</v>
+      </c>
+      <c r="K206" t="s">
         <v>786</v>
-      </c>
-      <c r="K206" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="207" spans="1:11">
@@ -10446,25 +10446,25 @@
         <v>14</v>
       </c>
       <c r="E207" t="s">
-        <v>705</v>
+        <v>784</v>
       </c>
       <c r="F207" t="s">
-        <v>784</v>
+        <v>706</v>
       </c>
       <c r="G207" t="s">
-        <v>707</v>
+        <v>785</v>
       </c>
       <c r="H207" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I207" t="s">
-        <v>785</v>
+        <v>709</v>
       </c>
       <c r="J207" t="s">
+        <v>339</v>
+      </c>
+      <c r="K207" t="s">
         <v>786</v>
-      </c>
-      <c r="K207" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="208" spans="1:11">
@@ -10481,25 +10481,25 @@
         <v>14</v>
       </c>
       <c r="E208" t="s">
-        <v>575</v>
+        <v>746</v>
       </c>
       <c r="F208" t="s">
-        <v>784</v>
+        <v>706</v>
       </c>
       <c r="G208" t="s">
-        <v>707</v>
+        <v>785</v>
       </c>
       <c r="H208" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I208" t="s">
-        <v>746</v>
+        <v>576</v>
       </c>
       <c r="J208" t="s">
+        <v>339</v>
+      </c>
+      <c r="K208" t="s">
         <v>786</v>
-      </c>
-      <c r="K208" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="209" spans="1:11">
@@ -10516,25 +10516,25 @@
         <v>14</v>
       </c>
       <c r="E209" t="s">
-        <v>705</v>
+        <v>784</v>
       </c>
       <c r="F209" t="s">
-        <v>784</v>
+        <v>706</v>
       </c>
       <c r="G209" t="s">
-        <v>707</v>
+        <v>785</v>
       </c>
       <c r="H209" t="s">
-        <v>338</v>
+        <v>708</v>
       </c>
       <c r="I209" t="s">
-        <v>785</v>
+        <v>709</v>
       </c>
       <c r="J209" t="s">
+        <v>339</v>
+      </c>
+      <c r="K209" t="s">
         <v>786</v>
-      </c>
-      <c r="K209" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="210" spans="1:11">
@@ -10560,13 +10560,13 @@
         <v>803</v>
       </c>
       <c r="H210" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I210" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J210" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K210" t="s">
         <v>806</v>
@@ -10592,13 +10592,13 @@
         <v>803</v>
       </c>
       <c r="H211" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I211" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J211" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K211" t="s">
         <v>806</v>
@@ -10627,13 +10627,13 @@
         <v>803</v>
       </c>
       <c r="H212" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I212" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J212" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K212" t="s">
         <v>806</v>
@@ -10659,13 +10659,13 @@
         <v>803</v>
       </c>
       <c r="H213" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I213" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J213" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K213" t="s">
         <v>806</v>
@@ -10694,13 +10694,13 @@
         <v>803</v>
       </c>
       <c r="H214" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I214" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J214" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K214" t="s">
         <v>806</v>
@@ -10720,7 +10720,7 @@
         <v>14</v>
       </c>
       <c r="E215" t="s">
-        <v>705</v>
+        <v>765</v>
       </c>
       <c r="F215" t="s">
         <v>802</v>
@@ -10729,13 +10729,13 @@
         <v>803</v>
       </c>
       <c r="H215" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I215" t="s">
-        <v>766</v>
+        <v>709</v>
       </c>
       <c r="J215" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K215" t="s">
         <v>806</v>
@@ -10764,13 +10764,13 @@
         <v>803</v>
       </c>
       <c r="H216" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I216" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J216" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K216" t="s">
         <v>806</v>
@@ -10799,13 +10799,13 @@
         <v>803</v>
       </c>
       <c r="H217" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I217" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J217" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K217" t="s">
         <v>806</v>
@@ -10831,13 +10831,13 @@
         <v>803</v>
       </c>
       <c r="H218" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I218" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J218" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K218" t="s">
         <v>806</v>
@@ -10863,13 +10863,13 @@
         <v>803</v>
       </c>
       <c r="H219" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I219" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J219" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K219" t="s">
         <v>806</v>
@@ -10889,7 +10889,7 @@
         <v>14</v>
       </c>
       <c r="E220" t="s">
-        <v>564</v>
+        <v>663</v>
       </c>
       <c r="F220" t="s">
         <v>802</v>
@@ -10898,13 +10898,13 @@
         <v>803</v>
       </c>
       <c r="H220" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I220" t="s">
-        <v>663</v>
+        <v>568</v>
       </c>
       <c r="J220" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K220" t="s">
         <v>806</v>
@@ -10933,13 +10933,13 @@
         <v>803</v>
       </c>
       <c r="H221" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I221" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J221" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K221" t="s">
         <v>806</v>
@@ -10968,13 +10968,13 @@
         <v>803</v>
       </c>
       <c r="H222" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I222" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J222" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K222" t="s">
         <v>806</v>
@@ -11000,13 +11000,13 @@
         <v>803</v>
       </c>
       <c r="H223" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I223" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J223" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K223" t="s">
         <v>806</v>
@@ -11035,13 +11035,13 @@
         <v>803</v>
       </c>
       <c r="H224" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I224" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J224" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K224" t="s">
         <v>806</v>
@@ -11070,13 +11070,13 @@
         <v>803</v>
       </c>
       <c r="H225" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I225" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J225" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K225" t="s">
         <v>806</v>
@@ -11105,13 +11105,13 @@
         <v>803</v>
       </c>
       <c r="H226" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I226" t="s">
         <v>576</v>
       </c>
       <c r="J226" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K226" t="s">
         <v>806</v>
@@ -11140,13 +11140,13 @@
         <v>803</v>
       </c>
       <c r="H227" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I227" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="J227" t="s">
-        <v>805</v>
+        <v>339</v>
       </c>
       <c r="K227" t="s">
         <v>806</v>
@@ -11175,13 +11175,13 @@
         <v>803</v>
       </c>
       <c r="H228" t="s">
+        <v>804</v>
+      </c>
+      <c r="I228" t="s">
         <v>338</v>
       </c>
-      <c r="I228" t="s">
+      <c r="J228" t="s">
         <v>339</v>
-      </c>
-      <c r="J228" t="s">
-        <v>805</v>
       </c>
       <c r="K228" t="s">
         <v>806</v>
@@ -11201,25 +11201,25 @@
         <v>14</v>
       </c>
       <c r="E229" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="F229" t="s">
-        <v>859</v>
+        <v>802</v>
       </c>
       <c r="G229" t="s">
-        <v>803</v>
+        <v>860</v>
       </c>
       <c r="H229" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I229" t="s">
-        <v>860</v>
+        <v>805</v>
       </c>
       <c r="J229" t="s">
+        <v>339</v>
+      </c>
+      <c r="K229" t="s">
         <v>861</v>
-      </c>
-      <c r="K229" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="230" spans="1:11">
@@ -11236,25 +11236,25 @@
         <v>14</v>
       </c>
       <c r="E230" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="F230" t="s">
-        <v>859</v>
+        <v>802</v>
       </c>
       <c r="G230" t="s">
-        <v>803</v>
+        <v>860</v>
       </c>
       <c r="H230" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I230" t="s">
-        <v>860</v>
+        <v>805</v>
       </c>
       <c r="J230" t="s">
+        <v>339</v>
+      </c>
+      <c r="K230" t="s">
         <v>861</v>
-      </c>
-      <c r="K230" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="231" spans="1:11">
@@ -11271,25 +11271,25 @@
         <v>14</v>
       </c>
       <c r="E231" t="s">
-        <v>564</v>
+        <v>623</v>
       </c>
       <c r="F231" t="s">
-        <v>859</v>
+        <v>802</v>
       </c>
       <c r="G231" t="s">
-        <v>803</v>
+        <v>860</v>
       </c>
       <c r="H231" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I231" t="s">
-        <v>623</v>
+        <v>568</v>
       </c>
       <c r="J231" t="s">
+        <v>339</v>
+      </c>
+      <c r="K231" t="s">
         <v>861</v>
-      </c>
-      <c r="K231" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="232" spans="1:11">
@@ -11306,25 +11306,25 @@
         <v>14</v>
       </c>
       <c r="E232" t="s">
-        <v>564</v>
+        <v>663</v>
       </c>
       <c r="F232" t="s">
-        <v>859</v>
+        <v>802</v>
       </c>
       <c r="G232" t="s">
-        <v>803</v>
+        <v>860</v>
       </c>
       <c r="H232" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I232" t="s">
-        <v>663</v>
+        <v>568</v>
       </c>
       <c r="J232" t="s">
+        <v>339</v>
+      </c>
+      <c r="K232" t="s">
         <v>861</v>
-      </c>
-      <c r="K232" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="233" spans="1:11">
@@ -11341,25 +11341,25 @@
         <v>14</v>
       </c>
       <c r="E233" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="F233" t="s">
-        <v>859</v>
+        <v>802</v>
       </c>
       <c r="G233" t="s">
-        <v>803</v>
+        <v>860</v>
       </c>
       <c r="H233" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I233" t="s">
-        <v>860</v>
+        <v>805</v>
       </c>
       <c r="J233" t="s">
+        <v>339</v>
+      </c>
+      <c r="K233" t="s">
         <v>861</v>
-      </c>
-      <c r="K233" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="234" spans="1:11">
@@ -11376,25 +11376,25 @@
         <v>14</v>
       </c>
       <c r="E234" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="F234" t="s">
-        <v>859</v>
+        <v>802</v>
       </c>
       <c r="G234" t="s">
-        <v>803</v>
+        <v>860</v>
       </c>
       <c r="H234" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I234" t="s">
-        <v>860</v>
+        <v>805</v>
       </c>
       <c r="J234" t="s">
+        <v>339</v>
+      </c>
+      <c r="K234" t="s">
         <v>861</v>
-      </c>
-      <c r="K234" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="235" spans="1:11">
@@ -11411,25 +11411,25 @@
         <v>14</v>
       </c>
       <c r="E235" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="F235" t="s">
-        <v>859</v>
+        <v>802</v>
       </c>
       <c r="G235" t="s">
-        <v>803</v>
+        <v>860</v>
       </c>
       <c r="H235" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I235" t="s">
-        <v>860</v>
+        <v>805</v>
       </c>
       <c r="J235" t="s">
+        <v>339</v>
+      </c>
+      <c r="K235" t="s">
         <v>861</v>
-      </c>
-      <c r="K235" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="236" spans="1:11">
@@ -11446,25 +11446,25 @@
         <v>14</v>
       </c>
       <c r="E236" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="F236" t="s">
-        <v>859</v>
+        <v>802</v>
       </c>
       <c r="G236" t="s">
-        <v>803</v>
+        <v>860</v>
       </c>
       <c r="H236" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I236" t="s">
-        <v>860</v>
+        <v>805</v>
       </c>
       <c r="J236" t="s">
+        <v>339</v>
+      </c>
+      <c r="K236" t="s">
         <v>861</v>
-      </c>
-      <c r="K236" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="237" spans="1:11">
@@ -11481,25 +11481,25 @@
         <v>14</v>
       </c>
       <c r="E237" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="F237" t="s">
-        <v>859</v>
+        <v>802</v>
       </c>
       <c r="G237" t="s">
-        <v>803</v>
+        <v>860</v>
       </c>
       <c r="H237" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I237" t="s">
-        <v>860</v>
+        <v>805</v>
       </c>
       <c r="J237" t="s">
+        <v>339</v>
+      </c>
+      <c r="K237" t="s">
         <v>861</v>
-      </c>
-      <c r="K237" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="238" spans="1:11">
@@ -11516,25 +11516,25 @@
         <v>14</v>
       </c>
       <c r="E238" t="s">
-        <v>801</v>
+        <v>859</v>
       </c>
       <c r="F238" t="s">
-        <v>859</v>
+        <v>802</v>
       </c>
       <c r="G238" t="s">
-        <v>803</v>
+        <v>860</v>
       </c>
       <c r="H238" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I238" t="s">
-        <v>860</v>
+        <v>805</v>
       </c>
       <c r="J238" t="s">
+        <v>339</v>
+      </c>
+      <c r="K238" t="s">
         <v>861</v>
-      </c>
-      <c r="K238" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="239" spans="1:11">
@@ -11551,25 +11551,25 @@
         <v>14</v>
       </c>
       <c r="E239" t="s">
-        <v>801</v>
+        <v>892</v>
       </c>
       <c r="F239" t="s">
-        <v>892</v>
+        <v>802</v>
       </c>
       <c r="G239" t="s">
-        <v>803</v>
+        <v>893</v>
       </c>
       <c r="H239" t="s">
-        <v>338</v>
+        <v>804</v>
       </c>
       <c r="I239" t="s">
-        <v>893</v>
+        <v>805</v>
       </c>
       <c r="J239" t="s">
+        <v>339</v>
+      </c>
+      <c r="K239" t="s">
         <v>894</v>
-      </c>
-      <c r="K239" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="240" spans="1:11">
@@ -11595,13 +11595,13 @@
         <v>899</v>
       </c>
       <c r="H240" t="s">
+        <v>899</v>
+      </c>
+      <c r="I240" t="s">
         <v>338</v>
       </c>
-      <c r="I240" t="s">
+      <c r="J240" t="s">
         <v>339</v>
-      </c>
-      <c r="J240" t="s">
-        <v>900</v>
       </c>
       <c r="K240" t="s">
         <v>900</v>
@@ -11630,13 +11630,13 @@
         <v>899</v>
       </c>
       <c r="H241" t="s">
+        <v>899</v>
+      </c>
+      <c r="I241" t="s">
         <v>338</v>
       </c>
-      <c r="I241" t="s">
+      <c r="J241" t="s">
         <v>339</v>
-      </c>
-      <c r="J241" t="s">
-        <v>900</v>
       </c>
       <c r="K241" t="s">
         <v>900</v>
@@ -11665,13 +11665,13 @@
         <v>899</v>
       </c>
       <c r="H242" t="s">
+        <v>899</v>
+      </c>
+      <c r="I242" t="s">
         <v>338</v>
       </c>
-      <c r="I242" t="s">
+      <c r="J242" t="s">
         <v>339</v>
-      </c>
-      <c r="J242" t="s">
-        <v>900</v>
       </c>
       <c r="K242" t="s">
         <v>900</v>
@@ -11700,13 +11700,13 @@
         <v>899</v>
       </c>
       <c r="H243" t="s">
+        <v>899</v>
+      </c>
+      <c r="I243" t="s">
         <v>338</v>
       </c>
-      <c r="I243" t="s">
+      <c r="J243" t="s">
         <v>339</v>
-      </c>
-      <c r="J243" t="s">
-        <v>900</v>
       </c>
       <c r="K243" t="s">
         <v>900</v>
@@ -11735,13 +11735,13 @@
         <v>899</v>
       </c>
       <c r="H244" t="s">
+        <v>899</v>
+      </c>
+      <c r="I244" t="s">
         <v>338</v>
       </c>
-      <c r="I244" t="s">
+      <c r="J244" t="s">
         <v>339</v>
-      </c>
-      <c r="J244" t="s">
-        <v>900</v>
       </c>
       <c r="K244" t="s">
         <v>900</v>
@@ -11770,13 +11770,13 @@
         <v>899</v>
       </c>
       <c r="H245" t="s">
+        <v>899</v>
+      </c>
+      <c r="I245" t="s">
         <v>338</v>
       </c>
-      <c r="I245" t="s">
+      <c r="J245" t="s">
         <v>339</v>
-      </c>
-      <c r="J245" t="s">
-        <v>900</v>
       </c>
       <c r="K245" t="s">
         <v>900</v>
@@ -11793,25 +11793,25 @@
         <v>14</v>
       </c>
       <c r="E246" t="s">
-        <v>533</v>
+        <v>918</v>
       </c>
       <c r="F246" t="s">
-        <v>918</v>
+        <v>898</v>
       </c>
       <c r="G246" t="s">
+        <v>919</v>
+      </c>
+      <c r="H246" t="s">
         <v>899</v>
       </c>
-      <c r="H246" t="s">
-        <v>338</v>
-      </c>
       <c r="I246" t="s">
-        <v>919</v>
+        <v>534</v>
       </c>
       <c r="J246" t="s">
+        <v>339</v>
+      </c>
+      <c r="K246" t="s">
         <v>920</v>
-      </c>
-      <c r="K246" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="247" spans="1:11">
@@ -11830,17 +11830,17 @@
       <c r="E247" t="s">
         <v>196</v>
       </c>
-      <c r="G247" t="s">
+      <c r="F247" t="s">
         <v>924</v>
       </c>
       <c r="H247" t="s">
+        <v>925</v>
+      </c>
+      <c r="I247" t="s">
         <v>197</v>
       </c>
-      <c r="I247" t="s">
+      <c r="J247" t="s">
         <v>198</v>
-      </c>
-      <c r="K247" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="248" spans="1:11">
@@ -11859,17 +11859,17 @@
       <c r="E248" t="s">
         <v>196</v>
       </c>
-      <c r="G248" t="s">
+      <c r="F248" t="s">
         <v>924</v>
       </c>
       <c r="H248" t="s">
+        <v>925</v>
+      </c>
+      <c r="I248" t="s">
         <v>197</v>
       </c>
-      <c r="I248" t="s">
+      <c r="J248" t="s">
         <v>198</v>
-      </c>
-      <c r="K248" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="249" spans="1:11">
@@ -11888,17 +11888,17 @@
       <c r="E249" t="s">
         <v>932</v>
       </c>
-      <c r="G249" t="s">
+      <c r="F249" t="s">
         <v>924</v>
       </c>
       <c r="H249" t="s">
-        <v>197</v>
+        <v>925</v>
       </c>
       <c r="I249" t="s">
         <v>933</v>
       </c>
-      <c r="K249" t="s">
-        <v>925</v>
+      <c r="J249" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="250" spans="1:11">
@@ -11917,17 +11917,17 @@
       <c r="E250" t="s">
         <v>196</v>
       </c>
-      <c r="G250" t="s">
+      <c r="F250" t="s">
         <v>924</v>
       </c>
       <c r="H250" t="s">
+        <v>925</v>
+      </c>
+      <c r="I250" t="s">
         <v>197</v>
       </c>
-      <c r="I250" t="s">
+      <c r="J250" t="s">
         <v>198</v>
-      </c>
-      <c r="K250" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="251" spans="1:11">
@@ -11943,17 +11943,17 @@
       <c r="E251" t="s">
         <v>196</v>
       </c>
-      <c r="G251" t="s">
+      <c r="F251" t="s">
         <v>924</v>
       </c>
       <c r="H251" t="s">
+        <v>925</v>
+      </c>
+      <c r="I251" t="s">
         <v>197</v>
       </c>
-      <c r="I251" t="s">
+      <c r="J251" t="s">
         <v>198</v>
-      </c>
-      <c r="K251" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="252" spans="1:11">
@@ -11972,17 +11972,17 @@
       <c r="E252" t="s">
         <v>196</v>
       </c>
-      <c r="G252" t="s">
+      <c r="F252" t="s">
         <v>924</v>
       </c>
       <c r="H252" t="s">
+        <v>925</v>
+      </c>
+      <c r="I252" t="s">
         <v>197</v>
       </c>
-      <c r="I252" t="s">
+      <c r="J252" t="s">
         <v>198</v>
-      </c>
-      <c r="K252" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="253" spans="1:11">
@@ -11998,17 +11998,17 @@
       <c r="E253" t="s">
         <v>944</v>
       </c>
-      <c r="G253" t="s">
+      <c r="F253" t="s">
         <v>945</v>
       </c>
       <c r="H253" t="s">
-        <v>338</v>
+        <v>946</v>
       </c>
       <c r="I253" t="s">
-        <v>946</v>
-      </c>
-      <c r="K253" t="s">
         <v>947</v>
+      </c>
+      <c r="J253" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="254" spans="1:11">
@@ -12027,17 +12027,17 @@
       <c r="E254" t="s">
         <v>454</v>
       </c>
-      <c r="G254" t="s">
+      <c r="F254" t="s">
         <v>945</v>
       </c>
       <c r="H254" t="s">
-        <v>190</v>
+        <v>946</v>
       </c>
       <c r="I254" t="s">
         <v>455</v>
       </c>
-      <c r="K254" t="s">
-        <v>947</v>
+      <c r="J254" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="255" spans="1:11">
@@ -12056,17 +12056,17 @@
       <c r="E255" t="s">
         <v>954</v>
       </c>
-      <c r="G255" t="s">
+      <c r="F255" t="s">
         <v>945</v>
       </c>
       <c r="H255" t="s">
-        <v>190</v>
+        <v>946</v>
       </c>
       <c r="I255" t="s">
         <v>955</v>
       </c>
-      <c r="K255" t="s">
-        <v>947</v>
+      <c r="J255" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="256" spans="1:11">
@@ -12085,20 +12085,20 @@
       <c r="E256" t="s">
         <v>954</v>
       </c>
-      <c r="G256" t="s">
+      <c r="F256" t="s">
         <v>945</v>
       </c>
       <c r="H256" t="s">
-        <v>190</v>
+        <v>946</v>
       </c>
       <c r="I256" t="s">
         <v>955</v>
       </c>
-      <c r="K256" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="257" spans="1:11">
+      <c r="J256" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10">
       <c r="A257" t="s">
         <v>959</v>
       </c>
@@ -12114,20 +12114,20 @@
       <c r="E257" t="s">
         <v>954</v>
       </c>
-      <c r="G257" t="s">
+      <c r="F257" t="s">
         <v>945</v>
       </c>
       <c r="H257" t="s">
-        <v>190</v>
+        <v>946</v>
       </c>
       <c r="I257" t="s">
         <v>955</v>
       </c>
-      <c r="K257" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="258" spans="1:11">
+      <c r="J257" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10">
       <c r="A258" t="s">
         <v>962</v>
       </c>
@@ -12143,20 +12143,20 @@
       <c r="E258" t="s">
         <v>705</v>
       </c>
-      <c r="G258" t="s">
+      <c r="F258" t="s">
         <v>945</v>
       </c>
       <c r="H258" t="s">
-        <v>338</v>
+        <v>946</v>
       </c>
       <c r="I258" t="s">
-        <v>708</v>
-      </c>
-      <c r="K258" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="259" spans="1:11">
+        <v>709</v>
+      </c>
+      <c r="J258" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10">
       <c r="A259" t="s">
         <v>965</v>
       </c>
@@ -12172,20 +12172,20 @@
       <c r="E259" t="s">
         <v>954</v>
       </c>
-      <c r="G259" t="s">
+      <c r="F259" t="s">
         <v>945</v>
       </c>
       <c r="H259" t="s">
-        <v>190</v>
+        <v>946</v>
       </c>
       <c r="I259" t="s">
         <v>955</v>
       </c>
-      <c r="K259" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="260" spans="1:11">
+      <c r="J259" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10">
       <c r="A260" t="s">
         <v>967</v>
       </c>
@@ -12201,20 +12201,20 @@
       <c r="E260" t="s">
         <v>337</v>
       </c>
-      <c r="G260" t="s">
+      <c r="F260" t="s">
         <v>945</v>
       </c>
       <c r="H260" t="s">
+        <v>946</v>
+      </c>
+      <c r="I260" t="s">
         <v>338</v>
       </c>
-      <c r="I260" t="s">
+      <c r="J260" t="s">
         <v>339</v>
       </c>
-      <c r="K260" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="261" spans="1:11">
+    </row>
+    <row r="261" spans="1:10">
       <c r="A261" t="s">
         <v>970</v>
       </c>
@@ -12230,20 +12230,20 @@
       <c r="E261" t="s">
         <v>973</v>
       </c>
-      <c r="G261" t="s">
+      <c r="F261" t="s">
         <v>945</v>
       </c>
       <c r="H261" t="s">
-        <v>406</v>
+        <v>946</v>
       </c>
       <c r="I261" t="s">
         <v>974</v>
       </c>
-      <c r="K261" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="262" spans="1:11">
+      <c r="J261" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10">
       <c r="A262" t="s">
         <v>975</v>
       </c>
@@ -12259,20 +12259,20 @@
       <c r="E262" t="s">
         <v>337</v>
       </c>
-      <c r="G262" t="s">
+      <c r="F262" t="s">
         <v>945</v>
       </c>
       <c r="H262" t="s">
+        <v>946</v>
+      </c>
+      <c r="I262" t="s">
         <v>338</v>
       </c>
-      <c r="I262" t="s">
+      <c r="J262" t="s">
         <v>339</v>
       </c>
-      <c r="K262" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="263" spans="1:11">
+    </row>
+    <row r="263" spans="1:10">
       <c r="A263" t="s">
         <v>978</v>
       </c>
@@ -12288,20 +12288,20 @@
       <c r="E263" t="s">
         <v>981</v>
       </c>
-      <c r="G263" t="s">
+      <c r="F263" t="s">
         <v>945</v>
       </c>
       <c r="H263" t="s">
-        <v>378</v>
+        <v>946</v>
       </c>
       <c r="I263" t="s">
         <v>982</v>
       </c>
-      <c r="K263" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="264" spans="1:11">
+      <c r="J263" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10">
       <c r="A264" t="s">
         <v>983</v>
       </c>
@@ -12317,20 +12317,20 @@
       <c r="E264" t="s">
         <v>58</v>
       </c>
-      <c r="G264" t="s">
+      <c r="F264" t="s">
         <v>945</v>
       </c>
       <c r="H264" t="s">
+        <v>946</v>
+      </c>
+      <c r="I264" t="s">
         <v>59</v>
       </c>
-      <c r="I264" t="s">
+      <c r="J264" t="s">
         <v>60</v>
       </c>
-      <c r="K264" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="265" spans="1:11">
+    </row>
+    <row r="265" spans="1:10">
       <c r="A265" t="s">
         <v>986</v>
       </c>
@@ -12346,20 +12346,20 @@
       <c r="E265" t="s">
         <v>15</v>
       </c>
-      <c r="G265" t="s">
+      <c r="F265" t="s">
         <v>945</v>
       </c>
       <c r="H265" t="s">
-        <v>18</v>
+        <v>946</v>
       </c>
       <c r="I265" t="s">
         <v>19</v>
       </c>
-      <c r="K265" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="266" spans="1:11">
+      <c r="J265" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10">
       <c r="A266" t="s">
         <v>989</v>
       </c>
@@ -12375,20 +12375,20 @@
       <c r="E266" t="s">
         <v>992</v>
       </c>
-      <c r="G266" t="s">
+      <c r="F266" t="s">
         <v>945</v>
       </c>
       <c r="H266" t="s">
-        <v>236</v>
+        <v>946</v>
       </c>
       <c r="I266" t="s">
         <v>993</v>
       </c>
-      <c r="K266" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="267" spans="1:11">
+      <c r="J266" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10">
       <c r="A267" t="s">
         <v>994</v>
       </c>
@@ -12404,20 +12404,20 @@
       <c r="E267" t="s">
         <v>243</v>
       </c>
-      <c r="G267" t="s">
+      <c r="F267" t="s">
         <v>997</v>
       </c>
       <c r="H267" t="s">
-        <v>236</v>
+        <v>998</v>
       </c>
       <c r="I267" t="s">
         <v>244</v>
       </c>
-      <c r="K267" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="268" spans="1:11">
+      <c r="J267" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10">
       <c r="A268" t="s">
         <v>999</v>
       </c>
@@ -12433,20 +12433,20 @@
       <c r="E268" t="s">
         <v>420</v>
       </c>
-      <c r="G268" t="s">
+      <c r="F268" t="s">
         <v>1002</v>
       </c>
       <c r="H268" t="s">
-        <v>378</v>
+        <v>1003</v>
       </c>
       <c r="I268" t="s">
-        <v>422</v>
-      </c>
-      <c r="K268" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="269" spans="1:11">
+        <v>423</v>
+      </c>
+      <c r="J268" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10">
       <c r="A269" t="s">
         <v>1004</v>
       </c>
@@ -12462,20 +12462,20 @@
       <c r="E269" t="s">
         <v>243</v>
       </c>
-      <c r="G269" t="s">
+      <c r="F269" t="s">
         <v>1007</v>
       </c>
       <c r="H269" t="s">
-        <v>236</v>
+        <v>1008</v>
       </c>
       <c r="I269" t="s">
         <v>244</v>
       </c>
-      <c r="K269" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="270" spans="1:11">
+      <c r="J269" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10">
       <c r="A270" t="s">
         <v>1009</v>
       </c>
@@ -12491,20 +12491,20 @@
       <c r="E270" t="s">
         <v>243</v>
       </c>
-      <c r="G270" t="s">
+      <c r="F270" t="s">
         <v>1007</v>
       </c>
       <c r="H270" t="s">
-        <v>236</v>
+        <v>1008</v>
       </c>
       <c r="I270" t="s">
         <v>244</v>
       </c>
-      <c r="K270" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="271" spans="1:11">
+      <c r="J270" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10">
       <c r="A271" t="s">
         <v>1012</v>
       </c>
@@ -12520,20 +12520,20 @@
       <c r="E271" t="s">
         <v>1015</v>
       </c>
-      <c r="G271" t="s">
+      <c r="F271" t="s">
         <v>1016</v>
       </c>
       <c r="H271" t="s">
-        <v>236</v>
+        <v>1017</v>
       </c>
       <c r="I271" t="s">
-        <v>1017</v>
-      </c>
-      <c r="K271" t="s">
         <v>1018</v>
       </c>
-    </row>
-    <row r="272" spans="1:11">
+      <c r="J271" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10">
       <c r="A272" t="s">
         <v>1019</v>
       </c>
@@ -12546,20 +12546,20 @@
       <c r="E272" t="s">
         <v>1015</v>
       </c>
-      <c r="G272" t="s">
+      <c r="F272" t="s">
         <v>1016</v>
       </c>
       <c r="H272" t="s">
-        <v>236</v>
+        <v>1017</v>
       </c>
       <c r="I272" t="s">
-        <v>1017</v>
-      </c>
-      <c r="K272" t="s">
         <v>1018</v>
       </c>
-    </row>
-    <row r="273" spans="1:11">
+      <c r="J272" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10">
       <c r="A273" t="s">
         <v>1021</v>
       </c>
@@ -12575,20 +12575,20 @@
       <c r="E273" t="s">
         <v>1015</v>
       </c>
-      <c r="G273" t="s">
+      <c r="F273" t="s">
         <v>1016</v>
       </c>
       <c r="H273" t="s">
-        <v>236</v>
+        <v>1017</v>
       </c>
       <c r="I273" t="s">
-        <v>1017</v>
-      </c>
-      <c r="K273" t="s">
         <v>1018</v>
       </c>
-    </row>
-    <row r="274" spans="1:11">
+      <c r="J273" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10">
       <c r="A274" t="s">
         <v>1024</v>
       </c>
@@ -12601,20 +12601,20 @@
       <c r="E274" t="s">
         <v>1015</v>
       </c>
-      <c r="G274" t="s">
+      <c r="F274" t="s">
         <v>1016</v>
       </c>
       <c r="H274" t="s">
-        <v>236</v>
+        <v>1017</v>
       </c>
       <c r="I274" t="s">
-        <v>1017</v>
-      </c>
-      <c r="K274" t="s">
         <v>1018</v>
       </c>
-    </row>
-    <row r="275" spans="1:11">
+      <c r="J274" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10">
       <c r="A275" t="s">
         <v>1026</v>
       </c>
@@ -12630,20 +12630,20 @@
       <c r="E275" t="s">
         <v>1015</v>
       </c>
-      <c r="G275" t="s">
+      <c r="F275" t="s">
         <v>1016</v>
       </c>
       <c r="H275" t="s">
-        <v>236</v>
+        <v>1017</v>
       </c>
       <c r="I275" t="s">
-        <v>1017</v>
-      </c>
-      <c r="K275" t="s">
         <v>1018</v>
       </c>
-    </row>
-    <row r="276" spans="1:11">
+      <c r="J275" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="276" spans="1:10">
       <c r="A276" t="s">
         <v>1029</v>
       </c>
@@ -12659,20 +12659,20 @@
       <c r="E276" t="s">
         <v>1015</v>
       </c>
-      <c r="G276" t="s">
+      <c r="F276" t="s">
         <v>1016</v>
       </c>
       <c r="H276" t="s">
-        <v>236</v>
+        <v>1017</v>
       </c>
       <c r="I276" t="s">
-        <v>1017</v>
-      </c>
-      <c r="K276" t="s">
         <v>1018</v>
       </c>
-    </row>
-    <row r="277" spans="1:11">
+      <c r="J276" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10">
       <c r="A277" t="s">
         <v>1032</v>
       </c>
@@ -12688,20 +12688,20 @@
       <c r="E277" t="s">
         <v>1015</v>
       </c>
-      <c r="G277" t="s">
+      <c r="F277" t="s">
         <v>1016</v>
       </c>
       <c r="H277" t="s">
-        <v>236</v>
+        <v>1017</v>
       </c>
       <c r="I277" t="s">
-        <v>1017</v>
-      </c>
-      <c r="K277" t="s">
         <v>1018</v>
       </c>
-    </row>
-    <row r="278" spans="1:11">
+      <c r="J277" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="278" spans="1:10">
       <c r="A278" t="s">
         <v>1035</v>
       </c>
@@ -12717,20 +12717,20 @@
       <c r="E278" t="s">
         <v>420</v>
       </c>
-      <c r="G278" t="s">
+      <c r="F278" t="s">
         <v>1038</v>
       </c>
       <c r="H278" t="s">
-        <v>378</v>
+        <v>1039</v>
       </c>
       <c r="I278" t="s">
-        <v>422</v>
-      </c>
-      <c r="K278" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="279" spans="1:11">
+        <v>423</v>
+      </c>
+      <c r="J278" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="279" spans="1:10">
       <c r="A279" t="s">
         <v>1040</v>
       </c>
@@ -12746,20 +12746,20 @@
       <c r="E279" t="s">
         <v>92</v>
       </c>
-      <c r="G279" t="s">
+      <c r="F279" t="s">
         <v>1038</v>
       </c>
       <c r="H279" t="s">
-        <v>59</v>
+        <v>1039</v>
       </c>
       <c r="I279" t="s">
-        <v>95</v>
-      </c>
-      <c r="K279" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="280" spans="1:11">
+        <v>96</v>
+      </c>
+      <c r="J279" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="280" spans="1:10">
       <c r="A280" t="s">
         <v>1043</v>
       </c>
@@ -12775,20 +12775,20 @@
       <c r="E280" t="s">
         <v>15</v>
       </c>
-      <c r="G280" t="s">
+      <c r="F280" t="s">
         <v>1038</v>
       </c>
       <c r="H280" t="s">
-        <v>18</v>
+        <v>1039</v>
       </c>
       <c r="I280" t="s">
         <v>19</v>
       </c>
-      <c r="K280" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="281" spans="1:11">
+      <c r="J280" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="281" spans="1:10">
       <c r="A281" t="s">
         <v>1046</v>
       </c>
@@ -12804,20 +12804,20 @@
       <c r="E281" t="s">
         <v>352</v>
       </c>
-      <c r="G281" t="s">
+      <c r="F281" t="s">
         <v>1038</v>
       </c>
       <c r="H281" t="s">
-        <v>236</v>
+        <v>1039</v>
       </c>
       <c r="I281" t="s">
         <v>353</v>
       </c>
-      <c r="K281" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="282" spans="1:11">
+      <c r="J281" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="282" spans="1:10">
       <c r="A282" t="s">
         <v>1049</v>
       </c>
@@ -12833,20 +12833,20 @@
       <c r="E282" t="s">
         <v>253</v>
       </c>
-      <c r="G282" t="s">
+      <c r="F282" t="s">
         <v>1038</v>
       </c>
       <c r="H282" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I282" t="s">
         <v>254</v>
       </c>
-      <c r="I282" t="s">
+      <c r="J282" t="s">
         <v>255</v>
       </c>
-      <c r="K282" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="283" spans="1:11">
+    </row>
+    <row r="283" spans="1:10">
       <c r="A283" t="s">
         <v>1052</v>
       </c>
@@ -12860,22 +12860,22 @@
         <v>14</v>
       </c>
       <c r="E283" t="s">
-        <v>801</v>
-      </c>
-      <c r="G283" t="s">
+        <v>892</v>
+      </c>
+      <c r="F283" t="s">
         <v>1055</v>
       </c>
       <c r="H283" t="s">
-        <v>338</v>
+        <v>1056</v>
       </c>
       <c r="I283" t="s">
-        <v>893</v>
-      </c>
-      <c r="K283" t="s">
-        <v>1056</v>
-      </c>
-    </row>
-    <row r="284" spans="1:11">
+        <v>805</v>
+      </c>
+      <c r="J283" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10">
       <c r="A284" t="s">
         <v>1057</v>
       </c>
@@ -12891,20 +12891,20 @@
       <c r="E284" t="s">
         <v>253</v>
       </c>
-      <c r="G284" t="s">
+      <c r="F284" t="s">
         <v>1060</v>
       </c>
       <c r="H284" t="s">
+        <v>1061</v>
+      </c>
+      <c r="I284" t="s">
         <v>254</v>
       </c>
-      <c r="I284" t="s">
+      <c r="J284" t="s">
         <v>255</v>
       </c>
-      <c r="K284" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="285" spans="1:11">
+    </row>
+    <row r="285" spans="1:10">
       <c r="A285" t="s">
         <v>1062</v>
       </c>
@@ -12917,20 +12917,20 @@
       <c r="E285" t="s">
         <v>352</v>
       </c>
-      <c r="G285" t="s">
+      <c r="F285" t="s">
         <v>1064</v>
       </c>
       <c r="H285" t="s">
-        <v>236</v>
+        <v>1065</v>
       </c>
       <c r="I285" t="s">
         <v>353</v>
       </c>
-      <c r="K285" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="286" spans="1:11">
+      <c r="J285" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="286" spans="1:10">
       <c r="A286" t="s">
         <v>1066</v>
       </c>
@@ -12946,20 +12946,20 @@
       <c r="E286" t="s">
         <v>981</v>
       </c>
-      <c r="G286" t="s">
+      <c r="F286" t="s">
         <v>1069</v>
       </c>
       <c r="H286" t="s">
-        <v>378</v>
+        <v>1070</v>
       </c>
       <c r="I286" t="s">
         <v>982</v>
       </c>
-      <c r="K286" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="287" spans="1:11">
+      <c r="J286" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="287" spans="1:10">
       <c r="A287" t="s">
         <v>1071</v>
       </c>
@@ -12975,20 +12975,20 @@
       <c r="E287" t="s">
         <v>981</v>
       </c>
-      <c r="G287" t="s">
+      <c r="F287" t="s">
         <v>1069</v>
       </c>
       <c r="H287" t="s">
-        <v>378</v>
+        <v>1070</v>
       </c>
       <c r="I287" t="s">
         <v>982</v>
       </c>
-      <c r="K287" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="288" spans="1:11">
+      <c r="J287" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="288" spans="1:10">
       <c r="A288" t="s">
         <v>1074</v>
       </c>
@@ -13004,20 +13004,20 @@
       <c r="E288" t="s">
         <v>75</v>
       </c>
-      <c r="G288" t="s">
+      <c r="F288" t="s">
         <v>1069</v>
       </c>
       <c r="H288" t="s">
-        <v>18</v>
+        <v>1070</v>
       </c>
       <c r="I288" t="s">
         <v>76</v>
       </c>
-      <c r="K288" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="289" spans="1:11">
+      <c r="J288" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="289" spans="1:10">
       <c r="A289" t="s">
         <v>1077</v>
       </c>
@@ -13033,20 +13033,20 @@
       <c r="E289" t="s">
         <v>58</v>
       </c>
-      <c r="G289" t="s">
+      <c r="F289" t="s">
         <v>1069</v>
       </c>
       <c r="H289" t="s">
+        <v>1070</v>
+      </c>
+      <c r="I289" t="s">
         <v>59</v>
       </c>
-      <c r="I289" t="s">
+      <c r="J289" t="s">
         <v>60</v>
       </c>
-      <c r="K289" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="290" spans="1:11">
+    </row>
+    <row r="290" spans="1:10">
       <c r="A290" t="s">
         <v>1080</v>
       </c>
@@ -13062,20 +13062,20 @@
       <c r="E290" t="s">
         <v>58</v>
       </c>
-      <c r="G290" t="s">
+      <c r="F290" t="s">
         <v>1069</v>
       </c>
       <c r="H290" t="s">
+        <v>1070</v>
+      </c>
+      <c r="I290" t="s">
         <v>59</v>
       </c>
-      <c r="I290" t="s">
+      <c r="J290" t="s">
         <v>60</v>
       </c>
-      <c r="K290" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="291" spans="1:11">
+    </row>
+    <row r="291" spans="1:10">
       <c r="A291" t="s">
         <v>1083</v>
       </c>
@@ -13091,20 +13091,20 @@
       <c r="E291" t="s">
         <v>352</v>
       </c>
-      <c r="G291" t="s">
+      <c r="F291" t="s">
         <v>1069</v>
       </c>
       <c r="H291" t="s">
-        <v>236</v>
+        <v>1070</v>
       </c>
       <c r="I291" t="s">
         <v>353</v>
       </c>
-      <c r="K291" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="292" spans="1:11">
+      <c r="J291" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10">
       <c r="A292" t="s">
         <v>1086</v>
       </c>
@@ -13120,20 +13120,20 @@
       <c r="E292" t="s">
         <v>352</v>
       </c>
-      <c r="G292" t="s">
+      <c r="F292" t="s">
         <v>1069</v>
       </c>
       <c r="H292" t="s">
-        <v>236</v>
+        <v>1070</v>
       </c>
       <c r="I292" t="s">
         <v>353</v>
       </c>
-      <c r="K292" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="293" spans="1:11">
+      <c r="J292" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10">
       <c r="A293" t="s">
         <v>1089</v>
       </c>
@@ -13149,20 +13149,20 @@
       <c r="E293" t="s">
         <v>352</v>
       </c>
-      <c r="G293" t="s">
+      <c r="F293" t="s">
         <v>1069</v>
       </c>
       <c r="H293" t="s">
-        <v>236</v>
+        <v>1070</v>
       </c>
       <c r="I293" t="s">
         <v>353</v>
       </c>
-      <c r="K293" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="294" spans="1:11">
+      <c r="J293" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="294" spans="1:10">
       <c r="A294" t="s">
         <v>1092</v>
       </c>
@@ -13178,20 +13178,20 @@
       <c r="E294" t="s">
         <v>352</v>
       </c>
-      <c r="G294" t="s">
+      <c r="F294" t="s">
         <v>1069</v>
       </c>
       <c r="H294" t="s">
-        <v>236</v>
+        <v>1070</v>
       </c>
       <c r="I294" t="s">
         <v>353</v>
       </c>
-      <c r="K294" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="295" spans="1:11">
+      <c r="J294" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="295" spans="1:10">
       <c r="A295" t="s">
         <v>1095</v>
       </c>
@@ -13207,20 +13207,20 @@
       <c r="E295" t="s">
         <v>352</v>
       </c>
-      <c r="G295" t="s">
+      <c r="F295" t="s">
         <v>1098</v>
       </c>
       <c r="H295" t="s">
-        <v>236</v>
+        <v>1099</v>
       </c>
       <c r="I295" t="s">
         <v>353</v>
       </c>
-      <c r="K295" t="s">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="296" spans="1:11">
+      <c r="J295" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="296" spans="1:10">
       <c r="A296" t="s">
         <v>1100</v>
       </c>
@@ -13236,17 +13236,17 @@
       <c r="E296" t="s">
         <v>352</v>
       </c>
-      <c r="G296" t="s">
+      <c r="F296" t="s">
         <v>1098</v>
       </c>
       <c r="H296" t="s">
-        <v>236</v>
+        <v>1099</v>
       </c>
       <c r="I296" t="s">
         <v>353</v>
       </c>
-      <c r="K296" t="s">
-        <v>1099</v>
+      <c r="J296" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>
